--- a/data/raw/crosswalk_variedad_INCAP.xlsx
+++ b/data/raw/crosswalk_variedad_INCAP.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wfp-my.sharepoint.com/personal/maicel_monzon_wfp_org/Documents/Documents/01_analisis_ENGIH2018/data/raw/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wfp-my.sharepoint.com/personal/maicel_monzon_wfp_org/Documents/Documents/Fases_Consultoria/01_analisis_ENGIH2018/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="14_{F8BE0E5F-76BA-446B-8942-BC5680A971A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04427166-A058-4856-B5AA-A5A8B6B978CB}"/>
+  <xr:revisionPtr revIDLastSave="368" documentId="14_{F8BE0E5F-76BA-446B-8942-BC5680A971A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA8EAFD1-C70C-4AC1-B63F-C5D263252057}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Datos" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Datos!$A$1:$R$773</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Datos!$A$1:$S$773</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4937" uniqueCount="2220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5006" uniqueCount="2232">
   <si>
     <t>Cómo usar este archivo</t>
   </si>
@@ -6697,13 +6697,55 @@
   </si>
   <si>
     <t>asumi Cafe instantaneo, preparado c/agua s/azucar</t>
+  </si>
+  <si>
+    <t>pendiente a buscar en otras tablas de consumo, aliento que mas se usa, importante completar</t>
+  </si>
+  <si>
+    <t>Fila 242 "Leche fresca o cruda de vaca" (890 regs) → apunta a `70201082` = **leche de oveja**. Es un animal distinto (7% grasa vs ~3.25% de vaca). No hay "leche cruda de vaca" en INCAP; lo más cercano es la leche entera fluida (`70201015`, la misma que ya usas para UHT)</t>
+  </si>
+  <si>
+    <t>Fila 232 "Bacalao" (1613 regs) → apunta a bacalao **fresco** (`70208021`, 54mg sodio/100g). El bacalao de consumo dominicano típico es **seco salado** (`70208022`, **7027mg sodio/100g**, 130x más).</t>
+  </si>
+  <si>
+    <t>Fila 88 "Spaghetti" (2186 regs) → apunta a "Pasta enlatada, spaghetti con tomate y carne" (`70213074`). Un espagueti seco comprado normalmente no trae carne ni salsa; hay opciones de pasta simple cruda/enriquecida (`70213057`/`70213060`) que calzan esto es un recordatorio de 24 horas, o sea, lo que come, confude el codigo con el espaguetis crudo</t>
+  </si>
+  <si>
+    <t>"INCAP contiene maíz dulce cocido/congelado. Se utiliza temporalmente como proxy hasta resolver inconsistencia observada con código 70211110 (aparente colisión con Sal de mesa). Revisar posteriormente contra USDA/FNDDS."</t>
+  </si>
+  <si>
+    <t>"Malta consumida en RD corresponde a bebida de malta no alcohólica. Se utiliza temporalmente una bebida azucarada como proxy hasta incorporar una fuente externa (USDA/FNDDS) con perfil específico de malta."</t>
+  </si>
+  <si>
+    <t>Variedad local confirmada por informante dominicano.</t>
+  </si>
+  <si>
+    <t>No existe variante con coco en INCAP.
+2
+Se utiliza habichuela negra cocida como proxy.</t>
+  </si>
+  <si>
+    <t>Proxy de habichuela roja cocida.
+2
+Variante con coco no disponible en INCAP.</t>
+  </si>
+  <si>
+    <t>Consumido como guandul verde; la cáscara no se consume habitualmente.</t>
+  </si>
+  <si>
+    <t>Preparación con coco no disponible en INCAP.
+2
+Se utiliza guandul cocido como proxy principal.</t>
+  </si>
+  <si>
+    <t>Proxy basado en maíz para popcorn.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6749,8 +6791,32 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF2E2B29"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -6792,6 +6858,12 @@
         <fgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -6820,7 +6892,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -6858,6 +6930,20 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7528,29 +7614,27 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:S773"/>
+  <dimension ref="A1:R773"/>
   <sheetFormatPr defaultRowHeight="14.5" outlineLevelCol="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.1796875" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="14.08984375" customWidth="1"/>
+    <col min="1" max="1" width="14.1796875" customWidth="1"/>
+    <col min="2" max="2" width="32.54296875" customWidth="1"/>
+    <col min="3" max="3" width="14.08984375" hidden="1" customWidth="1"/>
     <col min="4" max="4" width="21.81640625" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="14.6328125" customWidth="1"/>
-    <col min="6" max="6" width="24.54296875" customWidth="1"/>
-    <col min="7" max="7" width="2.36328125" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="9.453125" customWidth="1"/>
-    <col min="10" max="10" width="17.81640625" customWidth="1"/>
+    <col min="5" max="5" width="14.6328125" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="24.54296875" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="23.453125" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="18" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="9.453125" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="17.81640625" hidden="1" customWidth="1"/>
     <col min="11" max="11" width="16.7265625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="20.36328125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12.54296875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="20" customWidth="1"/>
-    <col min="15" max="15" width="12" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="16" max="16" width="22" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="17" max="17" width="9" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="18" max="18" width="11" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="19" max="19" width="8.7265625" collapsed="1"/>
+    <col min="15" max="15" width="12" customWidth="1" outlineLevel="1"/>
+    <col min="16" max="16" width="22" customWidth="1" outlineLevel="1"/>
+    <col min="17" max="17" width="9" customWidth="1" outlineLevel="1"/>
+    <col min="18" max="18" width="11" customWidth="1" outlineLevel="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="39" x14ac:dyDescent="0.35">
@@ -7584,13 +7668,13 @@
       <c r="J1" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="K1" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="L1" s="12" t="s">
+      <c r="L1" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="M1" s="12" t="s">
+      <c r="M1" s="19" t="s">
         <v>49</v>
       </c>
       <c r="N1" s="12" t="s">
@@ -7639,11 +7723,15 @@
         <v>67</v>
       </c>
       <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
+      <c r="L2" s="15" t="s">
+        <v>66</v>
+      </c>
       <c r="M2" s="15" t="b">
         <v>1</v>
       </c>
-      <c r="N2" s="15"/>
+      <c r="N2" s="15" t="s">
+        <v>2220</v>
+      </c>
       <c r="O2" s="16" t="s">
         <v>68</v>
       </c>
@@ -7657,7 +7745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A3" s="14">
         <v>408</v>
       </c>
@@ -7711,7 +7799,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A4" s="14">
         <v>110</v>
       </c>
@@ -7761,7 +7849,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A5" s="14">
         <v>545</v>
       </c>
@@ -7816,7 +7904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A6" s="14">
         <v>288</v>
       </c>
@@ -7871,7 +7959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A7" s="14">
         <v>410</v>
       </c>
@@ -7928,7 +8016,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A8" s="14">
         <v>293</v>
       </c>
@@ -7964,7 +8052,7 @@
         <v>70216009</v>
       </c>
       <c r="L8" s="15" t="s">
-        <v>211</v>
+        <v>73</v>
       </c>
       <c r="M8" s="15" t="b">
         <v>1</v>
@@ -7983,7 +8071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A9" s="14">
         <v>2</v>
       </c>
@@ -8033,7 +8121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A10" s="14">
         <v>588</v>
       </c>
@@ -8083,7 +8171,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A11" s="14">
         <v>392</v>
       </c>
@@ -8114,10 +8202,14 @@
       <c r="J11" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="K11" s="15"/>
-      <c r="L11" s="15"/>
+      <c r="K11" s="15">
+        <v>70211060</v>
+      </c>
+      <c r="L11" s="15" t="s">
+        <v>80</v>
+      </c>
       <c r="M11" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" s="15"/>
       <c r="O11" s="16" t="s">
@@ -8133,7 +8225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A12" s="14">
         <v>515</v>
       </c>
@@ -8183,7 +8275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A13" s="14">
         <v>66</v>
       </c>
@@ -8214,12 +8306,14 @@
       <c r="J13" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="K13" s="15"/>
+      <c r="K13" s="15">
+        <v>70213002</v>
+      </c>
       <c r="L13" s="15" t="s">
-        <v>211</v>
+        <v>80</v>
       </c>
       <c r="M13" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" s="15"/>
       <c r="O13" s="16" t="s">
@@ -8235,7 +8329,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A14" s="14">
         <v>581</v>
       </c>
@@ -8292,7 +8386,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A15" s="14">
         <v>459</v>
       </c>
@@ -8347,7 +8441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A16" s="14">
         <v>594</v>
       </c>
@@ -8397,7 +8491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A17" s="14">
         <v>67</v>
       </c>
@@ -8452,7 +8546,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A18" s="14">
         <v>314</v>
       </c>
@@ -8507,7 +8601,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A19" s="14">
         <v>1</v>
       </c>
@@ -8557,7 +8651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A20" s="14">
         <v>324</v>
       </c>
@@ -8612,7 +8706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A21" s="14">
         <v>552</v>
       </c>
@@ -8662,7 +8756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A22" s="14">
         <v>178</v>
       </c>
@@ -8712,7 +8806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A23" s="14">
         <v>385</v>
       </c>
@@ -8767,7 +8861,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A24" s="14">
         <v>243</v>
       </c>
@@ -8822,7 +8916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A25" s="14">
         <v>23</v>
       </c>
@@ -8872,7 +8966,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A26" s="14">
         <v>386</v>
       </c>
@@ -8922,7 +9016,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A27" s="14">
         <v>368</v>
       </c>
@@ -8977,7 +9071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A28" s="14">
         <v>254</v>
       </c>
@@ -9032,7 +9126,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A29" s="14">
         <v>371</v>
       </c>
@@ -9065,12 +9159,14 @@
         <v>70211254</v>
       </c>
       <c r="L29" s="15" t="s">
-        <v>211</v>
+        <v>80</v>
       </c>
       <c r="M29" s="15" t="b">
         <v>1</v>
       </c>
-      <c r="N29" s="15"/>
+      <c r="N29" s="23" t="s">
+        <v>2226</v>
+      </c>
       <c r="O29" s="16" t="s">
         <v>203</v>
       </c>
@@ -9084,7 +9180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A30" s="14">
         <v>610</v>
       </c>
@@ -9139,7 +9235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A31" s="14">
         <v>311</v>
       </c>
@@ -9194,7 +9290,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A32" s="14">
         <v>420</v>
       </c>
@@ -9249,7 +9345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A33" s="14">
         <v>399</v>
       </c>
@@ -9278,8 +9374,12 @@
       <c r="J33" s="14" t="s">
         <v>231</v>
       </c>
-      <c r="K33" s="15"/>
-      <c r="L33" s="15"/>
+      <c r="K33" s="15">
+        <v>70211020</v>
+      </c>
+      <c r="L33" s="15" t="s">
+        <v>80</v>
+      </c>
       <c r="M33" s="15" t="b">
         <v>1</v>
       </c>
@@ -9297,7 +9397,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A34" s="14">
         <v>303</v>
       </c>
@@ -9328,12 +9428,14 @@
       <c r="J34" s="14" t="s">
         <v>235</v>
       </c>
-      <c r="K34" s="15"/>
+      <c r="K34" s="14">
+        <v>70216018</v>
+      </c>
       <c r="L34" s="15" t="s">
-        <v>211</v>
+        <v>80</v>
       </c>
       <c r="M34" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N34" s="15"/>
       <c r="O34" s="16" t="s">
@@ -9349,7 +9451,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A35" s="14">
         <v>586</v>
       </c>
@@ -9399,7 +9501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A36" s="14">
         <v>88</v>
       </c>
@@ -9431,7 +9533,7 @@
         <v>245</v>
       </c>
       <c r="K36" s="14">
-        <v>70213074</v>
+        <v>70213061</v>
       </c>
       <c r="L36" s="15" t="s">
         <v>80</v>
@@ -9439,7 +9541,9 @@
       <c r="M36" s="15" t="b">
         <v>1</v>
       </c>
-      <c r="N36" s="15"/>
+      <c r="N36" s="15" t="s">
+        <v>2223</v>
+      </c>
       <c r="O36" s="16" t="s">
         <v>246</v>
       </c>
@@ -9453,7 +9557,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A37" s="14">
         <v>260</v>
       </c>
@@ -9508,59 +9612,61 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="14">
+    <row r="38" spans="1:18" s="21" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="20">
         <v>159</v>
       </c>
-      <c r="B38" s="14" t="s">
+      <c r="B38" s="20" t="s">
         <v>253</v>
       </c>
-      <c r="C38" s="14">
+      <c r="C38" s="20">
         <v>2127</v>
       </c>
-      <c r="D38" s="14" t="s">
+      <c r="D38" s="20" t="s">
         <v>107</v>
       </c>
-      <c r="E38" s="14">
+      <c r="E38" s="20">
         <v>70204044</v>
       </c>
-      <c r="F38" s="14" t="s">
+      <c r="F38" s="20" t="s">
         <v>254</v>
       </c>
-      <c r="G38" s="14" t="s">
+      <c r="G38" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H38" s="14" t="s">
+      <c r="H38" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="I38" s="14">
+      <c r="I38" s="20">
         <v>70207041</v>
       </c>
-      <c r="J38" s="14" t="s">
+      <c r="J38" s="20" t="s">
         <v>255</v>
       </c>
-      <c r="K38" s="14">
+      <c r="K38" s="20">
         <v>70207041</v>
       </c>
-      <c r="L38" s="15"/>
-      <c r="M38" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="N38" s="15"/>
-      <c r="O38" s="16" t="s">
+      <c r="L38" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="M38" s="20" t="b">
+        <v>1</v>
+      </c>
+      <c r="N38" s="20"/>
+      <c r="O38" s="20" t="s">
         <v>256</v>
       </c>
-      <c r="P38" s="16" t="s">
+      <c r="P38" s="20" t="s">
         <v>257</v>
       </c>
-      <c r="Q38" s="16">
+      <c r="Q38" s="20">
         <v>63.6</v>
       </c>
-      <c r="R38" s="16" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R38" s="20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A39" s="14">
         <v>177</v>
       </c>
@@ -9594,7 +9700,9 @@
       <c r="K39" s="14">
         <v>70207022</v>
       </c>
-      <c r="L39" s="15"/>
+      <c r="L39" s="15" t="s">
+        <v>80</v>
+      </c>
       <c r="M39" s="15" t="b">
         <v>1</v>
       </c>
@@ -9612,7 +9720,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A40" s="14">
         <v>649</v>
       </c>
@@ -9643,12 +9751,18 @@
       <c r="J40" s="14" t="s">
         <v>264</v>
       </c>
-      <c r="K40" s="15"/>
-      <c r="L40" s="15"/>
+      <c r="K40" s="15">
+        <v>70217063</v>
+      </c>
+      <c r="L40" s="15" t="s">
+        <v>211</v>
+      </c>
       <c r="M40" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="N40" s="15"/>
+        <v>1</v>
+      </c>
+      <c r="N40" s="23" t="s">
+        <v>2225</v>
+      </c>
       <c r="O40" s="16" t="s">
         <v>265</v>
       </c>
@@ -9662,7 +9776,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A41" s="14">
         <v>313</v>
       </c>
@@ -9687,10 +9801,14 @@
       <c r="H41" s="14"/>
       <c r="I41" s="14"/>
       <c r="J41" s="14"/>
-      <c r="K41" s="15"/>
-      <c r="L41" s="15"/>
+      <c r="K41" s="15">
+        <v>70212130</v>
+      </c>
+      <c r="L41" s="15" t="s">
+        <v>73</v>
+      </c>
       <c r="M41" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N41" s="15"/>
       <c r="O41" s="16" t="s">
@@ -9706,7 +9824,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A42" s="14">
         <v>262</v>
       </c>
@@ -9750,7 +9868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A43" s="14">
         <v>128</v>
       </c>
@@ -9794,7 +9912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A44" s="14">
         <v>553</v>
       </c>
@@ -9838,7 +9956,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A45" s="14">
         <v>393</v>
       </c>
@@ -9863,10 +9981,14 @@
       <c r="H45" s="14"/>
       <c r="I45" s="14"/>
       <c r="J45" s="14"/>
-      <c r="K45" s="15"/>
-      <c r="L45" s="15"/>
+      <c r="K45" s="15">
+        <v>70211058</v>
+      </c>
+      <c r="L45" s="15" t="s">
+        <v>73</v>
+      </c>
       <c r="M45" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N45" s="15"/>
       <c r="O45" s="16" t="s">
@@ -9882,7 +10004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A46" s="14">
         <v>620</v>
       </c>
@@ -9926,7 +10048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A47" s="14">
         <v>87</v>
       </c>
@@ -9958,9 +10080,11 @@
         <v>289</v>
       </c>
       <c r="K47" s="14">
-        <v>70213150</v>
-      </c>
-      <c r="L47" s="15"/>
+        <v>70213061</v>
+      </c>
+      <c r="L47" s="15" t="s">
+        <v>80</v>
+      </c>
       <c r="M47" s="15" t="b">
         <v>1</v>
       </c>
@@ -9978,7 +10102,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A48" s="14">
         <v>232</v>
       </c>
@@ -10010,16 +10134,17 @@
         <v>294</v>
       </c>
       <c r="K48" s="15">
-        <f t="shared" ref="K48:K49" si="8">I48</f>
-        <v>70208021</v>
+        <v>70208022</v>
       </c>
       <c r="L48" s="15" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="M48" s="15" t="b">
         <v>1</v>
       </c>
-      <c r="N48" s="15"/>
+      <c r="N48" s="15" t="s">
+        <v>2222</v>
+      </c>
       <c r="O48" s="16" t="s">
         <v>295</v>
       </c>
@@ -10033,7 +10158,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A49" s="14">
         <v>523</v>
       </c>
@@ -10065,7 +10190,7 @@
         <v>299</v>
       </c>
       <c r="K49" s="15">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="K49" si="8">I49</f>
         <v>70222005</v>
       </c>
       <c r="L49" s="15" t="s">
@@ -10088,7 +10213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A50" s="14">
         <v>108</v>
       </c>
@@ -10122,7 +10247,9 @@
       <c r="K50" s="14">
         <v>70205023</v>
       </c>
-      <c r="L50" s="15"/>
+      <c r="L50" s="15" t="s">
+        <v>80</v>
+      </c>
       <c r="M50" s="15" t="b">
         <v>1</v>
       </c>
@@ -10140,7 +10267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A51" s="14">
         <v>396</v>
       </c>
@@ -10171,12 +10298,14 @@
       <c r="J51" s="14" t="s">
         <v>308</v>
       </c>
-      <c r="K51" s="15"/>
+      <c r="K51" s="15">
+        <v>70211010</v>
+      </c>
       <c r="L51" s="15" t="s">
-        <v>211</v>
+        <v>73</v>
       </c>
       <c r="M51" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N51" s="15"/>
       <c r="O51" s="16" t="s">
@@ -10192,7 +10321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A52" s="14">
         <v>554</v>
       </c>
@@ -10242,7 +10371,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A53" s="14">
         <v>403</v>
       </c>
@@ -10297,7 +10426,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A54" s="14">
         <v>336</v>
       </c>
@@ -10352,7 +10481,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A55" s="14">
         <v>369</v>
       </c>
@@ -10407,7 +10536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A56" s="14">
         <v>323</v>
       </c>
@@ -10462,7 +10591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A57" s="14">
         <v>237</v>
       </c>
@@ -10493,10 +10622,14 @@
       <c r="J57" s="14" t="s">
         <v>334</v>
       </c>
-      <c r="K57" s="15"/>
-      <c r="L57" s="15"/>
+      <c r="K57" s="15">
+        <v>70208040</v>
+      </c>
+      <c r="L57" s="15" t="s">
+        <v>73</v>
+      </c>
       <c r="M57" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N57" s="15"/>
       <c r="O57" s="16" t="s">
@@ -10512,7 +10645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A58" s="14">
         <v>400</v>
       </c>
@@ -10567,7 +10700,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A59" s="14">
         <v>417</v>
       </c>
@@ -10598,12 +10731,14 @@
       <c r="J59" s="14" t="s">
         <v>344</v>
       </c>
-      <c r="K59" s="15"/>
+      <c r="K59" s="14">
+        <v>70211150</v>
+      </c>
       <c r="L59" s="15" t="s">
-        <v>211</v>
+        <v>73</v>
       </c>
       <c r="M59" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N59" s="15"/>
       <c r="O59" s="16" t="s">
@@ -10619,7 +10754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A60" s="14">
         <v>401</v>
       </c>
@@ -10650,10 +10785,14 @@
       <c r="J60" s="14" t="s">
         <v>349</v>
       </c>
-      <c r="K60" s="15"/>
-      <c r="L60" s="15"/>
+      <c r="K60" s="15">
+        <v>70211157</v>
+      </c>
+      <c r="L60" s="15" t="s">
+        <v>73</v>
+      </c>
       <c r="M60" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N60" s="15"/>
       <c r="O60" s="16" t="s">
@@ -10669,7 +10808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A61" s="14">
         <v>427</v>
       </c>
@@ -10724,7 +10863,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A62" s="14">
         <v>587</v>
       </c>
@@ -10758,7 +10897,9 @@
       <c r="K62" s="14">
         <v>70217047</v>
       </c>
-      <c r="L62" s="15"/>
+      <c r="L62" s="15" t="s">
+        <v>80</v>
+      </c>
       <c r="M62" s="15" t="b">
         <v>1</v>
       </c>
@@ -10776,7 +10917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A63" s="14">
         <v>71</v>
       </c>
@@ -10831,7 +10972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A64" s="14">
         <v>389</v>
       </c>
@@ -10886,7 +11027,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A65" s="14">
         <v>174</v>
       </c>
@@ -10941,7 +11082,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A66" s="14">
         <v>611</v>
       </c>
@@ -10996,7 +11137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A67" s="14">
         <v>506</v>
       </c>
@@ -11027,28 +11168,30 @@
       <c r="J67" s="14" t="s">
         <v>382</v>
       </c>
-      <c r="K67" s="15"/>
-      <c r="L67" s="15" t="s">
-        <v>458</v>
-      </c>
-      <c r="M67" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="N67" s="15"/>
-      <c r="O67" s="16" t="s">
+      <c r="K67" s="22">
+        <v>70211110</v>
+      </c>
+      <c r="L67" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="M67" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="N67" s="14"/>
+      <c r="O67" s="14" t="s">
         <v>383</v>
       </c>
-      <c r="P67" s="16" t="s">
+      <c r="P67" s="14" t="s">
         <v>301</v>
       </c>
-      <c r="Q67" s="16">
+      <c r="Q67" s="14">
         <v>63.2</v>
       </c>
-      <c r="R67" s="16" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R67" s="14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A68" s="14">
         <v>328</v>
       </c>
@@ -11103,7 +11246,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A69" s="14">
         <v>376</v>
       </c>
@@ -11158,11 +11301,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A70" s="14">
         <v>447</v>
       </c>
-      <c r="B70" s="14" t="s">
+      <c r="B70" s="18" t="s">
         <v>394</v>
       </c>
       <c r="C70" s="14">
@@ -11189,12 +11332,18 @@
       <c r="J70" s="14" t="s">
         <v>396</v>
       </c>
-      <c r="K70" s="15"/>
-      <c r="L70" s="15"/>
+      <c r="K70" s="14">
+        <v>70211242</v>
+      </c>
+      <c r="L70" s="15" t="s">
+        <v>211</v>
+      </c>
       <c r="M70" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="N70" s="15"/>
+        <v>1</v>
+      </c>
+      <c r="N70" s="23" t="s">
+        <v>2224</v>
+      </c>
       <c r="O70" s="16" t="s">
         <v>397</v>
       </c>
@@ -11208,7 +11357,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A71" s="14">
         <v>419</v>
       </c>
@@ -11237,9 +11386,11 @@
       <c r="J71" s="14" t="s">
         <v>401</v>
       </c>
-      <c r="K71" s="15"/>
+      <c r="K71" s="15">
+        <v>70211047</v>
+      </c>
       <c r="L71" s="15" t="s">
-        <v>211</v>
+        <v>73</v>
       </c>
       <c r="M71" s="15" t="b">
         <v>1</v>
@@ -11258,7 +11409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A72" s="14">
         <v>20</v>
       </c>
@@ -11313,7 +11464,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A73" s="14">
         <v>439</v>
       </c>
@@ -11344,10 +11495,14 @@
       <c r="J73" s="14" t="s">
         <v>408</v>
       </c>
-      <c r="K73" s="15"/>
-      <c r="L73" s="15"/>
+      <c r="K73" s="15">
+        <v>70211189</v>
+      </c>
+      <c r="L73" s="15" t="s">
+        <v>80</v>
+      </c>
       <c r="M73" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N73" s="15"/>
       <c r="O73" s="16" t="s">
@@ -11363,7 +11518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A74" s="14">
         <v>514</v>
       </c>
@@ -11418,7 +11573,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A75" s="14">
         <v>541</v>
       </c>
@@ -11468,7 +11623,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A76" s="14">
         <v>242</v>
       </c>
@@ -11498,15 +11653,17 @@
         <v>421</v>
       </c>
       <c r="K76" s="14">
-        <v>70201082</v>
+        <v>70201015</v>
       </c>
       <c r="L76" s="15" t="s">
-        <v>211</v>
+        <v>80</v>
       </c>
       <c r="M76" s="15" t="b">
         <v>1</v>
       </c>
-      <c r="N76" s="15"/>
+      <c r="N76" s="15" t="s">
+        <v>2221</v>
+      </c>
       <c r="O76" s="16" t="s">
         <v>187</v>
       </c>
@@ -11520,7 +11677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A77" s="14">
         <v>58</v>
       </c>
@@ -11564,7 +11721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A78" s="14">
         <v>19</v>
       </c>
@@ -11608,7 +11765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A79" s="14">
         <v>579</v>
       </c>
@@ -11652,7 +11809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A80" s="14">
         <v>414</v>
       </c>
@@ -11696,7 +11853,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A81" s="14">
         <v>56</v>
       </c>
@@ -11740,7 +11897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A82" s="14">
         <v>3587</v>
       </c>
@@ -11784,7 +11941,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A83" s="14">
         <v>367</v>
       </c>
@@ -11809,10 +11966,14 @@
       <c r="H83" s="14"/>
       <c r="I83" s="14"/>
       <c r="J83" s="14"/>
-      <c r="K83" s="15"/>
-      <c r="L83" s="15"/>
+      <c r="K83" s="15">
+        <v>70209060</v>
+      </c>
+      <c r="L83" s="15" t="s">
+        <v>73</v>
+      </c>
       <c r="M83" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N83" s="15"/>
       <c r="O83" s="16" t="s">
@@ -11828,7 +11989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A84" s="14">
         <v>432</v>
       </c>
@@ -11872,7 +12033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A85" s="14">
         <v>458</v>
       </c>
@@ -11916,7 +12077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A86" s="14">
         <v>359</v>
       </c>
@@ -11960,7 +12121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A87" s="14">
         <v>652</v>
       </c>
@@ -11989,26 +12150,28 @@
       <c r="J87" s="14" t="s">
         <v>459</v>
       </c>
-      <c r="K87" s="15"/>
-      <c r="L87" s="15"/>
-      <c r="M87" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="N87" s="15"/>
-      <c r="O87" s="16" t="s">
+      <c r="K87" s="14"/>
+      <c r="L87" s="14" t="s">
+        <v>458</v>
+      </c>
+      <c r="M87" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="N87" s="14"/>
+      <c r="O87" s="14" t="s">
         <v>460</v>
       </c>
-      <c r="P87" s="16" t="s">
+      <c r="P87" s="14" t="s">
         <v>461</v>
       </c>
-      <c r="Q87" s="16">
+      <c r="Q87" s="14">
         <v>55.3</v>
       </c>
-      <c r="R87" s="16" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R87" s="14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A88" s="14">
         <v>340</v>
       </c>
@@ -12052,7 +12215,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A89" s="14">
         <v>645</v>
       </c>
@@ -12096,7 +12259,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A90" s="14">
         <v>395</v>
       </c>
@@ -12140,7 +12303,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A91" s="14">
         <v>18</v>
       </c>
@@ -12184,7 +12347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A92" s="14">
         <v>326</v>
       </c>
@@ -12228,7 +12391,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A93" s="14">
         <v>76</v>
       </c>
@@ -12272,7 +12435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A94" s="14">
         <v>535</v>
       </c>
@@ -12316,7 +12479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A95" s="14">
         <v>383</v>
       </c>
@@ -12360,7 +12523,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A96" s="14">
         <v>267</v>
       </c>
@@ -12404,7 +12567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A97" s="14">
         <v>496</v>
       </c>
@@ -12448,7 +12611,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A98" s="14">
         <v>3506</v>
       </c>
@@ -12492,7 +12655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A99" s="14">
         <v>228</v>
       </c>
@@ -12536,7 +12699,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A100" s="14">
         <v>317</v>
       </c>
@@ -12580,7 +12743,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A101" s="14">
         <v>251</v>
       </c>
@@ -12624,7 +12787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A102" s="14">
         <v>457</v>
       </c>
@@ -12668,7 +12831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A103" s="14">
         <v>534</v>
       </c>
@@ -12712,7 +12875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A104" s="14">
         <v>263</v>
       </c>
@@ -12756,7 +12919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A105" s="14">
         <v>86</v>
       </c>
@@ -12781,10 +12944,14 @@
       <c r="H105" s="14"/>
       <c r="I105" s="14"/>
       <c r="J105" s="14"/>
-      <c r="K105" s="15"/>
-      <c r="L105" s="15"/>
+      <c r="K105" s="15">
+        <v>70213061</v>
+      </c>
+      <c r="L105" s="15" t="s">
+        <v>80</v>
+      </c>
       <c r="M105" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N105" s="15"/>
       <c r="O105" s="16" t="s">
@@ -12800,7 +12967,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A106" s="14">
         <v>608</v>
       </c>
@@ -12844,7 +13011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A107" s="14">
         <v>573</v>
       </c>
@@ -12888,7 +13055,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A108" s="14">
         <v>4919</v>
       </c>
@@ -12932,7 +13099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A109" s="14">
         <v>527</v>
       </c>
@@ -12976,7 +13143,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A110" s="14">
         <v>374</v>
       </c>
@@ -13001,12 +13168,18 @@
       <c r="H110" s="14"/>
       <c r="I110" s="14"/>
       <c r="J110" s="14"/>
-      <c r="K110" s="15"/>
-      <c r="L110" s="15"/>
+      <c r="K110" s="15">
+        <v>70211088</v>
+      </c>
+      <c r="L110" s="15" t="s">
+        <v>73</v>
+      </c>
       <c r="M110" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="N110" s="15"/>
+        <v>1</v>
+      </c>
+      <c r="N110" s="23" t="s">
+        <v>2229</v>
+      </c>
       <c r="O110" s="16" t="s">
         <v>392</v>
       </c>
@@ -13020,7 +13193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A111" s="14">
         <v>287</v>
       </c>
@@ -13064,7 +13237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A112" s="14">
         <v>48</v>
       </c>
@@ -13108,7 +13281,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A113" s="14">
         <v>501</v>
       </c>
@@ -13152,7 +13325,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A114" s="14">
         <v>430</v>
       </c>
@@ -13196,7 +13369,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A115" s="14">
         <v>616</v>
       </c>
@@ -13240,7 +13413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A116" s="14">
         <v>315</v>
       </c>
@@ -13284,7 +13457,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A117" s="14">
         <v>265</v>
       </c>
@@ -13328,7 +13501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A118" s="14">
         <v>571</v>
       </c>
@@ -13372,7 +13545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A119" s="14">
         <v>532</v>
       </c>
@@ -13416,7 +13589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A120" s="14">
         <v>312</v>
       </c>
@@ -13460,7 +13633,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A121" s="14">
         <v>542</v>
       </c>
@@ -13504,7 +13677,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A122" s="14">
         <v>9</v>
       </c>
@@ -13548,7 +13721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A123" s="14">
         <v>97</v>
       </c>
@@ -13592,7 +13765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A124" s="14">
         <v>275</v>
       </c>
@@ -13636,7 +13809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A125" s="14">
         <v>167</v>
       </c>
@@ -13680,7 +13853,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A126" s="14">
         <v>536</v>
       </c>
@@ -13730,7 +13903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A127" s="14">
         <v>307</v>
       </c>
@@ -13774,7 +13947,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A128" s="14">
         <v>565</v>
       </c>
@@ -13818,7 +13991,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A129" s="14">
         <v>3992</v>
       </c>
@@ -13862,7 +14035,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A130" s="14">
         <v>171</v>
       </c>
@@ -13906,7 +14079,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A131" s="14">
         <v>2473</v>
       </c>
@@ -13950,7 +14123,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A132" s="14">
         <v>21</v>
       </c>
@@ -13994,7 +14167,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A133" s="14">
         <v>609</v>
       </c>
@@ -14082,7 +14255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:18" ht="88.5" x14ac:dyDescent="0.35">
       <c r="A135" s="14">
         <v>2551</v>
       </c>
@@ -14107,12 +14280,18 @@
       <c r="H135" s="14"/>
       <c r="I135" s="14"/>
       <c r="J135" s="14"/>
-      <c r="K135" s="15"/>
-      <c r="L135" s="15"/>
+      <c r="K135" s="15">
+        <v>70209063</v>
+      </c>
+      <c r="L135" s="15" t="s">
+        <v>80</v>
+      </c>
       <c r="M135" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="N135" s="15"/>
+        <v>1</v>
+      </c>
+      <c r="N135" s="25" t="s">
+        <v>2230</v>
+      </c>
       <c r="O135" s="16" t="s">
         <v>392</v>
       </c>
@@ -14126,7 +14305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A136" s="14">
         <v>337</v>
       </c>
@@ -14170,7 +14349,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A137" s="14">
         <v>4413</v>
       </c>
@@ -14195,10 +14374,14 @@
       <c r="H137" s="14"/>
       <c r="I137" s="14"/>
       <c r="J137" s="14"/>
-      <c r="K137" s="15"/>
-      <c r="L137" s="15"/>
+      <c r="K137" s="15">
+        <v>70211110</v>
+      </c>
+      <c r="L137" s="15" t="s">
+        <v>211</v>
+      </c>
       <c r="M137" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N137" s="15"/>
       <c r="O137" s="16" t="s">
@@ -14214,7 +14397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A138" s="14">
         <v>80</v>
       </c>
@@ -14258,7 +14441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A139" s="14">
         <v>398</v>
       </c>
@@ -14302,7 +14485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A140" s="14">
         <v>117</v>
       </c>
@@ -14346,7 +14529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A141" s="14">
         <v>214</v>
       </c>
@@ -14390,7 +14573,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A142" s="14">
         <v>405</v>
       </c>
@@ -14434,7 +14617,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A143" s="14">
         <v>435</v>
       </c>
@@ -14478,7 +14661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A144" s="14">
         <v>525</v>
       </c>
@@ -14522,7 +14705,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A145" s="14">
         <v>497</v>
       </c>
@@ -14566,7 +14749,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A146" s="14">
         <v>316</v>
       </c>
@@ -14610,7 +14793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A147" s="14">
         <v>5882</v>
       </c>
@@ -14654,7 +14837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A148" s="14">
         <v>235</v>
       </c>
@@ -14698,7 +14881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A149" s="14">
         <v>3588</v>
       </c>
@@ -14742,7 +14925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A150" s="14">
         <v>4915</v>
       </c>
@@ -14786,7 +14969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A151" s="14">
         <v>5</v>
       </c>
@@ -14830,7 +15013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A152" s="14">
         <v>592</v>
       </c>
@@ -14874,7 +15057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A153" s="14">
         <v>546</v>
       </c>
@@ -14918,7 +15101,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A154" s="14">
         <v>256</v>
       </c>
@@ -14962,7 +15145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A155" s="14">
         <v>5692</v>
       </c>
@@ -15006,7 +15189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A156" s="14">
         <v>173</v>
       </c>
@@ -15050,7 +15233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A157" s="14">
         <v>375</v>
       </c>
@@ -15075,10 +15258,14 @@
       <c r="H157" s="14"/>
       <c r="I157" s="14"/>
       <c r="J157" s="14"/>
-      <c r="K157" s="15"/>
-      <c r="L157" s="15"/>
+      <c r="K157" s="15">
+        <v>70209024</v>
+      </c>
+      <c r="L157" s="15" t="s">
+        <v>73</v>
+      </c>
       <c r="M157" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N157" s="15"/>
       <c r="O157" s="16" t="s">
@@ -15094,7 +15281,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A158" s="14">
         <v>4461</v>
       </c>
@@ -15138,7 +15325,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A159" s="14">
         <v>247</v>
       </c>
@@ -15182,7 +15369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A160" s="14">
         <v>297</v>
       </c>
@@ -15226,7 +15413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A161" s="14">
         <v>6199</v>
       </c>
@@ -15270,7 +15457,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A162" s="14">
         <v>658</v>
       </c>
@@ -15299,26 +15486,28 @@
       <c r="J162" s="14" t="s">
         <v>459</v>
       </c>
-      <c r="K162" s="15"/>
-      <c r="L162" s="15"/>
-      <c r="M162" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="N162" s="15"/>
-      <c r="O162" s="16" t="s">
+      <c r="K162" s="14"/>
+      <c r="L162" s="14" t="s">
+        <v>458</v>
+      </c>
+      <c r="M162" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="N162" s="14"/>
+      <c r="O162" s="14" t="s">
         <v>704</v>
       </c>
-      <c r="P162" s="16" t="s">
+      <c r="P162" s="14" t="s">
         <v>621</v>
       </c>
-      <c r="Q162" s="16">
+      <c r="Q162" s="14">
         <v>60</v>
       </c>
-      <c r="R162" s="16" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="163" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R162" s="14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A163" s="14">
         <v>131</v>
       </c>
@@ -15362,7 +15551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A164" s="14">
         <v>277</v>
       </c>
@@ -15406,7 +15595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A165" s="14">
         <v>355</v>
       </c>
@@ -15450,7 +15639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A166" s="14">
         <v>57</v>
       </c>
@@ -15494,7 +15683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A167" s="14">
         <v>341</v>
       </c>
@@ -15538,7 +15727,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A168" s="14">
         <v>426</v>
       </c>
@@ -15582,7 +15771,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A169" s="14">
         <v>498</v>
       </c>
@@ -15626,7 +15815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A170" s="14">
         <v>282</v>
       </c>
@@ -15670,7 +15859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A171" s="14">
         <v>165</v>
       </c>
@@ -15714,7 +15903,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A172" s="14">
         <v>348</v>
       </c>
@@ -15758,7 +15947,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A173" s="14">
         <v>528</v>
       </c>
@@ -15802,7 +15991,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A174" s="14">
         <v>259</v>
       </c>
@@ -15846,7 +16035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A175" s="14">
         <v>132</v>
       </c>
@@ -15890,7 +16079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A176" s="14">
         <v>507</v>
       </c>
@@ -15915,10 +16104,14 @@
       <c r="H176" s="14"/>
       <c r="I176" s="14"/>
       <c r="J176" s="14"/>
-      <c r="K176" s="15"/>
-      <c r="L176" s="15"/>
+      <c r="K176" s="15">
+        <v>70211110</v>
+      </c>
+      <c r="L176" s="15" t="s">
+        <v>211</v>
+      </c>
       <c r="M176" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N176" s="15"/>
       <c r="O176" s="16" t="s">
@@ -15934,7 +16127,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A177" s="14">
         <v>123</v>
       </c>
@@ -15978,7 +16171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A178" s="14">
         <v>112</v>
       </c>
@@ -16022,7 +16215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A179" s="14">
         <v>207</v>
       </c>
@@ -16066,7 +16259,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A180" s="14">
         <v>121</v>
       </c>
@@ -16110,7 +16303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A181" s="14">
         <v>322</v>
       </c>
@@ -16154,7 +16347,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A182" s="14">
         <v>384</v>
       </c>
@@ -16198,7 +16391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A183" s="14">
         <v>59</v>
       </c>
@@ -16242,7 +16435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A184" s="14">
         <v>327</v>
       </c>
@@ -16286,7 +16479,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A185" s="14">
         <v>5599</v>
       </c>
@@ -16330,7 +16523,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A186" s="14">
         <v>640</v>
       </c>
@@ -16374,7 +16567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A187" s="14">
         <v>433</v>
       </c>
@@ -16418,7 +16611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A188" s="14">
         <v>622</v>
       </c>
@@ -16462,7 +16655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A189" s="14">
         <v>169</v>
       </c>
@@ -16506,7 +16699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A190" s="14">
         <v>255</v>
       </c>
@@ -16550,7 +16743,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A191" s="14">
         <v>499</v>
       </c>
@@ -16594,7 +16787,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A192" s="14">
         <v>407</v>
       </c>
@@ -16638,7 +16831,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A193" s="14">
         <v>10</v>
       </c>
@@ -16682,7 +16875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A194" s="14">
         <v>522</v>
       </c>
@@ -16726,7 +16919,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A195" s="14">
         <v>4148</v>
       </c>
@@ -16770,7 +16963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A196" s="14">
         <v>261</v>
       </c>
@@ -16814,7 +17007,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A197" s="14">
         <v>51</v>
       </c>
@@ -16858,7 +17051,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A198" s="14">
         <v>443</v>
       </c>
@@ -16883,10 +17076,14 @@
       <c r="H198" s="14"/>
       <c r="I198" s="14"/>
       <c r="J198" s="14"/>
-      <c r="K198" s="15"/>
-      <c r="L198" s="15"/>
+      <c r="K198" s="15">
+        <v>70209049</v>
+      </c>
+      <c r="L198" s="15" t="s">
+        <v>80</v>
+      </c>
       <c r="M198" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N198" s="15"/>
       <c r="O198" s="16" t="s">
@@ -16902,7 +17099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A199" s="14">
         <v>6</v>
       </c>
@@ -16946,7 +17143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A200" s="14">
         <v>650</v>
       </c>
@@ -16990,7 +17187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A201" s="14">
         <v>4882</v>
       </c>
@@ -17034,7 +17231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A202" s="14">
         <v>625</v>
       </c>
@@ -17078,7 +17275,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A203" s="14">
         <v>3809</v>
       </c>
@@ -17122,7 +17319,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A204" s="14">
         <v>623</v>
       </c>
@@ -17166,7 +17363,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A205" s="14">
         <v>185</v>
       </c>
@@ -17210,7 +17407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A206" s="14">
         <v>1892</v>
       </c>
@@ -17254,7 +17451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A207" s="14">
         <v>600</v>
       </c>
@@ -17298,7 +17495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A208" s="14">
         <v>334</v>
       </c>
@@ -17342,7 +17539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A209" s="14">
         <v>563</v>
       </c>
@@ -17386,7 +17583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A210" s="14">
         <v>3021</v>
       </c>
@@ -17430,7 +17627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A211" s="14">
         <v>183</v>
       </c>
@@ -17474,7 +17671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A212" s="14">
         <v>4149</v>
       </c>
@@ -17518,7 +17715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A213" s="14">
         <v>591</v>
       </c>
@@ -17562,7 +17759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A214" s="14">
         <v>379</v>
       </c>
@@ -17606,7 +17803,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A215" s="14">
         <v>366</v>
       </c>
@@ -17631,10 +17828,14 @@
       <c r="H215" s="14"/>
       <c r="I215" s="14"/>
       <c r="J215" s="14"/>
-      <c r="K215" s="15"/>
-      <c r="L215" s="15"/>
+      <c r="K215" s="15">
+        <v>70209003</v>
+      </c>
+      <c r="L215" s="15" t="s">
+        <v>73</v>
+      </c>
       <c r="M215" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N215" s="15"/>
       <c r="O215" s="16" t="s">
@@ -17650,7 +17851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A216" s="14">
         <v>83</v>
       </c>
@@ -17675,10 +17876,14 @@
       <c r="H216" s="14"/>
       <c r="I216" s="14"/>
       <c r="J216" s="14"/>
-      <c r="K216" s="15"/>
-      <c r="L216" s="15"/>
+      <c r="K216" s="15">
+        <v>70213050</v>
+      </c>
+      <c r="L216" s="15" t="s">
+        <v>73</v>
+      </c>
       <c r="M216" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N216" s="15"/>
       <c r="O216" s="16" t="s">
@@ -17694,7 +17899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A217" s="14">
         <v>3993</v>
       </c>
@@ -17738,7 +17943,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A218" s="14">
         <v>154</v>
       </c>
@@ -17782,7 +17987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A219" s="14">
         <v>49</v>
       </c>
@@ -17826,7 +18031,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A220" s="14">
         <v>638</v>
       </c>
@@ -17870,7 +18075,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="221" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A221" s="14">
         <v>269</v>
       </c>
@@ -17914,7 +18119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A222" s="14">
         <v>65</v>
       </c>
@@ -17958,7 +18163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A223" s="14">
         <v>145</v>
       </c>
@@ -18002,7 +18207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A224" s="14">
         <v>206</v>
       </c>
@@ -18046,7 +18251,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A225" s="14">
         <v>318</v>
       </c>
@@ -18090,7 +18295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A226" s="14">
         <v>4916</v>
       </c>
@@ -18134,7 +18339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A227" s="14">
         <v>268</v>
       </c>
@@ -18178,7 +18383,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="228" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A228" s="14">
         <v>245</v>
       </c>
@@ -18222,7 +18427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A229" s="14">
         <v>13</v>
       </c>
@@ -18266,7 +18471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A230" s="14">
         <v>321</v>
       </c>
@@ -18310,7 +18515,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="231" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A231" s="14">
         <v>202</v>
       </c>
@@ -18354,7 +18559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="232" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A232" s="14">
         <v>134</v>
       </c>
@@ -18398,7 +18603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A233" s="14">
         <v>377</v>
       </c>
@@ -18442,7 +18647,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="234" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A234" s="14">
         <v>166</v>
       </c>
@@ -18486,7 +18691,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A235" s="14">
         <v>382</v>
       </c>
@@ -18530,7 +18735,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A236" s="14">
         <v>511</v>
       </c>
@@ -18574,7 +18779,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="237" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A237" s="14">
         <v>347</v>
       </c>
@@ -18618,7 +18823,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="238" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A238" s="14">
         <v>8</v>
       </c>
@@ -18662,7 +18867,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="239" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A239" s="14">
         <v>101</v>
       </c>
@@ -18706,7 +18911,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="240" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A240" s="14">
         <v>143</v>
       </c>
@@ -18750,7 +18955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A241" s="14">
         <v>412</v>
       </c>
@@ -18794,7 +18999,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="242" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A242" s="14">
         <v>352</v>
       </c>
@@ -18838,7 +19043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A243" s="14">
         <v>209</v>
       </c>
@@ -18882,7 +19087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="244" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A244" s="14">
         <v>578</v>
       </c>
@@ -18926,7 +19131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A245" s="14">
         <v>257</v>
       </c>
@@ -18970,7 +19175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A246" s="14">
         <v>624</v>
       </c>
@@ -19014,7 +19219,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A247" s="14">
         <v>320</v>
       </c>
@@ -19058,7 +19263,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="248" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A248" s="14">
         <v>370</v>
       </c>
@@ -19083,10 +19288,14 @@
       <c r="H248" s="14"/>
       <c r="I248" s="14"/>
       <c r="J248" s="14"/>
-      <c r="K248" s="15"/>
-      <c r="L248" s="15"/>
+      <c r="K248" s="15">
+        <v>70211254</v>
+      </c>
+      <c r="L248" s="15" t="s">
+        <v>80</v>
+      </c>
       <c r="M248" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N248" s="15"/>
       <c r="O248" s="16" t="s">
@@ -19102,7 +19311,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A249" s="14">
         <v>484</v>
       </c>
@@ -19146,7 +19355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A250" s="14">
         <v>451</v>
       </c>
@@ -19190,7 +19399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A251" s="14">
         <v>162</v>
       </c>
@@ -19234,7 +19443,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="252" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A252" s="14">
         <v>558</v>
       </c>
@@ -19278,7 +19487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A253" s="14">
         <v>467</v>
       </c>
@@ -19322,7 +19531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A254" s="14">
         <v>3807</v>
       </c>
@@ -19366,7 +19575,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="255" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A255" s="14">
         <v>99</v>
       </c>
@@ -19410,7 +19619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A256" s="14">
         <v>555</v>
       </c>
@@ -19454,7 +19663,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="257" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A257" s="14">
         <v>2874</v>
       </c>
@@ -19498,7 +19707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A258" s="14">
         <v>491</v>
       </c>
@@ -19542,7 +19751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A259" s="14">
         <v>335</v>
       </c>
@@ -19586,7 +19795,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="260" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A260" s="14">
         <v>3812</v>
       </c>
@@ -19630,7 +19839,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="261" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A261" s="14">
         <v>208</v>
       </c>
@@ -19674,7 +19883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="262" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A262" s="14">
         <v>127</v>
       </c>
@@ -19718,7 +19927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A263" s="14">
         <v>612</v>
       </c>
@@ -19762,7 +19971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A264" s="14">
         <v>204</v>
       </c>
@@ -19806,7 +20015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="265" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A265" s="14">
         <v>404</v>
       </c>
@@ -19850,7 +20059,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="266" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A266" s="14">
         <v>236</v>
       </c>
@@ -19894,7 +20103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A267" s="14">
         <v>436</v>
       </c>
@@ -19938,7 +20147,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="268" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A268" s="14">
         <v>221</v>
       </c>
@@ -19982,7 +20191,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="269" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A269" s="14">
         <v>635</v>
       </c>
@@ -20026,7 +20235,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="270" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A270" s="14">
         <v>6467</v>
       </c>
@@ -20070,7 +20279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A271" s="14">
         <v>84</v>
       </c>
@@ -20095,10 +20304,14 @@
       <c r="H271" s="14"/>
       <c r="I271" s="14"/>
       <c r="J271" s="14"/>
-      <c r="K271" s="15"/>
-      <c r="L271" s="15"/>
+      <c r="K271" s="15">
+        <v>70213163</v>
+      </c>
+      <c r="L271" s="15" t="s">
+        <v>73</v>
+      </c>
       <c r="M271" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N271" s="15"/>
       <c r="O271" s="16" t="s">
@@ -20114,7 +20327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A272" s="14">
         <v>331</v>
       </c>
@@ -20158,7 +20371,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="273" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A273" s="14">
         <v>415</v>
       </c>
@@ -20202,7 +20415,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="274" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A274" s="14">
         <v>629</v>
       </c>
@@ -20246,7 +20459,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="275" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A275" s="14">
         <v>4913</v>
       </c>
@@ -20290,7 +20503,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="276" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A276" s="14">
         <v>126</v>
       </c>
@@ -20334,7 +20547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A277" s="14">
         <v>120</v>
       </c>
@@ -20378,7 +20591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A278" s="14">
         <v>72</v>
       </c>
@@ -20422,7 +20635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A279" s="14">
         <v>470</v>
       </c>
@@ -20466,7 +20679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A280" s="14">
         <v>122</v>
       </c>
@@ -20510,7 +20723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A281" s="14">
         <v>114</v>
       </c>
@@ -20554,7 +20767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A282" s="14">
         <v>442</v>
       </c>
@@ -20579,10 +20792,14 @@
       <c r="H282" s="14"/>
       <c r="I282" s="14"/>
       <c r="J282" s="14"/>
-      <c r="K282" s="15"/>
-      <c r="L282" s="15"/>
+      <c r="K282" s="15">
+        <v>70209058</v>
+      </c>
+      <c r="L282" s="15" t="s">
+        <v>80</v>
+      </c>
       <c r="M282" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N282" s="15"/>
       <c r="O282" s="16" t="s">
@@ -20598,7 +20815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A283" s="14">
         <v>281</v>
       </c>
@@ -20642,7 +20859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A284" s="14">
         <v>452</v>
       </c>
@@ -20686,7 +20903,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="285" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A285" s="14">
         <v>521</v>
       </c>
@@ -20730,7 +20947,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="286" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A286" s="14">
         <v>130</v>
       </c>
@@ -20774,7 +20991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A287" s="14">
         <v>5684</v>
       </c>
@@ -20818,7 +21035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A288" s="14">
         <v>300</v>
       </c>
@@ -20862,7 +21079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A289" s="14">
         <v>296</v>
       </c>
@@ -20906,7 +21123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A290" s="14">
         <v>24</v>
       </c>
@@ -20950,7 +21167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A291" s="14">
         <v>264</v>
       </c>
@@ -20994,7 +21211,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="292" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A292" s="14">
         <v>493</v>
       </c>
@@ -21038,7 +21255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A293" s="14">
         <v>3571</v>
       </c>
@@ -21082,7 +21299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A294" s="14">
         <v>468</v>
       </c>
@@ -21126,7 +21343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A295" s="14">
         <v>353</v>
       </c>
@@ -21170,7 +21387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A296" s="14">
         <v>556</v>
       </c>
@@ -21214,7 +21431,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="297" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A297" s="14">
         <v>4917</v>
       </c>
@@ -21258,7 +21475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A298" s="14">
         <v>5042</v>
       </c>
@@ -21302,7 +21519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A299" s="14">
         <v>453</v>
       </c>
@@ -21346,7 +21563,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="300" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A300" s="14">
         <v>5839</v>
       </c>
@@ -21390,7 +21607,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="301" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A301" s="14">
         <v>5683</v>
       </c>
@@ -21434,7 +21651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A302" s="14">
         <v>196</v>
       </c>
@@ -21478,7 +21695,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="303" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A303" s="14">
         <v>137</v>
       </c>
@@ -21522,7 +21739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A304" s="14">
         <v>295</v>
       </c>
@@ -21566,7 +21783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A305" s="14">
         <v>223</v>
       </c>
@@ -21610,7 +21827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A306" s="14">
         <v>4</v>
       </c>
@@ -21654,7 +21871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A307" s="14">
         <v>319</v>
       </c>
@@ -21698,7 +21915,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="308" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A308" s="14">
         <v>494</v>
       </c>
@@ -21742,7 +21959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A309" s="14">
         <v>5965</v>
       </c>
@@ -21786,7 +22003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A310" s="14">
         <v>4611</v>
       </c>
@@ -21830,7 +22047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="311" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A311" s="14">
         <v>606</v>
       </c>
@@ -21874,7 +22091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A312" s="14">
         <v>216</v>
       </c>
@@ -21918,7 +22135,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="313" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A313" s="14">
         <v>94</v>
       </c>
@@ -21962,7 +22179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A314" s="14">
         <v>6545</v>
       </c>
@@ -22006,7 +22223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A315" s="14">
         <v>356</v>
       </c>
@@ -22050,7 +22267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A316" s="14">
         <v>438</v>
       </c>
@@ -22075,10 +22292,14 @@
       <c r="H316" s="14"/>
       <c r="I316" s="14"/>
       <c r="J316" s="14"/>
-      <c r="K316" s="15"/>
-      <c r="L316" s="15"/>
+      <c r="K316" s="15">
+        <v>70209063</v>
+      </c>
+      <c r="L316" s="15" t="s">
+        <v>80</v>
+      </c>
       <c r="M316" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N316" s="15"/>
       <c r="O316" s="16" t="s">
@@ -22094,7 +22315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A317" s="14">
         <v>164</v>
       </c>
@@ -22138,7 +22359,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="318" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A318" s="14">
         <v>3</v>
       </c>
@@ -22182,7 +22403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A319" s="14">
         <v>6446</v>
       </c>
@@ -22226,7 +22447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="320" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A320" s="14">
         <v>529</v>
       </c>
@@ -22270,7 +22491,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="321" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A321" s="14">
         <v>596</v>
       </c>
@@ -22314,7 +22535,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="322" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A322" s="14">
         <v>98</v>
       </c>
@@ -22358,7 +22579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A323" s="14">
         <v>537</v>
       </c>
@@ -22406,7 +22627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A324" s="14">
         <v>5049</v>
       </c>
@@ -22450,7 +22671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A325" s="14">
         <v>3810</v>
       </c>
@@ -22494,7 +22715,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="326" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A326" s="14">
         <v>6031</v>
       </c>
@@ -22538,7 +22759,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="327" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A327" s="14">
         <v>339</v>
       </c>
@@ -22582,7 +22803,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="328" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A328" s="14">
         <v>330</v>
       </c>
@@ -22626,7 +22847,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="329" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A329" s="14">
         <v>351</v>
       </c>
@@ -22670,7 +22891,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="330" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A330" s="14">
         <v>346</v>
       </c>
@@ -22714,7 +22935,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="331" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A331" s="14">
         <v>184</v>
       </c>
@@ -22758,7 +22979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="332" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A332" s="14">
         <v>53</v>
       </c>
@@ -22802,7 +23023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A333" s="14">
         <v>423</v>
       </c>
@@ -22846,7 +23067,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="334" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A334" s="14">
         <v>413</v>
       </c>
@@ -22890,7 +23111,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="335" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A335" s="14">
         <v>560</v>
       </c>
@@ -22934,7 +23155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="336" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A336" s="14">
         <v>575</v>
       </c>
@@ -22978,7 +23199,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="337" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A337" s="14">
         <v>566</v>
       </c>
@@ -23022,7 +23243,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="338" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A338" s="14">
         <v>75</v>
       </c>
@@ -23066,7 +23287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="339" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A339" s="14">
         <v>149</v>
       </c>
@@ -23110,7 +23331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="340" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A340" s="14">
         <v>222</v>
       </c>
@@ -23154,7 +23375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="341" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A341" s="14">
         <v>378</v>
       </c>
@@ -23198,7 +23419,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="342" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A342" s="14">
         <v>3504</v>
       </c>
@@ -23242,7 +23463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="343" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A343" s="14">
         <v>92</v>
       </c>
@@ -23286,7 +23507,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="344" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A344" s="14">
         <v>512</v>
       </c>
@@ -23330,7 +23551,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="345" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A345" s="14">
         <v>613</v>
       </c>
@@ -23374,7 +23595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="346" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A346" s="14">
         <v>634</v>
       </c>
@@ -23418,7 +23639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="347" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A347" s="14">
         <v>107</v>
       </c>
@@ -23462,7 +23683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="348" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A348" s="14">
         <v>380</v>
       </c>
@@ -23506,7 +23727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="349" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A349" s="14">
         <v>194</v>
       </c>
@@ -23550,7 +23771,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="350" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A350" s="14">
         <v>478</v>
       </c>
@@ -23594,7 +23815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="351" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A351" s="14">
         <v>105</v>
       </c>
@@ -23638,7 +23859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="352" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A352" s="14">
         <v>4702</v>
       </c>
@@ -23682,7 +23903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="353" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A353" s="14">
         <v>544</v>
       </c>
@@ -23726,7 +23947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="354" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A354" s="14">
         <v>548</v>
       </c>
@@ -23770,7 +23991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="355" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A355" s="14">
         <v>598</v>
       </c>
@@ -23814,7 +24035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="356" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A356" s="14">
         <v>325</v>
       </c>
@@ -23858,7 +24079,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="357" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A357" s="14">
         <v>195</v>
       </c>
@@ -23902,7 +24123,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="358" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A358" s="14">
         <v>78</v>
       </c>
@@ -23946,7 +24167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="359" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A359" s="14">
         <v>655</v>
       </c>
@@ -23975,26 +24196,28 @@
       <c r="J359" s="14" t="s">
         <v>459</v>
       </c>
-      <c r="K359" s="15"/>
-      <c r="L359" s="15"/>
-      <c r="M359" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="N359" s="15"/>
-      <c r="O359" s="16" t="s">
+      <c r="K359" s="14"/>
+      <c r="L359" s="14" t="s">
+        <v>458</v>
+      </c>
+      <c r="M359" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="N359" s="14"/>
+      <c r="O359" s="14" t="s">
         <v>1262</v>
       </c>
-      <c r="P359" s="16" t="s">
+      <c r="P359" s="14" t="s">
         <v>1263</v>
       </c>
-      <c r="Q359" s="16">
+      <c r="Q359" s="14">
         <v>53.3</v>
       </c>
-      <c r="R359" s="16" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="360" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R359" s="14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="360" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A360" s="14">
         <v>4948</v>
       </c>
@@ -24038,7 +24261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="361" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A361" s="14">
         <v>203</v>
       </c>
@@ -24082,7 +24305,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="362" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A362" s="14">
         <v>2848</v>
       </c>
@@ -24126,7 +24349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="363" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A363" s="14">
         <v>618</v>
       </c>
@@ -24170,7 +24393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="364" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A364" s="14">
         <v>615</v>
       </c>
@@ -24214,7 +24437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="365" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A365" s="14">
         <v>524</v>
       </c>
@@ -24258,7 +24481,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="366" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A366" s="14">
         <v>4399</v>
       </c>
@@ -24302,7 +24525,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="367" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A367" s="14">
         <v>160</v>
       </c>
@@ -24346,7 +24569,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="368" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A368" s="14">
         <v>4414</v>
       </c>
@@ -24390,7 +24613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="369" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A369" s="14">
         <v>6105</v>
       </c>
@@ -24434,7 +24657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="370" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A370" s="14">
         <v>4406</v>
       </c>
@@ -24459,10 +24682,14 @@
       <c r="H370" s="14"/>
       <c r="I370" s="14"/>
       <c r="J370" s="14"/>
-      <c r="K370" s="15"/>
-      <c r="L370" s="15"/>
+      <c r="K370" s="15">
+        <v>70213032</v>
+      </c>
+      <c r="L370" s="15" t="s">
+        <v>80</v>
+      </c>
       <c r="M370" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N370" s="15"/>
       <c r="O370" s="16" t="s">
@@ -24478,7 +24705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="371" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A371" s="14">
         <v>5595</v>
       </c>
@@ -24522,7 +24749,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="372" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A372" s="14">
         <v>559</v>
       </c>
@@ -24566,7 +24793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="373" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A373" s="14">
         <v>4918</v>
       </c>
@@ -24610,7 +24837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="374" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A374" s="14">
         <v>431</v>
       </c>
@@ -24635,10 +24862,14 @@
       <c r="H374" s="14"/>
       <c r="I374" s="14"/>
       <c r="J374" s="14"/>
-      <c r="K374" s="15"/>
-      <c r="L374" s="15"/>
+      <c r="K374" s="15">
+        <v>70211078</v>
+      </c>
+      <c r="L374" s="15" t="s">
+        <v>80</v>
+      </c>
       <c r="M374" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N374" s="15"/>
       <c r="O374" s="16" t="s">
@@ -24654,7 +24885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="375" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A375" s="14">
         <v>4701</v>
       </c>
@@ -24698,7 +24929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="376" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A376" s="14">
         <v>113</v>
       </c>
@@ -24742,7 +24973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="377" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A377" s="14">
         <v>104</v>
       </c>
@@ -24786,7 +25017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="378" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A378" s="14">
         <v>6440</v>
       </c>
@@ -24830,7 +25061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="379" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A379" s="14">
         <v>111</v>
       </c>
@@ -24874,7 +25105,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="380" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A380" s="14">
         <v>5932</v>
       </c>
@@ -24918,7 +25149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="381" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A381" s="14">
         <v>306</v>
       </c>
@@ -24962,7 +25193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="382" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A382" s="14">
         <v>212</v>
       </c>
@@ -25006,7 +25237,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="383" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A383" s="14">
         <v>2632</v>
       </c>
@@ -25050,7 +25281,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="384" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A384" s="14">
         <v>280</v>
       </c>
@@ -25094,7 +25325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="385" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A385" s="14">
         <v>170</v>
       </c>
@@ -25138,7 +25369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="386" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A386" s="14">
         <v>1536</v>
       </c>
@@ -25167,26 +25398,28 @@
       <c r="J386" s="14" t="s">
         <v>459</v>
       </c>
-      <c r="K386" s="15"/>
-      <c r="L386" s="15"/>
-      <c r="M386" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="N386" s="15"/>
-      <c r="O386" s="16" t="s">
+      <c r="K386" s="14"/>
+      <c r="L386" s="14" t="s">
+        <v>458</v>
+      </c>
+      <c r="M386" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="N386" s="14"/>
+      <c r="O386" s="14" t="s">
         <v>1328</v>
       </c>
-      <c r="P386" s="16" t="s">
+      <c r="P386" s="14" t="s">
         <v>1329</v>
       </c>
-      <c r="Q386" s="16">
+      <c r="Q386" s="14">
         <v>58.8</v>
       </c>
-      <c r="R386" s="16" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="387" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R386" s="14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="387" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A387" s="14">
         <v>200</v>
       </c>
@@ -25230,7 +25463,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="388" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A388" s="14">
         <v>82</v>
       </c>
@@ -25255,10 +25488,14 @@
       <c r="H388" s="14"/>
       <c r="I388" s="14"/>
       <c r="J388" s="14"/>
-      <c r="K388" s="15"/>
-      <c r="L388" s="15"/>
+      <c r="K388" s="15">
+        <v>70213050</v>
+      </c>
+      <c r="L388" s="15" t="s">
+        <v>80</v>
+      </c>
       <c r="M388" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N388" s="15"/>
       <c r="O388" s="16" t="s">
@@ -25274,7 +25511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="389" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A389" s="14">
         <v>4401</v>
       </c>
@@ -25318,7 +25555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="390" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A390" s="14">
         <v>6304</v>
       </c>
@@ -25362,7 +25599,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="391" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A391" s="14">
         <v>5490</v>
       </c>
@@ -25406,7 +25643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="392" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A392" s="14">
         <v>182</v>
       </c>
@@ -25450,7 +25687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="393" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A393" s="14">
         <v>466</v>
       </c>
@@ -25494,7 +25731,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="394" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A394" s="14">
         <v>3577</v>
       </c>
@@ -25538,7 +25775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="395" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A395" s="14">
         <v>409</v>
       </c>
@@ -25582,7 +25819,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="396" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A396" s="14">
         <v>140</v>
       </c>
@@ -25626,7 +25863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="397" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A397" s="14">
         <v>2869</v>
       </c>
@@ -25670,7 +25907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="398" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A398" s="14">
         <v>3242</v>
       </c>
@@ -25714,7 +25951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="399" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A399" s="14">
         <v>456</v>
       </c>
@@ -25758,7 +25995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="400" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A400" s="14">
         <v>7890</v>
       </c>
@@ -25802,7 +26039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="401" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A401" s="14">
         <v>3546</v>
       </c>
@@ -25846,7 +26083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="402" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A402" s="14">
         <v>3073</v>
       </c>
@@ -25871,10 +26108,14 @@
       <c r="H402" s="14"/>
       <c r="I402" s="14"/>
       <c r="J402" s="14"/>
-      <c r="K402" s="15"/>
-      <c r="L402" s="15"/>
+      <c r="K402" s="15">
+        <v>70211189</v>
+      </c>
+      <c r="L402" s="15" t="s">
+        <v>80</v>
+      </c>
       <c r="M402" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N402" s="15"/>
       <c r="O402" s="16" t="s">
@@ -25890,7 +26131,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="403" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A403" s="14">
         <v>213</v>
       </c>
@@ -25934,7 +26175,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="404" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A404" s="14">
         <v>4952</v>
       </c>
@@ -25978,7 +26219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="405" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A405" s="14">
         <v>77</v>
       </c>
@@ -26022,7 +26263,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="406" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A406" s="14">
         <v>6579</v>
       </c>
@@ -26066,7 +26307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="407" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A407" s="14">
         <v>118</v>
       </c>
@@ -26110,7 +26351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="408" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A408" s="14">
         <v>434</v>
       </c>
@@ -26154,7 +26395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="409" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A409" s="14">
         <v>4542</v>
       </c>
@@ -26202,7 +26443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="410" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A410" s="14">
         <v>73</v>
       </c>
@@ -26246,7 +26487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="411" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A411" s="14">
         <v>642</v>
       </c>
@@ -26290,7 +26531,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="412" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A412" s="14">
         <v>3925</v>
       </c>
@@ -26334,7 +26575,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="413" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A413" s="14">
         <v>74</v>
       </c>
@@ -26378,7 +26619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="414" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A414" s="14">
         <v>3586</v>
       </c>
@@ -26422,7 +26663,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="415" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A415" s="14">
         <v>590</v>
       </c>
@@ -26466,7 +26707,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="416" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A416" s="14">
         <v>32</v>
       </c>
@@ -26491,12 +26732,18 @@
       <c r="H416" s="14"/>
       <c r="I416" s="14"/>
       <c r="J416" s="14"/>
-      <c r="K416" s="15"/>
-      <c r="L416" s="15"/>
+      <c r="K416" s="15">
+        <v>70213163</v>
+      </c>
+      <c r="L416" s="15" t="s">
+        <v>80</v>
+      </c>
       <c r="M416" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="N416" s="15"/>
+        <v>1</v>
+      </c>
+      <c r="N416" s="23" t="s">
+        <v>2231</v>
+      </c>
       <c r="O416" s="16" t="s">
         <v>1398</v>
       </c>
@@ -26510,7 +26757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="417" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A417" s="14">
         <v>3096</v>
       </c>
@@ -26554,7 +26801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="418" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A418" s="14">
         <v>373</v>
       </c>
@@ -26598,7 +26845,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="419" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A419" s="14">
         <v>397</v>
       </c>
@@ -26642,7 +26889,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="420" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A420" s="14">
         <v>5883</v>
       </c>
@@ -26686,7 +26933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="421" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A421" s="14">
         <v>69</v>
       </c>
@@ -26730,7 +26977,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="422" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A422" s="14">
         <v>133</v>
       </c>
@@ -26774,7 +27021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="423" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A423" s="14">
         <v>657</v>
       </c>
@@ -26803,26 +27050,28 @@
       <c r="J423" s="14" t="s">
         <v>459</v>
       </c>
-      <c r="K423" s="15"/>
-      <c r="L423" s="15"/>
-      <c r="M423" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="N423" s="15"/>
-      <c r="O423" s="16" t="s">
+      <c r="K423" s="14"/>
+      <c r="L423" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="M423" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="N423" s="14"/>
+      <c r="O423" s="14" t="s">
         <v>1262</v>
       </c>
-      <c r="P423" s="16" t="s">
+      <c r="P423" s="14" t="s">
         <v>1418</v>
       </c>
-      <c r="Q423" s="16">
+      <c r="Q423" s="14">
         <v>55.6</v>
       </c>
-      <c r="R423" s="16" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="424" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R423" s="14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="424" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A424" s="14">
         <v>106</v>
       </c>
@@ -26866,7 +27115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="425" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A425" s="14">
         <v>6451</v>
       </c>
@@ -26910,7 +27159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="426" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A426" s="14">
         <v>290</v>
       </c>
@@ -26954,7 +27203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="427" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A427" s="14">
         <v>161</v>
       </c>
@@ -26998,7 +27247,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="428" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A428" s="14">
         <v>4199</v>
       </c>
@@ -27042,7 +27291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="429" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:18" ht="76" x14ac:dyDescent="0.35">
       <c r="A429" s="14">
         <v>3076</v>
       </c>
@@ -27067,12 +27316,18 @@
       <c r="H429" s="14"/>
       <c r="I429" s="14"/>
       <c r="J429" s="14"/>
-      <c r="K429" s="15"/>
-      <c r="L429" s="15"/>
+      <c r="K429" s="15">
+        <v>70209058</v>
+      </c>
+      <c r="L429" s="15" t="s">
+        <v>80</v>
+      </c>
       <c r="M429" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="N429" s="15"/>
+        <v>1</v>
+      </c>
+      <c r="N429" s="25" t="s">
+        <v>2227</v>
+      </c>
       <c r="O429" s="16" t="s">
         <v>1437</v>
       </c>
@@ -27086,7 +27341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="430" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A430" s="14">
         <v>4460</v>
       </c>
@@ -27130,7 +27385,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="431" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A431" s="14">
         <v>3553</v>
       </c>
@@ -27174,7 +27429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="432" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A432" s="14">
         <v>125</v>
       </c>
@@ -27218,7 +27473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="433" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A433" s="14">
         <v>17</v>
       </c>
@@ -27262,7 +27517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="434" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A434" s="14">
         <v>488</v>
       </c>
@@ -27306,7 +27561,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="435" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A435" s="14">
         <v>576</v>
       </c>
@@ -27350,7 +27605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="436" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A436" s="14">
         <v>332</v>
       </c>
@@ -27394,7 +27649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="437" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A437" s="14">
         <v>5362</v>
       </c>
@@ -27438,7 +27693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="438" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A438" s="14">
         <v>5908</v>
       </c>
@@ -27482,7 +27737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="439" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A439" s="14">
         <v>8776</v>
       </c>
@@ -27526,7 +27781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="440" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A440" s="14">
         <v>6274</v>
       </c>
@@ -27570,7 +27825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="441" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A441" s="14">
         <v>6071</v>
       </c>
@@ -27614,7 +27869,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="442" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A442" s="14">
         <v>6213</v>
       </c>
@@ -27658,7 +27913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="443" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A443" s="14">
         <v>551</v>
       </c>
@@ -27702,7 +27957,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="444" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A444" s="14">
         <v>5850</v>
       </c>
@@ -27746,7 +28001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="445" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A445" s="14">
         <v>437</v>
       </c>
@@ -27790,7 +28045,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="446" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A446" s="14">
         <v>276</v>
       </c>
@@ -27834,7 +28089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="447" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A447" s="14">
         <v>14</v>
       </c>
@@ -27878,7 +28133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="448" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A448" s="14">
         <v>201</v>
       </c>
@@ -27922,7 +28177,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="449" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A449" s="14">
         <v>299</v>
       </c>
@@ -27966,7 +28221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="450" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A450" s="14">
         <v>530</v>
       </c>
@@ -28010,7 +28265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="451" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A451" s="14">
         <v>15</v>
       </c>
@@ -28054,7 +28309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="452" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A452" s="14">
         <v>115</v>
       </c>
@@ -28098,7 +28353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="453" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A453" s="14">
         <v>653</v>
       </c>
@@ -28127,26 +28382,28 @@
       <c r="J453" s="14" t="s">
         <v>459</v>
       </c>
-      <c r="K453" s="15"/>
-      <c r="L453" s="15"/>
-      <c r="M453" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="N453" s="15"/>
-      <c r="O453" s="16" t="s">
+      <c r="K453" s="14"/>
+      <c r="L453" s="14" t="s">
+        <v>458</v>
+      </c>
+      <c r="M453" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="N453" s="14"/>
+      <c r="O453" s="14" t="s">
         <v>460</v>
       </c>
-      <c r="P453" s="16" t="s">
+      <c r="P453" s="14" t="s">
         <v>1505</v>
       </c>
-      <c r="Q453" s="16">
+      <c r="Q453" s="14">
         <v>54.5</v>
       </c>
-      <c r="R453" s="16" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="454" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R453" s="14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="454" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A454" s="14">
         <v>440</v>
       </c>
@@ -28190,7 +28447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="455" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A455" s="14">
         <v>654</v>
       </c>
@@ -28219,26 +28476,28 @@
       <c r="J455" s="14" t="s">
         <v>459</v>
       </c>
-      <c r="K455" s="15"/>
-      <c r="L455" s="15"/>
-      <c r="M455" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="N455" s="15"/>
-      <c r="O455" s="16" t="s">
+      <c r="K455" s="14"/>
+      <c r="L455" s="14" t="s">
+        <v>458</v>
+      </c>
+      <c r="M455" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="N455" s="14"/>
+      <c r="O455" s="14" t="s">
         <v>1511</v>
       </c>
-      <c r="P455" s="16" t="s">
+      <c r="P455" s="14" t="s">
         <v>1407</v>
       </c>
-      <c r="Q455" s="16">
+      <c r="Q455" s="14">
         <v>57.1</v>
       </c>
-      <c r="R455" s="16" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="456" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R455" s="14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="456" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A456" s="14">
         <v>4999</v>
       </c>
@@ -28282,7 +28541,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="457" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A457" s="14">
         <v>44</v>
       </c>
@@ -28326,7 +28585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="458" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A458" s="14">
         <v>549</v>
       </c>
@@ -28370,7 +28629,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="459" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A459" s="14">
         <v>372</v>
       </c>
@@ -28414,7 +28673,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="460" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A460" s="14">
         <v>329</v>
       </c>
@@ -28458,7 +28717,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="461" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A461" s="14">
         <v>350</v>
       </c>
@@ -28502,7 +28761,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="462" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A462" s="14">
         <v>6469</v>
       </c>
@@ -28546,7 +28805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="463" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A463" s="14">
         <v>22</v>
       </c>
@@ -28590,7 +28849,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="464" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A464" s="14">
         <v>656</v>
       </c>
@@ -28619,26 +28878,28 @@
       <c r="J464" s="14" t="s">
         <v>459</v>
       </c>
-      <c r="K464" s="15"/>
-      <c r="L464" s="15"/>
-      <c r="M464" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="N464" s="15"/>
-      <c r="O464" s="16" t="s">
+      <c r="K464" s="14"/>
+      <c r="L464" s="14" t="s">
+        <v>458</v>
+      </c>
+      <c r="M464" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="N464" s="14"/>
+      <c r="O464" s="14" t="s">
         <v>1262</v>
       </c>
-      <c r="P464" s="16" t="s">
+      <c r="P464" s="14" t="s">
         <v>1534</v>
       </c>
-      <c r="Q464" s="16">
+      <c r="Q464" s="14">
         <v>60</v>
       </c>
-      <c r="R464" s="16" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="465" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R464" s="14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="465" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A465" s="14">
         <v>135</v>
       </c>
@@ -28682,7 +28943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="466" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A466" s="14">
         <v>3501</v>
       </c>
@@ -28726,7 +28987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="467" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A467" s="14">
         <v>2775</v>
       </c>
@@ -28770,7 +29031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="468" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A468" s="14">
         <v>3079</v>
       </c>
@@ -28814,7 +29075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="469" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A469" s="14">
         <v>4398</v>
       </c>
@@ -28858,7 +29119,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="470" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A470" s="14">
         <v>3503</v>
       </c>
@@ -28902,7 +29163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="471" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A471" s="14">
         <v>6547</v>
       </c>
@@ -28946,7 +29207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="472" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A472" s="14">
         <v>6472</v>
       </c>
@@ -28990,7 +29251,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="473" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A473" s="14">
         <v>2694</v>
       </c>
@@ -29034,7 +29295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="474" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A474" s="14">
         <v>5300</v>
       </c>
@@ -29078,7 +29339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="475" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A475" s="14">
         <v>205</v>
       </c>
@@ -29122,7 +29383,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="476" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A476" s="14">
         <v>388</v>
       </c>
@@ -29166,7 +29427,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="477" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A477" s="14">
         <v>176</v>
       </c>
@@ -29210,7 +29471,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="478" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A478" s="14">
         <v>3813</v>
       </c>
@@ -29254,7 +29515,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="479" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A479" s="14">
         <v>365</v>
       </c>
@@ -29298,7 +29559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="480" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A480" s="14">
         <v>619</v>
       </c>
@@ -29342,7 +29603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="481" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A481" s="14">
         <v>4886</v>
       </c>
@@ -29386,7 +29647,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="482" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A482" s="14">
         <v>231</v>
       </c>
@@ -29430,7 +29691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="483" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A483" s="14">
         <v>2182</v>
       </c>
@@ -29474,7 +29735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="484" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A484" s="14">
         <v>7386</v>
       </c>
@@ -29518,7 +29779,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="485" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A485" s="14">
         <v>60</v>
       </c>
@@ -29562,7 +29823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="486" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A486" s="14">
         <v>3529</v>
       </c>
@@ -29606,7 +29867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="487" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A487" s="14">
         <v>179</v>
       </c>
@@ -29650,7 +29911,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="488" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A488" s="14">
         <v>233</v>
       </c>
@@ -29675,12 +29936,18 @@
       <c r="H488" s="14"/>
       <c r="I488" s="14"/>
       <c r="J488" s="14"/>
-      <c r="K488" s="15"/>
-      <c r="L488" s="15"/>
+      <c r="K488" s="15">
+        <v>70208022</v>
+      </c>
+      <c r="L488" s="15" t="s">
+        <v>80</v>
+      </c>
       <c r="M488" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="N488" s="15"/>
+        <v>1</v>
+      </c>
+      <c r="N488" s="15" t="s">
+        <v>2222</v>
+      </c>
       <c r="O488" s="16" t="s">
         <v>1302</v>
       </c>
@@ -29694,7 +29961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="489" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A489" s="14">
         <v>2184</v>
       </c>
@@ -29738,7 +30005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="490" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A490" s="14">
         <v>7460</v>
       </c>
@@ -29782,7 +30049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="491" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A491" s="14">
         <v>641</v>
       </c>
@@ -29826,7 +30093,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="492" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A492" s="14">
         <v>6442</v>
       </c>
@@ -29870,7 +30137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="493" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A493" s="14">
         <v>482</v>
       </c>
@@ -29914,7 +30181,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="494" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A494" s="14">
         <v>6466</v>
       </c>
@@ -29958,7 +30225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="495" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A495" s="14">
         <v>660</v>
       </c>
@@ -30002,7 +30269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="496" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A496" s="14">
         <v>6464</v>
       </c>
@@ -30046,7 +30313,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="497" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A497" s="14">
         <v>41</v>
       </c>
@@ -30090,7 +30357,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="498" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A498" s="14">
         <v>12</v>
       </c>
@@ -30134,7 +30401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="499" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A499" s="14">
         <v>6068</v>
       </c>
@@ -30178,7 +30445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="500" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A500" s="14">
         <v>47</v>
       </c>
@@ -30222,7 +30489,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="501" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A501" s="14">
         <v>518</v>
       </c>
@@ -30266,7 +30533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="502" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A502" s="14">
         <v>6653</v>
       </c>
@@ -30310,7 +30577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="503" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A503" s="14">
         <v>5834</v>
       </c>
@@ -30354,7 +30621,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="504" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A504" s="14">
         <v>2672</v>
       </c>
@@ -30398,7 +30665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="505" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A505" s="14">
         <v>6240</v>
       </c>
@@ -30442,7 +30709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="506" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A506" s="14">
         <v>3498</v>
       </c>
@@ -30486,7 +30753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="507" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A507" s="14">
         <v>225</v>
       </c>
@@ -30530,7 +30797,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="508" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A508" s="14">
         <v>5876</v>
       </c>
@@ -30574,7 +30841,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="509" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A509" s="14">
         <v>5448</v>
       </c>
@@ -30618,7 +30885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="510" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A510" s="14">
         <v>5864</v>
       </c>
@@ -30662,7 +30929,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="511" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A511" s="14">
         <v>8246</v>
       </c>
@@ -30706,7 +30973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="512" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A512" s="14">
         <v>342</v>
       </c>
@@ -30750,7 +31017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="513" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A513" s="14">
         <v>402</v>
       </c>
@@ -30794,7 +31061,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="514" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A514" s="14">
         <v>561</v>
       </c>
@@ -30838,7 +31105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="515" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A515" s="14">
         <v>4707</v>
       </c>
@@ -30882,7 +31149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="516" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A516" s="14">
         <v>294</v>
       </c>
@@ -30926,7 +31193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="517" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A517" s="14">
         <v>8392</v>
       </c>
@@ -30970,7 +31237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="518" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A518" s="14">
         <v>441</v>
       </c>
@@ -30995,10 +31262,14 @@
       <c r="H518" s="14"/>
       <c r="I518" s="14"/>
       <c r="J518" s="14"/>
-      <c r="K518" s="15"/>
-      <c r="L518" s="15"/>
+      <c r="K518" s="15">
+        <v>70209004</v>
+      </c>
+      <c r="L518" s="15" t="s">
+        <v>73</v>
+      </c>
       <c r="M518" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N518" s="15"/>
       <c r="O518" s="16" t="s">
@@ -31014,7 +31285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="519" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A519" s="14">
         <v>5212</v>
       </c>
@@ -31058,7 +31329,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="520" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A520" s="14">
         <v>547</v>
       </c>
@@ -31102,7 +31373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="521" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A521" s="14">
         <v>6553</v>
       </c>
@@ -31146,7 +31417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="522" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A522" s="14">
         <v>95</v>
       </c>
@@ -31190,7 +31461,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="523" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A523" s="14">
         <v>7</v>
       </c>
@@ -31234,7 +31505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="524" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A524" s="14">
         <v>513</v>
       </c>
@@ -31278,7 +31549,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="525" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A525" s="14">
         <v>3052</v>
       </c>
@@ -31322,7 +31593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="526" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A526" s="14">
         <v>3134</v>
       </c>
@@ -31347,10 +31618,14 @@
       <c r="H526" s="14"/>
       <c r="I526" s="14"/>
       <c r="J526" s="14"/>
-      <c r="K526" s="15"/>
-      <c r="L526" s="15"/>
+      <c r="K526" s="15">
+        <v>70213050</v>
+      </c>
+      <c r="L526" s="15" t="s">
+        <v>80</v>
+      </c>
       <c r="M526" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N526" s="15"/>
       <c r="O526" s="16" t="s">
@@ -31366,7 +31641,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="527" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A527" s="14">
         <v>116</v>
       </c>
@@ -31410,7 +31685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="528" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A528" s="14">
         <v>394</v>
       </c>
@@ -31454,7 +31729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="529" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A529" s="14">
         <v>4539</v>
       </c>
@@ -31498,7 +31773,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="530" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A530" s="14">
         <v>390</v>
       </c>
@@ -31523,10 +31798,14 @@
       <c r="H530" s="14"/>
       <c r="I530" s="14"/>
       <c r="J530" s="14"/>
-      <c r="K530" s="15"/>
-      <c r="L530" s="15"/>
+      <c r="K530" s="15">
+        <v>70211010</v>
+      </c>
+      <c r="L530" s="15" t="s">
+        <v>80</v>
+      </c>
       <c r="M530" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N530" s="15"/>
       <c r="O530" s="16" t="s">
@@ -31542,7 +31821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="531" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A531" s="14">
         <v>503</v>
       </c>
@@ -31586,7 +31865,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="532" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A532" s="14">
         <v>283</v>
       </c>
@@ -31630,7 +31909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="533" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A533" s="14">
         <v>90</v>
       </c>
@@ -31674,7 +31953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="534" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A534" s="14">
         <v>639</v>
       </c>
@@ -31718,7 +31997,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="535" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A535" s="14">
         <v>220</v>
       </c>
@@ -31762,7 +32041,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="536" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A536" s="14">
         <v>463</v>
       </c>
@@ -31806,7 +32085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="537" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A537" s="14">
         <v>211</v>
       </c>
@@ -31850,7 +32129,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="538" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A538" s="14">
         <v>6443</v>
       </c>
@@ -31894,7 +32173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="539" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A539" s="14">
         <v>224</v>
       </c>
@@ -31938,7 +32217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="540" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A540" s="14">
         <v>476</v>
       </c>
@@ -31964,7 +32243,9 @@
       <c r="I540" s="14"/>
       <c r="J540" s="14"/>
       <c r="K540" s="15"/>
-      <c r="L540" s="15"/>
+      <c r="L540" s="15" t="s">
+        <v>211</v>
+      </c>
       <c r="M540" s="15" t="b">
         <v>0</v>
       </c>
@@ -31982,7 +32263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="541" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A541" s="14">
         <v>253</v>
       </c>
@@ -32026,7 +32307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="542" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A542" s="14">
         <v>4379</v>
       </c>
@@ -32070,7 +32351,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="543" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A543" s="14">
         <v>418</v>
       </c>
@@ -32114,7 +32395,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="544" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A544" s="14">
         <v>4076</v>
       </c>
@@ -32158,7 +32439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="545" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A545" s="14">
         <v>562</v>
       </c>
@@ -32202,7 +32483,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="546" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A546" s="14">
         <v>5958</v>
       </c>
@@ -32246,7 +32527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="547" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A547" s="14">
         <v>509</v>
       </c>
@@ -32290,7 +32571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="548" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A548" s="14">
         <v>477</v>
       </c>
@@ -32334,7 +32615,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="549" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A549" s="14">
         <v>4914</v>
       </c>
@@ -32378,7 +32659,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="550" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A550" s="14">
         <v>100</v>
       </c>
@@ -32422,7 +32703,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="551" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A551" s="14">
         <v>429</v>
       </c>
@@ -32466,7 +32747,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="552" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A552" s="14">
         <v>158</v>
       </c>
@@ -32510,7 +32791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="553" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A553" s="14">
         <v>4896</v>
       </c>
@@ -32554,7 +32835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="554" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A554" s="14">
         <v>519</v>
       </c>
@@ -32598,7 +32879,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="555" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A555" s="14">
         <v>210</v>
       </c>
@@ -32642,7 +32923,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="556" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="556" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A556" s="14">
         <v>186</v>
       </c>
@@ -32686,7 +32967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="557" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A557" s="14">
         <v>193</v>
       </c>
@@ -32730,7 +33011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="558" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="558" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A558" s="14">
         <v>599</v>
       </c>
@@ -32774,7 +33055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="559" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="559" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A559" s="14">
         <v>129</v>
       </c>
@@ -32818,7 +33099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="560" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="560" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A560" s="14">
         <v>5369</v>
       </c>
@@ -32862,7 +33143,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="561" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="561" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A561" s="14">
         <v>4986</v>
       </c>
@@ -32906,7 +33187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="562" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A562" s="14">
         <v>5377</v>
       </c>
@@ -32931,10 +33212,14 @@
       <c r="H562" s="14"/>
       <c r="I562" s="14"/>
       <c r="J562" s="14"/>
-      <c r="K562" s="15"/>
-      <c r="L562" s="15"/>
+      <c r="K562" s="15">
+        <v>70213032</v>
+      </c>
+      <c r="L562" s="15" t="s">
+        <v>80</v>
+      </c>
       <c r="M562" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N562" s="15"/>
       <c r="O562" s="16" t="s">
@@ -32950,7 +33235,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="563" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:18" ht="63.5" x14ac:dyDescent="0.35">
       <c r="A563" s="14">
         <v>3585</v>
       </c>
@@ -32975,12 +33260,18 @@
       <c r="H563" s="14"/>
       <c r="I563" s="14"/>
       <c r="J563" s="14"/>
-      <c r="K563" s="15"/>
-      <c r="L563" s="15"/>
+      <c r="K563" s="15">
+        <v>70209049</v>
+      </c>
+      <c r="L563" s="15" t="s">
+        <v>80</v>
+      </c>
       <c r="M563" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="N563" s="15"/>
+        <v>1</v>
+      </c>
+      <c r="N563" s="25" t="s">
+        <v>2228</v>
+      </c>
       <c r="O563" s="16" t="s">
         <v>1437</v>
       </c>
@@ -32994,7 +33285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="564" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A564" s="14">
         <v>487</v>
       </c>
@@ -33038,7 +33329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="565" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A565" s="14">
         <v>5743</v>
       </c>
@@ -33082,7 +33373,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="566" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="566" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A566" s="14">
         <v>344</v>
       </c>
@@ -33126,7 +33417,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="567" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="567" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A567" s="14">
         <v>147</v>
       </c>
@@ -33170,7 +33461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="568" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="568" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A568" s="14">
         <v>6454</v>
       </c>
@@ -33214,7 +33505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="569" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="569" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A569" s="14">
         <v>6441</v>
       </c>
@@ -33258,7 +33549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="570" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="570" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A570" s="14">
         <v>5959</v>
       </c>
@@ -33302,7 +33593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="571" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="571" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A571" s="14">
         <v>62</v>
       </c>
@@ -33346,7 +33637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="572" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="572" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A572" s="14">
         <v>8201</v>
       </c>
@@ -33390,7 +33681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="573" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="573" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A573" s="14">
         <v>6456</v>
       </c>
@@ -33434,7 +33725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="574" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A574" s="14">
         <v>643</v>
       </c>
@@ -33478,7 +33769,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="575" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="575" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A575" s="14">
         <v>2875</v>
       </c>
@@ -33522,7 +33813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="576" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="576" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A576" s="14">
         <v>602</v>
       </c>
@@ -33566,7 +33857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="577" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="577" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A577" s="14">
         <v>502</v>
       </c>
@@ -33610,7 +33901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="578" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="578" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A578" s="14">
         <v>465</v>
       </c>
@@ -33654,7 +33945,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="579" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="579" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A579" s="14">
         <v>7372</v>
       </c>
@@ -33698,7 +33989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="580" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="580" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A580" s="14">
         <v>8707</v>
       </c>
@@ -33742,7 +34033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="581" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="581" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A581" s="14">
         <v>2881</v>
       </c>
@@ -33786,7 +34077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="582" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="582" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A582" s="14">
         <v>4374</v>
       </c>
@@ -33830,7 +34121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="583" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="583" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A583" s="14">
         <v>7370</v>
       </c>
@@ -33874,7 +34165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="584" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="584" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A584" s="14">
         <v>2261</v>
       </c>
@@ -33918,7 +34209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="585" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="585" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A585" s="14">
         <v>6986</v>
       </c>
@@ -33962,7 +34253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="586" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="586" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A586" s="14">
         <v>89</v>
       </c>
@@ -34006,7 +34297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="587" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="587" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A587" s="14">
         <v>189</v>
       </c>
@@ -34050,7 +34341,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="588" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="588" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A588" s="14">
         <v>7392</v>
       </c>
@@ -34094,7 +34385,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="589" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="589" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A589" s="14">
         <v>5931</v>
       </c>
@@ -34138,7 +34429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="590" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="590" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A590" s="14">
         <v>464</v>
       </c>
@@ -34182,7 +34473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="591" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="591" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A591" s="14">
         <v>7714</v>
       </c>
@@ -34226,7 +34517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="592" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="592" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A592" s="14">
         <v>481</v>
       </c>
@@ -34270,7 +34561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="593" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="593" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A593" s="14">
         <v>469</v>
       </c>
@@ -34314,7 +34605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="594" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="594" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A594" s="14">
         <v>5875</v>
       </c>
@@ -34358,7 +34649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="595" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="595" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A595" s="14">
         <v>6030</v>
       </c>
@@ -34402,7 +34693,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="596" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="596" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A596" s="14">
         <v>483</v>
       </c>
@@ -34446,7 +34737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="597" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="597" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A597" s="14">
         <v>5732</v>
       </c>
@@ -34490,7 +34781,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="598" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="598" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A598" s="14">
         <v>604</v>
       </c>
@@ -34534,7 +34825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="599" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="599" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A599" s="14">
         <v>181</v>
       </c>
@@ -34578,7 +34869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="600" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="600" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A600" s="14">
         <v>52</v>
       </c>
@@ -34622,7 +34913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="601" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="601" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A601" s="14">
         <v>3007</v>
       </c>
@@ -34666,7 +34957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="602" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="602" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A602" s="14">
         <v>7367</v>
       </c>
@@ -34710,7 +35001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="603" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="603" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A603" s="14">
         <v>345</v>
       </c>
@@ -34754,7 +35045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="604" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="604" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A604" s="14">
         <v>6546</v>
       </c>
@@ -34798,7 +35089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="605" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="605" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A605" s="14">
         <v>6371</v>
       </c>
@@ -34842,7 +35133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="606" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="606" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A606" s="14">
         <v>445</v>
       </c>
@@ -34886,7 +35177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="607" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="607" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A607" s="14">
         <v>480</v>
       </c>
@@ -34930,7 +35221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="608" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="608" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A608" s="14">
         <v>3589</v>
       </c>
@@ -34974,7 +35265,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="609" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="609" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A609" s="14">
         <v>119</v>
       </c>
@@ -35018,7 +35309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="610" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="610" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A610" s="14">
         <v>449</v>
       </c>
@@ -35062,7 +35353,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="611" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="611" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A611" s="14">
         <v>5168</v>
       </c>
@@ -35106,7 +35397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="612" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="612" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A612" s="14">
         <v>6167</v>
       </c>
@@ -35150,7 +35441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="613" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="613" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A613" s="14">
         <v>3994</v>
       </c>
@@ -35194,7 +35485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="614" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="614" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A614" s="14">
         <v>6447</v>
       </c>
@@ -35238,7 +35529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="615" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="615" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A615" s="14">
         <v>2682</v>
       </c>
@@ -35282,7 +35573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="616" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="616" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A616" s="14">
         <v>450</v>
       </c>
@@ -35326,7 +35617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="617" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="617" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A617" s="14">
         <v>3531</v>
       </c>
@@ -35370,7 +35661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="618" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="618" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A618" s="14">
         <v>5567</v>
       </c>
@@ -35414,7 +35705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="619" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="619" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A619" s="14">
         <v>3508</v>
       </c>
@@ -35458,7 +35749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="620" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="620" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A620" s="14">
         <v>5871</v>
       </c>
@@ -35502,7 +35793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="621" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="621" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A621" s="14">
         <v>7517</v>
       </c>
@@ -35546,7 +35837,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="622" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="622" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A622" s="14">
         <v>3505</v>
       </c>
@@ -35590,7 +35881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="623" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="623" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A623" s="14">
         <v>6250</v>
       </c>
@@ -35634,7 +35925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="624" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="624" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A624" s="14">
         <v>589</v>
       </c>
@@ -35678,7 +35969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="625" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="625" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A625" s="14">
         <v>3080</v>
       </c>
@@ -35722,7 +36013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="626" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="626" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A626" s="14">
         <v>597</v>
       </c>
@@ -35766,7 +36057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="627" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="627" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A627" s="14">
         <v>422</v>
       </c>
@@ -35810,7 +36101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="628" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="628" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A628" s="14">
         <v>4261</v>
       </c>
@@ -35854,7 +36145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="629" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="629" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A629" s="14">
         <v>4400</v>
       </c>
@@ -35898,7 +36189,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="630" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="630" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A630" s="14">
         <v>2668</v>
       </c>
@@ -35946,7 +36237,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="631" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="631" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A631" s="14">
         <v>278</v>
       </c>
@@ -35990,7 +36281,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="632" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="632" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A632" s="14">
         <v>4404</v>
       </c>
@@ -36034,7 +36325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="633" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="633" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A633" s="14">
         <v>172</v>
       </c>
@@ -36078,7 +36369,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="634" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="634" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A634" s="14">
         <v>199</v>
       </c>
@@ -36122,7 +36413,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="635" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="635" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A635" s="14">
         <v>580</v>
       </c>
@@ -36166,7 +36457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="636" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="636" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A636" s="14">
         <v>3136</v>
       </c>
@@ -36210,7 +36501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="637" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="637" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A637" s="14">
         <v>192</v>
       </c>
@@ -36254,7 +36545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="638" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="638" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A638" s="14">
         <v>6095</v>
       </c>
@@ -36298,7 +36589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="639" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="639" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A639" s="14">
         <v>5863</v>
       </c>
@@ -36342,7 +36633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="640" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="640" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A640" s="14">
         <v>4576</v>
       </c>
@@ -36386,7 +36677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="641" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="641" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A641" s="14">
         <v>2850</v>
       </c>
@@ -36430,7 +36721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="642" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="642" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A642" s="14">
         <v>7377</v>
       </c>
@@ -36474,7 +36765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="643" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="643" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A643" s="14">
         <v>215</v>
       </c>
@@ -36518,7 +36809,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="644" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="644" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A644" s="14">
         <v>2546</v>
       </c>
@@ -36562,7 +36853,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="645" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="645" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A645" s="14">
         <v>157</v>
       </c>
@@ -36606,7 +36897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="646" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="646" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A646" s="14">
         <v>646</v>
       </c>
@@ -36650,7 +36941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="647" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="647" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A647" s="14">
         <v>416</v>
       </c>
@@ -36694,7 +36985,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="648" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="648" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A648" s="14">
         <v>38</v>
       </c>
@@ -36738,7 +37029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="649" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="649" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A649" s="14">
         <v>8877</v>
       </c>
@@ -36782,7 +37073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="650" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="650" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A650" s="14">
         <v>187</v>
       </c>
@@ -36826,7 +37117,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="651" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="651" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A651" s="14">
         <v>7838</v>
       </c>
@@ -36870,7 +37161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="652" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="652" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A652" s="14">
         <v>500</v>
       </c>
@@ -36914,7 +37205,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="653" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="653" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A653" s="14">
         <v>6455</v>
       </c>
@@ -36958,7 +37249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="654" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="654" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A654" s="14">
         <v>7837</v>
       </c>
@@ -37002,7 +37293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="655" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="655" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A655" s="14">
         <v>582</v>
       </c>
@@ -37048,7 +37339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="656" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="656" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A656" s="14">
         <v>520</v>
       </c>
@@ -37092,7 +37383,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="657" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="657" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A657" s="14">
         <v>61</v>
       </c>
@@ -37136,7 +37427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="658" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="658" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A658" s="14">
         <v>7459</v>
       </c>
@@ -37180,7 +37471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="659" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="659" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A659" s="14">
         <v>7839</v>
       </c>
@@ -37224,7 +37515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="660" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="660" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A660" s="14">
         <v>8863</v>
       </c>
@@ -37268,7 +37559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="661" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="661" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A661" s="14">
         <v>4824</v>
       </c>
@@ -37312,7 +37603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="662" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="662" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A662" s="14">
         <v>7381</v>
       </c>
@@ -37356,7 +37647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="663" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="663" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A663" s="14">
         <v>8872</v>
       </c>
@@ -37381,10 +37672,14 @@
       <c r="H663" s="14"/>
       <c r="I663" s="14"/>
       <c r="J663" s="14"/>
-      <c r="K663" s="15"/>
-      <c r="L663" s="15"/>
+      <c r="K663" s="15">
+        <v>70211010</v>
+      </c>
+      <c r="L663" s="15" t="s">
+        <v>80</v>
+      </c>
       <c r="M663" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N663" s="15"/>
       <c r="O663" s="16" t="s">
@@ -37400,7 +37695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="664" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="664" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A664" s="14">
         <v>6655</v>
       </c>
@@ -37444,7 +37739,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="665" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="665" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A665" s="14">
         <v>3520</v>
       </c>
@@ -37488,7 +37783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="666" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="666" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A666" s="14">
         <v>3527</v>
       </c>
@@ -37532,7 +37827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="667" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="667" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A667" s="14">
         <v>175</v>
       </c>
@@ -37576,7 +37871,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="668" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="668" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A668" s="14">
         <v>151</v>
       </c>
@@ -37620,7 +37915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="669" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="669" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A669" s="14">
         <v>446</v>
       </c>
@@ -37645,10 +37940,14 @@
       <c r="H669" s="14"/>
       <c r="I669" s="14"/>
       <c r="J669" s="14"/>
-      <c r="K669" s="15"/>
-      <c r="L669" s="15"/>
+      <c r="K669" s="15">
+        <v>70211242</v>
+      </c>
+      <c r="L669" s="15" t="s">
+        <v>80</v>
+      </c>
       <c r="M669" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N669" s="15"/>
       <c r="O669" s="16" t="s">
@@ -37664,7 +37963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="670" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="670" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A670" s="14">
         <v>3584</v>
       </c>
@@ -37708,7 +38007,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="671" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="671" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A671" s="14">
         <v>6444</v>
       </c>
@@ -37752,7 +38051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="672" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="672" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A672" s="14">
         <v>2765</v>
       </c>
@@ -37796,7 +38095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="673" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="673" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A673" s="14">
         <v>8611</v>
       </c>
@@ -37840,7 +38139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="674" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="674" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A674" s="14">
         <v>8460</v>
       </c>
@@ -37884,7 +38183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="675" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="675" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A675" s="14">
         <v>3530</v>
       </c>
@@ -37928,7 +38227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="676" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="676" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A676" s="14">
         <v>8779</v>
       </c>
@@ -37972,7 +38271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="677" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="677" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A677" s="14">
         <v>272</v>
       </c>
@@ -38016,7 +38315,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="678" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="678" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A678" s="14">
         <v>8229</v>
       </c>
@@ -38060,7 +38359,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="679" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="679" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A679" s="14">
         <v>5665</v>
       </c>
@@ -38104,7 +38403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="680" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="680" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A680" s="14">
         <v>3905</v>
       </c>
@@ -38148,7 +38447,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="681" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="681" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A681" s="14">
         <v>2936</v>
       </c>
@@ -38192,7 +38491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="682" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="682" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A682" s="14">
         <v>227</v>
       </c>
@@ -38236,7 +38535,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="683" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="683" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A683" s="14">
         <v>8869</v>
       </c>
@@ -38280,7 +38579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="684" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="684" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A684" s="14">
         <v>2392</v>
       </c>
@@ -38324,7 +38623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="685" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="685" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A685" s="14">
         <v>363</v>
       </c>
@@ -38368,7 +38667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="686" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="686" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A686" s="14">
         <v>309</v>
       </c>
@@ -38412,7 +38711,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="687" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="687" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A687" s="14">
         <v>2615</v>
       </c>
@@ -38456,7 +38755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="688" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="688" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A688" s="14">
         <v>266</v>
       </c>
@@ -38500,7 +38799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="689" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="689" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A689" s="14">
         <v>5164</v>
       </c>
@@ -38544,7 +38843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="690" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="690" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A690" s="14">
         <v>81</v>
       </c>
@@ -38588,7 +38887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="691" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="691" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A691" s="14">
         <v>5337</v>
       </c>
@@ -38632,7 +38931,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="692" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="692" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A692" s="14">
         <v>3581</v>
       </c>
@@ -38676,7 +38975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="693" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="693" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A693" s="14">
         <v>6994</v>
       </c>
@@ -38720,7 +39019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="694" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="694" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A694" s="14">
         <v>4920</v>
       </c>
@@ -38764,7 +39063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="695" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="695" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A695" s="14">
         <v>29</v>
       </c>
@@ -38808,7 +39107,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="696" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="696" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A696" s="14">
         <v>627</v>
       </c>
@@ -38852,7 +39151,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="697" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="697" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A697" s="14">
         <v>6106</v>
       </c>
@@ -38896,7 +39195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="698" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="698" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A698" s="14">
         <v>4403</v>
       </c>
@@ -38921,10 +39220,14 @@
       <c r="H698" s="14"/>
       <c r="I698" s="14"/>
       <c r="J698" s="14"/>
-      <c r="K698" s="15"/>
-      <c r="L698" s="15"/>
+      <c r="K698" s="24">
+        <v>70209050</v>
+      </c>
+      <c r="L698" s="15" t="s">
+        <v>80</v>
+      </c>
       <c r="M698" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N698" s="15"/>
       <c r="O698" s="16" t="s">
@@ -38940,7 +39243,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="699" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="699" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A699" s="14">
         <v>4668</v>
       </c>
@@ -38984,7 +39287,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="700" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="700" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A700" s="14">
         <v>2076</v>
       </c>
@@ -39028,7 +39331,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="701" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="701" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A701" s="14">
         <v>5600</v>
       </c>
@@ -39072,7 +39375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="702" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="702" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A702" s="14">
         <v>146</v>
       </c>
@@ -39116,7 +39419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="703" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="703" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A703" s="14">
         <v>8876</v>
       </c>
@@ -39160,7 +39463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="704" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="704" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A704" s="14">
         <v>4669</v>
       </c>
@@ -39204,7 +39507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="705" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="705" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A705" s="14">
         <v>2785</v>
       </c>
@@ -39248,7 +39551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="706" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="706" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A706" s="14">
         <v>3500</v>
       </c>
@@ -39292,7 +39595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="707" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="707" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A707" s="14">
         <v>4884</v>
       </c>
@@ -39336,7 +39639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="708" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="708" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A708" s="14">
         <v>567</v>
       </c>
@@ -39380,7 +39683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="709" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="709" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A709" s="14">
         <v>4269</v>
       </c>
@@ -39424,7 +39727,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="710" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="710" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A710" s="14">
         <v>234</v>
       </c>
@@ -39468,7 +39771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="711" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="711" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A711" s="14">
         <v>574</v>
       </c>
@@ -39512,7 +39815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="712" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="712" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A712" s="14">
         <v>3526</v>
       </c>
@@ -39556,7 +39859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="713" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="713" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A713" s="14">
         <v>2710</v>
       </c>
@@ -39600,7 +39903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="714" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="714" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A714" s="14">
         <v>455</v>
       </c>
@@ -39644,7 +39947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="715" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="715" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A715" s="14">
         <v>5914</v>
       </c>
@@ -39688,7 +39991,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="716" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="716" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A716" s="14">
         <v>6069</v>
       </c>
@@ -39732,7 +40035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="717" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="717" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A717" s="14">
         <v>6465</v>
       </c>
@@ -39776,7 +40079,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="718" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="718" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A718" s="14">
         <v>308</v>
       </c>
@@ -39820,7 +40123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="719" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="719" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A719" s="14">
         <v>252</v>
       </c>
@@ -39864,7 +40167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="720" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="720" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A720" s="14">
         <v>5744</v>
       </c>
@@ -39908,7 +40211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="721" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="721" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A721" s="14">
         <v>141</v>
       </c>
@@ -39952,7 +40255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="722" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="722" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A722" s="14">
         <v>5790</v>
       </c>
@@ -39996,7 +40299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="723" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="723" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A723" s="14">
         <v>5835</v>
       </c>
@@ -40040,7 +40343,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="724" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="724" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A724" s="14">
         <v>4369</v>
       </c>
@@ -40084,7 +40387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="725" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="725" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A725" s="14">
         <v>4405</v>
       </c>
@@ -40128,7 +40431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="726" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="726" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A726" s="14">
         <v>6302</v>
       </c>
@@ -40172,7 +40475,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="727" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="727" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A727" s="14">
         <v>2702</v>
       </c>
@@ -40216,7 +40519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="728" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="728" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A728" s="14">
         <v>96</v>
       </c>
@@ -40260,7 +40563,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="729" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="729" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A729" s="14">
         <v>239</v>
       </c>
@@ -40304,7 +40607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="730" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="730" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A730" s="14">
         <v>4888</v>
       </c>
@@ -40348,7 +40651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="731" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="731" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A731" s="14">
         <v>636</v>
       </c>
@@ -40392,7 +40695,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="732" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="732" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A732" s="14">
         <v>6559</v>
       </c>
@@ -40436,7 +40739,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="733" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="733" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A733" s="14">
         <v>2685</v>
       </c>
@@ -40480,7 +40783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="734" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="734" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A734" s="14">
         <v>5907</v>
       </c>
@@ -40524,7 +40827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="735" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="735" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A735" s="14">
         <v>6652</v>
       </c>
@@ -40568,7 +40871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="736" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="736" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A736" s="14">
         <v>6157</v>
       </c>
@@ -40612,7 +40915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="737" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="737" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A737" s="14">
         <v>197</v>
       </c>
@@ -40656,7 +40959,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="738" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="738" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A738" s="14">
         <v>289</v>
       </c>
@@ -40700,7 +41003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="739" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="739" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A739" s="14">
         <v>3022</v>
       </c>
@@ -40744,7 +41047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="740" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="740" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A740" s="14">
         <v>2180</v>
       </c>
@@ -40788,7 +41091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="741" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="741" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A741" s="14">
         <v>2671</v>
       </c>
@@ -40832,7 +41135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="742" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="742" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A742" s="14">
         <v>2311</v>
       </c>
@@ -40861,26 +41164,28 @@
       <c r="J742" s="14" t="s">
         <v>459</v>
       </c>
-      <c r="K742" s="15"/>
-      <c r="L742" s="15"/>
-      <c r="M742" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="N742" s="15"/>
-      <c r="O742" s="16" t="s">
+      <c r="K742" s="14"/>
+      <c r="L742" s="14" t="s">
+        <v>458</v>
+      </c>
+      <c r="M742" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="N742" s="14"/>
+      <c r="O742" s="14" t="s">
         <v>2161</v>
       </c>
-      <c r="P742" s="16" t="s">
+      <c r="P742" s="14" t="s">
         <v>1418</v>
       </c>
-      <c r="Q742" s="16">
+      <c r="Q742" s="14">
         <v>64</v>
       </c>
-      <c r="R742" s="16" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="743" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R742" s="14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="743" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A743" s="14">
         <v>5741</v>
       </c>
@@ -40924,7 +41229,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="744" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="744" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A744" s="14">
         <v>406</v>
       </c>
@@ -40968,7 +41273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="745" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="745" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A745" s="14">
         <v>1310</v>
       </c>
@@ -40997,26 +41302,28 @@
       <c r="J745" s="14" t="s">
         <v>459</v>
       </c>
-      <c r="K745" s="15"/>
-      <c r="L745" s="15"/>
-      <c r="M745" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="N745" s="15"/>
-      <c r="O745" s="16" t="s">
+      <c r="K745" s="14"/>
+      <c r="L745" s="14" t="s">
+        <v>458</v>
+      </c>
+      <c r="M745" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="N745" s="14"/>
+      <c r="O745" s="14" t="s">
         <v>2166</v>
       </c>
-      <c r="P745" s="16" t="s">
+      <c r="P745" s="14" t="s">
         <v>2167</v>
       </c>
-      <c r="Q745" s="16">
+      <c r="Q745" s="14">
         <v>50</v>
       </c>
-      <c r="R745" s="16" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="746" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R745" s="14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="746" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A746" s="14">
         <v>142</v>
       </c>
@@ -41060,7 +41367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="747" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="747" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A747" s="14">
         <v>5441</v>
       </c>
@@ -41104,7 +41411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="748" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="748" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A748" s="14">
         <v>2887</v>
       </c>
@@ -41148,7 +41455,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="749" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="749" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A749" s="14">
         <v>2667</v>
       </c>
@@ -41192,7 +41499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="750" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="750" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A750" s="14">
         <v>6746</v>
       </c>
@@ -41236,7 +41543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="751" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="751" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A751" s="14">
         <v>304</v>
       </c>
@@ -41261,10 +41568,14 @@
       <c r="H751" s="14"/>
       <c r="I751" s="14"/>
       <c r="J751" s="14"/>
-      <c r="K751" s="15"/>
-      <c r="L751" s="15"/>
+      <c r="K751" s="14">
+        <v>70216018</v>
+      </c>
+      <c r="L751" s="15" t="s">
+        <v>80</v>
+      </c>
       <c r="M751" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N751" s="15"/>
       <c r="O751" s="16" t="s">
@@ -41280,7 +41591,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="752" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="752" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A752" s="14">
         <v>5852</v>
       </c>
@@ -41324,7 +41635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="753" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="753" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A753" s="14">
         <v>5405</v>
       </c>
@@ -41368,7 +41679,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="754" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="754" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A754" s="14">
         <v>3578</v>
       </c>
@@ -41412,7 +41723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="755" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="755" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A755" s="14">
         <v>2179</v>
       </c>
@@ -41456,7 +41767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="756" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="756" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A756" s="14">
         <v>2665</v>
       </c>
@@ -41500,7 +41811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="757" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="757" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A757" s="14">
         <v>3591</v>
       </c>
@@ -41544,7 +41855,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="758" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="758" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A758" s="14">
         <v>6743</v>
       </c>
@@ -41588,7 +41899,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="759" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="759" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A759" s="14">
         <v>492</v>
       </c>
@@ -41632,7 +41943,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="760" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="760" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A760" s="14">
         <v>5717</v>
       </c>
@@ -41676,7 +41987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="761" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="761" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A761" s="14">
         <v>2181</v>
       </c>
@@ -41720,7 +42031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="762" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="762" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A762" s="14">
         <v>5671</v>
       </c>
@@ -41764,7 +42075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="763" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="763" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A763" s="14">
         <v>6453</v>
       </c>
@@ -41808,7 +42119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="764" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="764" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A764" s="14">
         <v>3190</v>
       </c>
@@ -41852,7 +42163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="765" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="765" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A765" s="14">
         <v>2673</v>
       </c>
@@ -41896,7 +42207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="766" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="766" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A766" s="14">
         <v>6958</v>
       </c>
@@ -41940,7 +42251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="767" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="767" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A767" s="14">
         <v>6369</v>
       </c>
@@ -41984,7 +42295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="768" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="768" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A768" s="14">
         <v>3570</v>
       </c>
@@ -42028,7 +42339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="769" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="769" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A769" s="14">
         <v>8244</v>
       </c>
@@ -42072,7 +42383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="770" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="770" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A770" s="14">
         <v>6580</v>
       </c>
@@ -42116,7 +42427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="771" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="771" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A771" s="14">
         <v>3961</v>
       </c>
@@ -42160,7 +42471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="772" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="772" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A772" s="14">
         <v>6461</v>
       </c>
@@ -42204,7 +42515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="773" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="773" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A773" s="14">
         <v>6033</v>
       </c>
@@ -42249,14 +42560,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R773" xr:uid="{00000000-0009-0000-0000-000001000000}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="Caldo de pollo (Sopita Concentrada)"/>
-        <filter val="Caldo de pollo en polvo"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:S773" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <conditionalFormatting sqref="B2:B773">
     <cfRule type="expression" dxfId="4" priority="5">
       <formula>$H2&lt;&gt;""</formula>

--- a/data/raw/crosswalk_variedad_INCAP.xlsx
+++ b/data/raw/crosswalk_variedad_INCAP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wfp-my.sharepoint.com/personal/maicel_monzon_wfp_org/Documents/Documents/Fases_Consultoria/01_analisis_ENGIH2018/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="368" documentId="14_{F8BE0E5F-76BA-446B-8942-BC5680A971A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA8EAFD1-C70C-4AC1-B63F-C5D263252057}"/>
+  <xr:revisionPtr revIDLastSave="454" documentId="14_{F8BE0E5F-76BA-446B-8942-BC5680A971A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF0E0AF7-0E0D-4AC1-AD13-F9A3A744D940}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Datos" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Datos!$A$1:$S$773</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Datos!$A$1:$R$773</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5006" uniqueCount="2232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5019" uniqueCount="2232">
   <si>
     <t>Cómo usar este archivo</t>
   </si>
@@ -6892,7 +6892,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -6944,6 +6944,9 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7617,9 +7620,9 @@
   <dimension ref="A1:R773"/>
   <sheetFormatPr defaultRowHeight="14.5" outlineLevelCol="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.1796875" customWidth="1"/>
+    <col min="1" max="1" width="14.1796875" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="32.54296875" customWidth="1"/>
-    <col min="3" max="3" width="14.08984375" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="14.08984375" customWidth="1"/>
     <col min="4" max="4" width="21.81640625" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="14.6328125" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="24.54296875" hidden="1" customWidth="1"/>
@@ -7627,7 +7630,7 @@
     <col min="8" max="8" width="18" hidden="1" customWidth="1"/>
     <col min="9" max="9" width="9.453125" hidden="1" customWidth="1"/>
     <col min="10" max="10" width="17.81640625" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="16.7265625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.7265625" customWidth="1"/>
     <col min="12" max="12" width="20.36328125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12.54296875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="20" customWidth="1"/>
@@ -7644,7 +7647,7 @@
       <c r="B1" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="26" t="s">
         <v>28</v>
       </c>
       <c r="D1" s="11" t="s">
@@ -12548,10 +12551,14 @@
       <c r="H96" s="14"/>
       <c r="I96" s="14"/>
       <c r="J96" s="14"/>
-      <c r="K96" s="15"/>
-      <c r="L96" s="15"/>
+      <c r="K96" s="15">
+        <v>70201032</v>
+      </c>
+      <c r="L96" s="15" t="s">
+        <v>73</v>
+      </c>
       <c r="M96" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N96" s="15"/>
       <c r="O96" s="16" t="s">
@@ -15350,10 +15357,14 @@
       <c r="H159" s="14"/>
       <c r="I159" s="14"/>
       <c r="J159" s="14"/>
-      <c r="K159" s="15"/>
-      <c r="L159" s="15"/>
+      <c r="K159" s="15">
+        <v>70201103</v>
+      </c>
+      <c r="L159" s="15" t="s">
+        <v>73</v>
+      </c>
       <c r="M159" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N159" s="15"/>
       <c r="O159" s="16" t="s">
@@ -15840,10 +15851,14 @@
       <c r="H170" s="14"/>
       <c r="I170" s="14"/>
       <c r="J170" s="14"/>
-      <c r="K170" s="15"/>
-      <c r="L170" s="15"/>
+      <c r="K170" s="15">
+        <v>70201083</v>
+      </c>
+      <c r="L170" s="15" t="s">
+        <v>73</v>
+      </c>
       <c r="M170" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N170" s="15"/>
       <c r="O170" s="16" t="s">
@@ -16724,10 +16739,14 @@
       <c r="H190" s="14"/>
       <c r="I190" s="14"/>
       <c r="J190" s="14"/>
-      <c r="K190" s="15"/>
-      <c r="L190" s="15"/>
+      <c r="K190" s="15">
+        <v>70201009</v>
+      </c>
+      <c r="L190" s="15" t="s">
+        <v>73</v>
+      </c>
       <c r="M190" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N190" s="15"/>
       <c r="O190" s="16" t="s">
@@ -18408,10 +18427,14 @@
       <c r="H228" s="14"/>
       <c r="I228" s="14"/>
       <c r="J228" s="14"/>
-      <c r="K228" s="15"/>
-      <c r="L228" s="15"/>
+      <c r="K228" s="15">
+        <v>70201008</v>
+      </c>
+      <c r="L228" s="15" t="s">
+        <v>80</v>
+      </c>
       <c r="M228" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N228" s="15"/>
       <c r="O228" s="16" t="s">
@@ -20840,10 +20863,14 @@
       <c r="H283" s="14"/>
       <c r="I283" s="14"/>
       <c r="J283" s="14"/>
-      <c r="K283" s="15"/>
-      <c r="L283" s="15"/>
+      <c r="K283" s="15">
+        <v>70201086</v>
+      </c>
+      <c r="L283" s="15" t="s">
+        <v>73</v>
+      </c>
       <c r="M283" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N283" s="15"/>
       <c r="O283" s="16" t="s">
@@ -21192,10 +21219,14 @@
       <c r="H291" s="14"/>
       <c r="I291" s="14"/>
       <c r="J291" s="14"/>
-      <c r="K291" s="15"/>
-      <c r="L291" s="15"/>
+      <c r="K291" s="15">
+        <v>70201026</v>
+      </c>
+      <c r="L291" s="15" t="s">
+        <v>73</v>
+      </c>
       <c r="M291" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N291" s="15"/>
       <c r="O291" s="16" t="s">
@@ -27140,10 +27171,14 @@
       <c r="H425" s="14"/>
       <c r="I425" s="14"/>
       <c r="J425" s="14"/>
-      <c r="K425" s="15"/>
-      <c r="L425" s="15"/>
+      <c r="K425" s="15">
+        <v>70201105</v>
+      </c>
+      <c r="L425" s="15" t="s">
+        <v>73</v>
+      </c>
       <c r="M425" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N425" s="15"/>
       <c r="O425" s="16" t="s">
@@ -30866,10 +30901,14 @@
       <c r="H509" s="14"/>
       <c r="I509" s="14"/>
       <c r="J509" s="14"/>
-      <c r="K509" s="15"/>
-      <c r="L509" s="15"/>
+      <c r="K509" s="15">
+        <v>70201052</v>
+      </c>
+      <c r="L509" s="15" t="s">
+        <v>73</v>
+      </c>
       <c r="M509" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N509" s="15"/>
       <c r="O509" s="16" t="s">
@@ -31310,10 +31349,14 @@
       <c r="H519" s="14"/>
       <c r="I519" s="14"/>
       <c r="J519" s="14"/>
-      <c r="K519" s="15"/>
-      <c r="L519" s="15"/>
+      <c r="K519" s="15">
+        <v>70201119</v>
+      </c>
+      <c r="L519" s="15" t="s">
+        <v>73</v>
+      </c>
       <c r="M519" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N519" s="15"/>
       <c r="O519" s="16" t="s">
@@ -33706,10 +33749,14 @@
       <c r="H573" s="14"/>
       <c r="I573" s="14"/>
       <c r="J573" s="14"/>
-      <c r="K573" s="15"/>
-      <c r="L573" s="15"/>
+      <c r="K573" s="15">
+        <v>70201010</v>
+      </c>
+      <c r="L573" s="15" t="s">
+        <v>73</v>
+      </c>
       <c r="M573" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N573" s="15"/>
       <c r="O573" s="16" t="s">
@@ -37230,10 +37277,14 @@
       <c r="H653" s="14"/>
       <c r="I653" s="14"/>
       <c r="J653" s="14"/>
-      <c r="K653" s="15"/>
-      <c r="L653" s="15"/>
+      <c r="K653" s="15">
+        <v>70201015</v>
+      </c>
+      <c r="L653" s="15" t="s">
+        <v>80</v>
+      </c>
       <c r="M653" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N653" s="15"/>
       <c r="O653" s="16" t="s">
@@ -42100,10 +42151,14 @@
       <c r="H763" s="14"/>
       <c r="I763" s="14"/>
       <c r="J763" s="14"/>
-      <c r="K763" s="15"/>
-      <c r="L763" s="15"/>
+      <c r="K763" s="15">
+        <v>70201103</v>
+      </c>
+      <c r="L763" s="15" t="s">
+        <v>80</v>
+      </c>
       <c r="M763" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N763" s="15"/>
       <c r="O763" s="16" t="s">
@@ -42560,7 +42615,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S773" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
+  <autoFilter ref="A1:R773" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <conditionalFormatting sqref="B2:B773">
     <cfRule type="expression" dxfId="4" priority="5">
       <formula>$H2&lt;&gt;""</formula>

--- a/data/raw/crosswalk_variedad_INCAP.xlsx
+++ b/data/raw/crosswalk_variedad_INCAP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wfp-my.sharepoint.com/personal/maicel_monzon_wfp_org/Documents/Documents/Fases_Consultoria/01_analisis_ENGIH2018/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="454" documentId="14_{F8BE0E5F-76BA-446B-8942-BC5680A971A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF0E0AF7-0E0D-4AC1-AD13-F9A3A744D940}"/>
+  <xr:revisionPtr revIDLastSave="516" documentId="14_{F8BE0E5F-76BA-446B-8942-BC5680A971A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B86A18F-06E1-4855-8336-057BAE4CE478}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5019" uniqueCount="2232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5031" uniqueCount="2232">
   <si>
     <t>Cómo usar este archivo</t>
   </si>
@@ -7623,12 +7623,12 @@
     <col min="1" max="1" width="14.1796875" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="32.54296875" customWidth="1"/>
     <col min="3" max="3" width="14.08984375" customWidth="1"/>
-    <col min="4" max="4" width="21.81640625" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.81640625" customWidth="1"/>
     <col min="5" max="5" width="14.6328125" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="24.54296875" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="23.453125" hidden="1" customWidth="1"/>
     <col min="8" max="8" width="18" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="9.453125" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="9.453125" customWidth="1"/>
     <col min="10" max="10" width="17.81640625" hidden="1" customWidth="1"/>
     <col min="11" max="11" width="16.7265625" customWidth="1"/>
     <col min="12" max="12" width="20.36328125" bestFit="1" customWidth="1"/>
@@ -7650,7 +7650,7 @@
       <c r="C1" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="26" t="s">
         <v>30</v>
       </c>
       <c r="E1" s="11" t="s">
@@ -7833,10 +7833,14 @@
       <c r="J4" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="K4" s="15"/>
-      <c r="L4" s="15"/>
+      <c r="K4" s="14">
+        <v>70203019</v>
+      </c>
+      <c r="L4" s="15" t="s">
+        <v>80</v>
+      </c>
       <c r="M4" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N4" s="15"/>
       <c r="O4" s="16" t="s">
@@ -7939,7 +7943,7 @@
         <v>94</v>
       </c>
       <c r="K6" s="15">
-        <f t="shared" ref="K6:K8" si="0">I6</f>
+        <f>I6</f>
         <v>70202002</v>
       </c>
       <c r="L6" s="15" t="s">
@@ -7994,7 +7998,7 @@
         <v>99</v>
       </c>
       <c r="K7" s="15">
-        <f t="shared" si="0"/>
+        <f>I7</f>
         <v>70211006</v>
       </c>
       <c r="L7" s="15" t="s">
@@ -8051,7 +8055,7 @@
         <v>99</v>
       </c>
       <c r="K8" s="15">
-        <f t="shared" si="0"/>
+        <f>I8</f>
         <v>70216009</v>
       </c>
       <c r="L8" s="15" t="s">
@@ -8105,10 +8109,14 @@
       <c r="J9" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="K9" s="15"/>
-      <c r="L9" s="15"/>
+      <c r="K9" s="14">
+        <v>70214021</v>
+      </c>
+      <c r="L9" s="15" t="s">
+        <v>80</v>
+      </c>
       <c r="M9" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" s="15"/>
       <c r="O9" s="16" t="s">
@@ -8155,10 +8163,14 @@
       <c r="J10" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="K10" s="15"/>
-      <c r="L10" s="15"/>
+      <c r="K10" s="15">
+        <v>70217063</v>
+      </c>
+      <c r="L10" s="15" t="s">
+        <v>80</v>
+      </c>
       <c r="M10" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" s="15"/>
       <c r="O10" s="16" t="s">
@@ -8259,10 +8271,14 @@
       <c r="J12" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="K12" s="15"/>
-      <c r="L12" s="15"/>
+      <c r="K12" s="14">
+        <v>70222047</v>
+      </c>
+      <c r="L12" s="15" t="s">
+        <v>80</v>
+      </c>
       <c r="M12" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" s="15"/>
       <c r="O12" s="16" t="s">
@@ -8364,7 +8380,7 @@
         <v>137</v>
       </c>
       <c r="K14" s="15">
-        <f t="shared" ref="K14:K15" si="1">I14</f>
+        <f>I14</f>
         <v>70217039</v>
       </c>
       <c r="L14" s="15" t="s">
@@ -8421,7 +8437,7 @@
         <v>143</v>
       </c>
       <c r="K15" s="15">
-        <f t="shared" si="1"/>
+        <f>I15</f>
         <v>70215003</v>
       </c>
       <c r="L15" s="15" t="s">
@@ -8526,7 +8542,7 @@
         <v>153</v>
       </c>
       <c r="K17" s="15">
-        <f t="shared" ref="K17:K18" si="2">I17</f>
+        <f>I17</f>
         <v>70213004</v>
       </c>
       <c r="L17" s="15" t="s">
@@ -8581,7 +8597,7 @@
         <v>99</v>
       </c>
       <c r="K18" s="15">
-        <f t="shared" si="2"/>
+        <f>I18</f>
         <v>70212131</v>
       </c>
       <c r="L18" s="15" t="s">
@@ -8635,10 +8651,14 @@
       <c r="J19" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="K19" s="15"/>
-      <c r="L19" s="15"/>
+      <c r="K19" s="14">
+        <v>70214112</v>
+      </c>
+      <c r="L19" s="15" t="s">
+        <v>80</v>
+      </c>
       <c r="M19" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N19" s="15"/>
       <c r="O19" s="16" t="s">
@@ -8686,7 +8706,7 @@
         <v>99</v>
       </c>
       <c r="K20" s="15">
-        <f t="shared" ref="K20" si="3">I20</f>
+        <f>I20</f>
         <v>70212011</v>
       </c>
       <c r="L20" s="15" t="s">
@@ -8740,10 +8760,14 @@
       <c r="J21" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="K21" s="15"/>
-      <c r="L21" s="15"/>
+      <c r="K21" s="14">
+        <v>70222022</v>
+      </c>
+      <c r="L21" s="15" t="s">
+        <v>80</v>
+      </c>
       <c r="M21" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N21" s="15"/>
       <c r="O21" s="16" t="s">
@@ -8790,10 +8814,14 @@
       <c r="J22" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="K22" s="15"/>
-      <c r="L22" s="15"/>
+      <c r="K22" s="15">
+        <v>70207037</v>
+      </c>
+      <c r="L22" s="15" t="s">
+        <v>80</v>
+      </c>
       <c r="M22" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N22" s="15"/>
       <c r="O22" s="16" t="s">
@@ -8841,7 +8869,7 @@
         <v>99</v>
       </c>
       <c r="K23" s="15">
-        <f t="shared" ref="K23:K24" si="4">I23</f>
+        <f>I23</f>
         <v>70211167</v>
       </c>
       <c r="L23" s="15" t="s">
@@ -8896,7 +8924,7 @@
         <v>186</v>
       </c>
       <c r="K24" s="15">
-        <f t="shared" si="4"/>
+        <f>I24</f>
         <v>70201015</v>
       </c>
       <c r="L24" s="15" t="s">
@@ -8950,10 +8978,14 @@
       <c r="J25" s="14" t="s">
         <v>192</v>
       </c>
-      <c r="K25" s="15"/>
-      <c r="L25" s="15"/>
+      <c r="K25" s="15">
+        <v>70214009</v>
+      </c>
+      <c r="L25" s="15" t="s">
+        <v>80</v>
+      </c>
       <c r="M25" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N25" s="15"/>
       <c r="O25" s="16" t="s">
@@ -9000,10 +9032,14 @@
       <c r="J26" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="K26" s="15"/>
-      <c r="L26" s="15"/>
+      <c r="K26" s="24">
+        <v>70211127</v>
+      </c>
+      <c r="L26" s="15" t="s">
+        <v>80</v>
+      </c>
       <c r="M26" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N26" s="15"/>
       <c r="O26" s="16" t="s">
@@ -9051,7 +9087,7 @@
         <v>202</v>
       </c>
       <c r="K27" s="15">
-        <f t="shared" ref="K27:K28" si="5">I27</f>
+        <f>I27</f>
         <v>70209006</v>
       </c>
       <c r="L27" s="15" t="s">
@@ -9106,7 +9142,7 @@
         <v>207</v>
       </c>
       <c r="K28" s="15">
-        <f t="shared" si="5"/>
+        <f>I28</f>
         <v>70201014</v>
       </c>
       <c r="L28" s="15" t="s">
@@ -9215,7 +9251,7 @@
         <v>216</v>
       </c>
       <c r="K30" s="15">
-        <f t="shared" ref="K30:K32" si="6">I30</f>
+        <f>I30</f>
         <v>70212107</v>
       </c>
       <c r="L30" s="15" t="s">
@@ -9270,7 +9306,7 @@
         <v>221</v>
       </c>
       <c r="K31" s="15">
-        <f t="shared" si="6"/>
+        <f>I31</f>
         <v>70211005</v>
       </c>
       <c r="L31" s="15" t="s">
@@ -9325,7 +9361,7 @@
         <v>226</v>
       </c>
       <c r="K32" s="15">
-        <f t="shared" si="6"/>
+        <f>I32</f>
         <v>70211157</v>
       </c>
       <c r="L32" s="15" t="s">
@@ -9485,10 +9521,14 @@
       <c r="J35" s="14" t="s">
         <v>240</v>
       </c>
-      <c r="K35" s="15"/>
-      <c r="L35" s="15"/>
+      <c r="K35" s="24">
+        <v>70214004</v>
+      </c>
+      <c r="L35" s="15" t="s">
+        <v>80</v>
+      </c>
       <c r="M35" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N35" s="15"/>
       <c r="O35" s="16" t="s">
@@ -9592,7 +9632,7 @@
         <v>250</v>
       </c>
       <c r="K37" s="15">
-        <f t="shared" ref="K37" si="7">I37</f>
+        <f>I37</f>
         <v>70201052</v>
       </c>
       <c r="L37" s="15" t="s">
@@ -9758,7 +9798,7 @@
         <v>70217063</v>
       </c>
       <c r="L40" s="15" t="s">
-        <v>211</v>
+        <v>80</v>
       </c>
       <c r="M40" s="15" t="b">
         <v>1</v>
@@ -9827,17 +9867,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:18" s="21" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A42" s="14">
         <v>262</v>
       </c>
-      <c r="B42" s="14" t="s">
+      <c r="B42" s="20" t="s">
         <v>270</v>
       </c>
-      <c r="C42" s="14">
+      <c r="C42" s="20">
         <v>1770</v>
       </c>
-      <c r="D42" s="14" t="s">
+      <c r="D42" s="20" t="s">
         <v>63</v>
       </c>
       <c r="E42" s="14">
@@ -9850,24 +9890,28 @@
         <v>185</v>
       </c>
       <c r="H42" s="14"/>
-      <c r="I42" s="14"/>
+      <c r="I42" s="20"/>
       <c r="J42" s="14"/>
-      <c r="K42" s="15"/>
-      <c r="L42" s="15"/>
-      <c r="M42" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="N42" s="15"/>
-      <c r="O42" s="16" t="s">
+      <c r="K42" s="20">
+        <v>70201029</v>
+      </c>
+      <c r="L42" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="M42" s="20" t="b">
+        <v>1</v>
+      </c>
+      <c r="N42" s="20"/>
+      <c r="O42" s="20" t="s">
         <v>251</v>
       </c>
-      <c r="P42" s="16" t="s">
+      <c r="P42" s="20" t="s">
         <v>272</v>
       </c>
-      <c r="Q42" s="16">
+      <c r="Q42" s="20">
         <v>70.599999999999994</v>
       </c>
-      <c r="R42" s="16" t="b">
+      <c r="R42" s="20" t="b">
         <v>0</v>
       </c>
     </row>
@@ -10193,7 +10237,7 @@
         <v>299</v>
       </c>
       <c r="K49" s="15">
-        <f t="shared" ref="K49" si="8">I49</f>
+        <f>I49</f>
         <v>70222005</v>
       </c>
       <c r="L49" s="15" t="s">
@@ -10406,7 +10450,7 @@
         <v>318</v>
       </c>
       <c r="K53" s="15">
-        <f t="shared" ref="K53:K56" si="9">I53</f>
+        <f>I53</f>
         <v>70211023</v>
       </c>
       <c r="L53" s="15" t="s">
@@ -10461,7 +10505,7 @@
         <v>323</v>
       </c>
       <c r="K54" s="15">
-        <f t="shared" si="9"/>
+        <f>I54</f>
         <v>70212103</v>
       </c>
       <c r="L54" s="15" t="s">
@@ -10516,7 +10560,7 @@
         <v>327</v>
       </c>
       <c r="K55" s="15">
-        <f t="shared" si="9"/>
+        <f>I55</f>
         <v>70209050</v>
       </c>
       <c r="L55" s="15" t="s">
@@ -10571,7 +10615,7 @@
         <v>330</v>
       </c>
       <c r="K56" s="15">
-        <f t="shared" si="9"/>
+        <f>I56</f>
         <v>70212010</v>
       </c>
       <c r="L56" s="15" t="s">
@@ -10680,7 +10724,7 @@
         <v>339</v>
       </c>
       <c r="K58" s="15">
-        <f t="shared" ref="K58" si="10">I58</f>
+        <f>I58</f>
         <v>70211169</v>
       </c>
       <c r="L58" s="15" t="s">
@@ -10843,7 +10887,7 @@
         <v>354</v>
       </c>
       <c r="K61" s="15">
-        <f t="shared" ref="K61" si="11">I61</f>
+        <f>I61</f>
         <v>70211105</v>
       </c>
       <c r="L61" s="15" t="s">
@@ -10952,7 +10996,7 @@
         <v>364</v>
       </c>
       <c r="K63" s="15">
-        <f t="shared" ref="K63:K66" si="12">I63</f>
+        <f>I63</f>
         <v>70213008</v>
       </c>
       <c r="L63" s="15" t="s">
@@ -11007,7 +11051,7 @@
         <v>369</v>
       </c>
       <c r="K64" s="15">
-        <f t="shared" si="12"/>
+        <f>I64</f>
         <v>70211033</v>
       </c>
       <c r="L64" s="15" t="s">
@@ -11062,7 +11106,7 @@
         <v>374</v>
       </c>
       <c r="K65" s="15">
-        <f t="shared" si="12"/>
+        <f>I65</f>
         <v>70207015</v>
       </c>
       <c r="L65" s="15" t="s">
@@ -11117,7 +11161,7 @@
         <v>379</v>
       </c>
       <c r="K66" s="15">
-        <f t="shared" si="12"/>
+        <f>I66</f>
         <v>70212121</v>
       </c>
       <c r="L66" s="15" t="s">
@@ -11175,7 +11219,7 @@
         <v>70211110</v>
       </c>
       <c r="L67" s="14" t="s">
-        <v>211</v>
+        <v>73</v>
       </c>
       <c r="M67" s="14" t="b">
         <v>1</v>
@@ -11226,7 +11270,7 @@
         <v>386</v>
       </c>
       <c r="K68" s="15">
-        <f t="shared" ref="K68:K69" si="13">I68</f>
+        <f>I68</f>
         <v>70212073</v>
       </c>
       <c r="L68" s="15" t="s">
@@ -11281,7 +11325,7 @@
         <v>391</v>
       </c>
       <c r="K69" s="15">
-        <f t="shared" si="13"/>
+        <f>I69</f>
         <v>70211088</v>
       </c>
       <c r="L69" s="15" t="s">
@@ -11339,7 +11383,7 @@
         <v>70211242</v>
       </c>
       <c r="L70" s="15" t="s">
-        <v>211</v>
+        <v>80</v>
       </c>
       <c r="M70" s="15" t="b">
         <v>1</v>
@@ -11444,7 +11488,7 @@
         <v>405</v>
       </c>
       <c r="K72" s="15">
-        <f t="shared" ref="K72" si="14">I72</f>
+        <f>I72</f>
         <v>70214002</v>
       </c>
       <c r="L72" s="15" t="s">
@@ -11553,7 +11597,7 @@
         <v>411</v>
       </c>
       <c r="K74" s="15">
-        <f t="shared" ref="K74" si="15">I74</f>
+        <f>I74</f>
         <v>70222047</v>
       </c>
       <c r="L74" s="15" t="s">
@@ -11705,10 +11749,14 @@
       <c r="H77" s="14"/>
       <c r="I77" s="14"/>
       <c r="J77" s="14"/>
-      <c r="K77" s="15"/>
-      <c r="L77" s="15"/>
+      <c r="K77" s="24">
+        <v>70213038</v>
+      </c>
+      <c r="L77" s="15" t="s">
+        <v>73</v>
+      </c>
       <c r="M77" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N77" s="15"/>
       <c r="O77" s="16" t="s">
@@ -14385,7 +14433,7 @@
         <v>70211110</v>
       </c>
       <c r="L137" s="15" t="s">
-        <v>211</v>
+        <v>80</v>
       </c>
       <c r="M137" s="15" t="b">
         <v>1</v>
@@ -16123,7 +16171,7 @@
         <v>70211110</v>
       </c>
       <c r="L176" s="15" t="s">
-        <v>211</v>
+        <v>80</v>
       </c>
       <c r="M176" s="15" t="b">
         <v>1</v>

--- a/data/raw/crosswalk_variedad_INCAP.xlsx
+++ b/data/raw/crosswalk_variedad_INCAP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wfp-my.sharepoint.com/personal/maicel_monzon_wfp_org/Documents/Documents/Fases_Consultoria/01_analisis_ENGIH2018/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="516" documentId="14_{F8BE0E5F-76BA-446B-8942-BC5680A971A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B86A18F-06E1-4855-8336-057BAE4CE478}"/>
+  <xr:revisionPtr revIDLastSave="630" documentId="14_{F8BE0E5F-76BA-446B-8942-BC5680A971A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BFFF6C68-3DC3-41E6-9B4C-6932758A73CA}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Datos" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Datos!$A$1:$R$773</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Datos!$A$1:$S$773</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5031" uniqueCount="2232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5053" uniqueCount="2233">
   <si>
     <t>Cómo usar este archivo</t>
   </si>
@@ -6739,6 +6739,9 @@
   </si>
   <si>
     <t>Proxy basado en maíz para popcorn.</t>
+  </si>
+  <si>
+    <t>Cereal de desayuno; proxy dentro de cereales fortificados.</t>
   </si>
 </sst>
 </file>
@@ -6816,7 +6819,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -6864,6 +6867,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -6892,7 +6901,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -6948,6 +6957,10 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7629,7 +7642,7 @@
     <col min="7" max="7" width="23.453125" hidden="1" customWidth="1"/>
     <col min="8" max="8" width="18" hidden="1" customWidth="1"/>
     <col min="9" max="9" width="9.453125" customWidth="1"/>
-    <col min="10" max="10" width="17.81640625" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="17.81640625" customWidth="1"/>
     <col min="11" max="11" width="16.7265625" customWidth="1"/>
     <col min="12" max="12" width="20.36328125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12.54296875" bestFit="1" customWidth="1"/>
@@ -9940,10 +9953,14 @@
       <c r="H43" s="14"/>
       <c r="I43" s="14"/>
       <c r="J43" s="14"/>
-      <c r="K43" s="15"/>
-      <c r="L43" s="15"/>
+      <c r="K43" s="15">
+        <v>70204025</v>
+      </c>
+      <c r="L43" s="15" t="s">
+        <v>211</v>
+      </c>
       <c r="M43" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N43" s="15"/>
       <c r="O43" s="16" t="s">
@@ -11797,10 +11814,14 @@
       <c r="H78" s="14"/>
       <c r="I78" s="14"/>
       <c r="J78" s="14"/>
-      <c r="K78" s="15"/>
-      <c r="L78" s="15"/>
+      <c r="K78" s="24">
+        <v>70214009</v>
+      </c>
+      <c r="L78" s="15" t="s">
+        <v>73</v>
+      </c>
       <c r="M78" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N78" s="15"/>
       <c r="O78" s="16" t="s">
@@ -11885,10 +11906,14 @@
       <c r="H80" s="14"/>
       <c r="I80" s="14"/>
       <c r="J80" s="14"/>
-      <c r="K80" s="15"/>
-      <c r="L80" s="15"/>
+      <c r="K80" s="15">
+        <v>70211138</v>
+      </c>
+      <c r="L80" s="15" t="s">
+        <v>73</v>
+      </c>
       <c r="M80" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N80" s="15"/>
       <c r="O80" s="16" t="s">
@@ -11929,10 +11954,14 @@
       <c r="H81" s="14"/>
       <c r="I81" s="14"/>
       <c r="J81" s="14"/>
-      <c r="K81" s="15"/>
-      <c r="L81" s="15"/>
+      <c r="K81" s="15">
+        <v>70213031</v>
+      </c>
+      <c r="L81" s="15" t="s">
+        <v>80</v>
+      </c>
       <c r="M81" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N81" s="15"/>
       <c r="O81" s="16" t="s">
@@ -11973,10 +12002,14 @@
       <c r="H82" s="14"/>
       <c r="I82" s="14"/>
       <c r="J82" s="14"/>
-      <c r="K82" s="15"/>
-      <c r="L82" s="15"/>
+      <c r="K82" s="15">
+        <v>70211118</v>
+      </c>
+      <c r="L82" s="15" t="s">
+        <v>80</v>
+      </c>
       <c r="M82" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N82" s="15"/>
       <c r="O82" s="16" t="s">
@@ -12044,7 +12077,7 @@
       <c r="A84" s="14">
         <v>432</v>
       </c>
-      <c r="B84" s="14" t="s">
+      <c r="B84" s="18" t="s">
         <v>445</v>
       </c>
       <c r="C84" s="14">
@@ -12109,10 +12142,14 @@
       <c r="H85" s="14"/>
       <c r="I85" s="14"/>
       <c r="J85" s="14"/>
-      <c r="K85" s="15"/>
-      <c r="L85" s="15"/>
+      <c r="K85" s="15">
+        <v>70215036</v>
+      </c>
+      <c r="L85" s="15" t="s">
+        <v>73</v>
+      </c>
       <c r="M85" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N85" s="15"/>
       <c r="O85" s="16" t="s">
@@ -12132,7 +12169,7 @@
       <c r="A86" s="14">
         <v>359</v>
       </c>
-      <c r="B86" s="14" t="s">
+      <c r="B86" s="18" t="s">
         <v>452</v>
       </c>
       <c r="C86" s="14">
@@ -12153,10 +12190,14 @@
       <c r="H86" s="14"/>
       <c r="I86" s="14"/>
       <c r="J86" s="14"/>
-      <c r="K86" s="15"/>
-      <c r="L86" s="15"/>
+      <c r="K86" s="24">
+        <v>70212156</v>
+      </c>
+      <c r="L86" s="15" t="s">
+        <v>80</v>
+      </c>
       <c r="M86" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N86" s="15"/>
       <c r="O86" s="16" t="s">
@@ -12247,10 +12288,14 @@
       <c r="H88" s="14"/>
       <c r="I88" s="14"/>
       <c r="J88" s="14"/>
-      <c r="K88" s="15"/>
-      <c r="L88" s="15"/>
+      <c r="K88" s="15">
+        <v>70212125</v>
+      </c>
+      <c r="L88" s="15" t="s">
+        <v>80</v>
+      </c>
       <c r="M88" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N88" s="15"/>
       <c r="O88" s="16" t="s">
@@ -12270,7 +12315,7 @@
       <c r="A89" s="14">
         <v>645</v>
       </c>
-      <c r="B89" s="14" t="s">
+      <c r="B89" s="18" t="s">
         <v>466</v>
       </c>
       <c r="C89" s="14">
@@ -12335,10 +12380,14 @@
       <c r="H90" s="14"/>
       <c r="I90" s="14"/>
       <c r="J90" s="14"/>
-      <c r="K90" s="15"/>
-      <c r="L90" s="15"/>
+      <c r="K90" s="15">
+        <v>70211060</v>
+      </c>
+      <c r="L90" s="15" t="s">
+        <v>80</v>
+      </c>
       <c r="M90" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N90" s="15"/>
       <c r="O90" s="16" t="s">
@@ -12354,17 +12403,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:18" s="30" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A91" s="14">
         <v>18</v>
       </c>
-      <c r="B91" s="14" t="s">
+      <c r="B91" s="29" t="s">
         <v>473</v>
       </c>
-      <c r="C91" s="14">
+      <c r="C91" s="29">
         <v>668</v>
       </c>
-      <c r="D91" s="14" t="s">
+      <c r="D91" s="29" t="s">
         <v>63</v>
       </c>
       <c r="E91" s="14">
@@ -12377,24 +12426,28 @@
         <v>103</v>
       </c>
       <c r="H91" s="14"/>
-      <c r="I91" s="14"/>
-      <c r="J91" s="14"/>
-      <c r="K91" s="15"/>
-      <c r="L91" s="15"/>
-      <c r="M91" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="N91" s="15"/>
-      <c r="O91" s="16" t="s">
+      <c r="I91" s="29"/>
+      <c r="J91" s="29"/>
+      <c r="K91" s="24">
+        <v>70214002</v>
+      </c>
+      <c r="L91" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="M91" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="N91" s="29"/>
+      <c r="O91" s="29" t="s">
         <v>193</v>
       </c>
-      <c r="P91" s="16" t="s">
+      <c r="P91" s="29" t="s">
         <v>475</v>
       </c>
-      <c r="Q91" s="16">
+      <c r="Q91" s="29">
         <v>76.900000000000006</v>
       </c>
-      <c r="R91" s="16" t="b">
+      <c r="R91" s="29" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12423,10 +12476,14 @@
       <c r="H92" s="14"/>
       <c r="I92" s="14"/>
       <c r="J92" s="14"/>
-      <c r="K92" s="15"/>
-      <c r="L92" s="15"/>
+      <c r="K92" s="15">
+        <v>70212112</v>
+      </c>
+      <c r="L92" s="15" t="s">
+        <v>73</v>
+      </c>
       <c r="M92" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N92" s="15"/>
       <c r="O92" s="16" t="s">
@@ -12442,17 +12499,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:18" s="21" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A93" s="14">
         <v>76</v>
       </c>
-      <c r="B93" s="14" t="s">
+      <c r="B93" s="20" t="s">
         <v>480</v>
       </c>
-      <c r="C93" s="14">
+      <c r="C93" s="20">
         <v>656</v>
       </c>
-      <c r="D93" s="14" t="s">
+      <c r="D93" s="20" t="s">
         <v>107</v>
       </c>
       <c r="E93" s="14">
@@ -12465,24 +12522,30 @@
         <v>142</v>
       </c>
       <c r="H93" s="14"/>
-      <c r="I93" s="14"/>
-      <c r="J93" s="14"/>
-      <c r="K93" s="15"/>
-      <c r="L93" s="15"/>
-      <c r="M93" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="N93" s="15"/>
-      <c r="O93" s="16" t="s">
+      <c r="I93" s="20"/>
+      <c r="J93" s="20"/>
+      <c r="K93" s="20">
+        <v>70213027</v>
+      </c>
+      <c r="L93" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="M93" s="20" t="b">
+        <v>1</v>
+      </c>
+      <c r="N93" s="28" t="s">
+        <v>2232</v>
+      </c>
+      <c r="O93" s="20" t="s">
         <v>482</v>
       </c>
-      <c r="P93" s="16" t="s">
+      <c r="P93" s="20" t="s">
         <v>483</v>
       </c>
-      <c r="Q93" s="16">
+      <c r="Q93" s="20">
         <v>58.5</v>
       </c>
-      <c r="R93" s="16" t="b">
+      <c r="R93" s="20" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12511,10 +12574,14 @@
       <c r="H94" s="14"/>
       <c r="I94" s="14"/>
       <c r="J94" s="14"/>
-      <c r="K94" s="15"/>
-      <c r="L94" s="15"/>
+      <c r="K94" s="24">
+        <v>70222017</v>
+      </c>
+      <c r="L94" s="15" t="s">
+        <v>80</v>
+      </c>
       <c r="M94" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N94" s="15"/>
       <c r="O94" s="16" t="s">
@@ -12555,10 +12622,14 @@
       <c r="H95" s="14"/>
       <c r="I95" s="14"/>
       <c r="J95" s="14"/>
-      <c r="K95" s="15"/>
-      <c r="L95" s="15"/>
+      <c r="K95" s="15">
+        <v>70211195</v>
+      </c>
+      <c r="L95" s="15" t="s">
+        <v>73</v>
+      </c>
       <c r="M95" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N95" s="15"/>
       <c r="O95" s="16" t="s">
@@ -12735,10 +12806,14 @@
       <c r="H99" s="14"/>
       <c r="I99" s="14"/>
       <c r="J99" s="14"/>
-      <c r="K99" s="15"/>
-      <c r="L99" s="15"/>
+      <c r="K99" s="24">
+        <v>70208018</v>
+      </c>
+      <c r="L99" s="15" t="s">
+        <v>73</v>
+      </c>
       <c r="M99" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N99" s="15"/>
       <c r="O99" s="16" t="s">
@@ -12779,16 +12854,20 @@
       <c r="H100" s="14"/>
       <c r="I100" s="14"/>
       <c r="J100" s="14"/>
-      <c r="K100" s="15"/>
-      <c r="L100" s="15"/>
+      <c r="K100" s="15">
+        <v>70212031</v>
+      </c>
+      <c r="L100" s="15" t="s">
+        <v>73</v>
+      </c>
       <c r="M100" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N100" s="15"/>
       <c r="O100" s="16" t="s">
         <v>507</v>
       </c>
-      <c r="P100" s="16" t="s">
+      <c r="P100" s="27" t="s">
         <v>508</v>
       </c>
       <c r="Q100" s="16">
@@ -12823,10 +12902,14 @@
       <c r="H101" s="14"/>
       <c r="I101" s="14"/>
       <c r="J101" s="14"/>
-      <c r="K101" s="15"/>
-      <c r="L101" s="15"/>
+      <c r="K101" s="15">
+        <v>70201010</v>
+      </c>
+      <c r="L101" s="15" t="s">
+        <v>73</v>
+      </c>
       <c r="M101" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N101" s="15"/>
       <c r="O101" s="16" t="s">
@@ -12867,10 +12950,14 @@
       <c r="H102" s="14"/>
       <c r="I102" s="14"/>
       <c r="J102" s="14"/>
-      <c r="K102" s="15"/>
-      <c r="L102" s="15"/>
+      <c r="K102" s="15">
+        <v>70211191</v>
+      </c>
+      <c r="L102" s="15" t="s">
+        <v>80</v>
+      </c>
       <c r="M102" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N102" s="15"/>
       <c r="O102" s="16" t="s">
@@ -12911,10 +12998,14 @@
       <c r="H103" s="14"/>
       <c r="I103" s="14"/>
       <c r="J103" s="14"/>
-      <c r="K103" s="15"/>
-      <c r="L103" s="15"/>
+      <c r="K103" s="24">
+        <v>70222017</v>
+      </c>
+      <c r="L103" s="15" t="s">
+        <v>73</v>
+      </c>
       <c r="M103" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N103" s="15"/>
       <c r="O103" s="16" t="s">
@@ -12930,17 +13021,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:18" s="21" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A104" s="14">
         <v>263</v>
       </c>
-      <c r="B104" s="14" t="s">
+      <c r="B104" s="20" t="s">
         <v>518</v>
       </c>
-      <c r="C104" s="14">
+      <c r="C104" s="20">
         <v>502</v>
       </c>
-      <c r="D104" s="14" t="s">
+      <c r="D104" s="20" t="s">
         <v>63</v>
       </c>
       <c r="E104" s="14">
@@ -12953,24 +13044,28 @@
         <v>185</v>
       </c>
       <c r="H104" s="14"/>
-      <c r="I104" s="14"/>
-      <c r="J104" s="14"/>
-      <c r="K104" s="15"/>
-      <c r="L104" s="15"/>
-      <c r="M104" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="N104" s="15"/>
-      <c r="O104" s="16" t="s">
+      <c r="I104" s="20"/>
+      <c r="J104" s="20"/>
+      <c r="K104" s="20">
+        <v>70201029</v>
+      </c>
+      <c r="L104" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="M104" s="20" t="b">
+        <v>1</v>
+      </c>
+      <c r="N104" s="20"/>
+      <c r="O104" s="20" t="s">
         <v>251</v>
       </c>
-      <c r="P104" s="16" t="s">
+      <c r="P104" s="20" t="s">
         <v>272</v>
       </c>
-      <c r="Q104" s="16">
+      <c r="Q104" s="20">
         <v>83.3</v>
       </c>
-      <c r="R104" s="16" t="b">
+      <c r="R104" s="20" t="b">
         <v>0</v>
       </c>
     </row>
@@ -29755,10 +29850,14 @@
       <c r="H482" s="14"/>
       <c r="I482" s="14"/>
       <c r="J482" s="14"/>
-      <c r="K482" s="15"/>
-      <c r="L482" s="15"/>
+      <c r="K482" s="24">
+        <v>70208018</v>
+      </c>
+      <c r="L482" s="15" t="s">
+        <v>80</v>
+      </c>
       <c r="M482" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N482" s="15"/>
       <c r="O482" s="16" t="s">
@@ -42663,7 +42762,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R773" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
+  <autoFilter ref="A1:S773" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <conditionalFormatting sqref="B2:B773">
     <cfRule type="expression" dxfId="4" priority="5">
       <formula>$H2&lt;&gt;""</formula>

--- a/data/raw/crosswalk_variedad_INCAP.xlsx
+++ b/data/raw/crosswalk_variedad_INCAP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wfp-my.sharepoint.com/personal/maicel_monzon_wfp_org/Documents/Documents/Fases_Consultoria/01_analisis_ENGIH2018/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="630" documentId="14_{F8BE0E5F-76BA-446B-8942-BC5680A971A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BFFF6C68-3DC3-41E6-9B4C-6932758A73CA}"/>
+  <xr:revisionPtr revIDLastSave="655" documentId="14_{F8BE0E5F-76BA-446B-8942-BC5680A971A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E60BA1F-8A1A-420F-8BB6-58EE6519D40F}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5053" uniqueCount="2233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5056" uniqueCount="2234">
   <si>
     <t>Cómo usar este archivo</t>
   </si>
@@ -6742,13 +6742,16 @@
   </si>
   <si>
     <t>Cereal de desayuno; proxy dentro de cereales fortificados.</t>
+  </si>
+  <si>
+    <t>FNDDS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6818,8 +6821,26 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="8" tint="-0.249977111117893"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="8" tint="-0.249977111117893"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="8" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -6873,6 +6894,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -6901,7 +6934,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -6961,6 +6994,19 @@
     <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7630,31 +7676,32 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:R773"/>
+  <dimension ref="A1:S773"/>
   <sheetFormatPr defaultRowHeight="14.5" outlineLevelCol="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.1796875" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="14.1796875" style="40" customWidth="1"/>
     <col min="2" max="2" width="32.54296875" customWidth="1"/>
     <col min="3" max="3" width="14.08984375" customWidth="1"/>
-    <col min="4" max="4" width="21.81640625" customWidth="1"/>
-    <col min="5" max="5" width="14.6328125" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="24.54296875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.81640625" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="14.6328125" customWidth="1"/>
+    <col min="6" max="6" width="48.1796875" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="23.453125" hidden="1" customWidth="1"/>
     <col min="8" max="8" width="18" hidden="1" customWidth="1"/>
     <col min="9" max="9" width="9.453125" customWidth="1"/>
-    <col min="10" max="10" width="17.81640625" customWidth="1"/>
+    <col min="10" max="10" width="17.81640625" hidden="1" customWidth="1"/>
     <col min="11" max="11" width="16.7265625" customWidth="1"/>
     <col min="12" max="12" width="20.36328125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12.54296875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="20" customWidth="1"/>
-    <col min="15" max="15" width="12" customWidth="1" outlineLevel="1"/>
-    <col min="16" max="16" width="22" customWidth="1" outlineLevel="1"/>
-    <col min="17" max="17" width="9" customWidth="1" outlineLevel="1"/>
-    <col min="18" max="18" width="11" customWidth="1" outlineLevel="1"/>
+    <col min="15" max="15" width="12" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="16" max="16" width="22" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="17" max="17" width="9" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="18" max="18" width="11" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="19" max="19" width="8.7265625" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="39" x14ac:dyDescent="0.35">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="35" t="s">
         <v>23</v>
       </c>
       <c r="B1" s="11" t="s">
@@ -7709,114 +7756,114 @@
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A2" s="14">
+    <row r="2" spans="1:18" s="32" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="36">
         <v>569</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="41" t="s">
         <v>62</v>
       </c>
-      <c r="C2" s="14">
+      <c r="C2" s="31">
         <v>18087</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="D2" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="E2" s="14">
+      <c r="E2" s="31">
         <v>70207012</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="F2" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="G2" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="H2" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14" t="s">
+      <c r="I2" s="31"/>
+      <c r="J2" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15" t="s">
+      <c r="K2" s="31"/>
+      <c r="L2" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="M2" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="N2" s="15" t="s">
+      <c r="M2" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="N2" s="31" t="s">
         <v>2220</v>
       </c>
-      <c r="O2" s="16" t="s">
+      <c r="O2" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="P2" s="16" t="s">
+      <c r="P2" s="31" t="s">
         <v>69</v>
       </c>
-      <c r="Q2" s="16">
+      <c r="Q2" s="31">
         <v>72.7</v>
       </c>
-      <c r="R2" s="16" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A3" s="14">
+      <c r="R2" s="31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" s="34" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="37">
         <v>408</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="C3" s="14">
+      <c r="C3" s="33">
         <v>15414</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="33" t="s">
         <v>63</v>
       </c>
-      <c r="E3" s="14">
+      <c r="E3" s="33">
         <v>70211223</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="33" t="s">
         <v>71</v>
       </c>
-      <c r="G3" s="14" t="s">
+      <c r="G3" s="33" t="s">
         <v>72</v>
       </c>
-      <c r="H3" s="14" t="s">
+      <c r="H3" s="33" t="s">
         <v>73</v>
       </c>
-      <c r="I3" s="14">
+      <c r="I3" s="33">
         <v>70211223</v>
       </c>
-      <c r="J3" s="14" t="s">
+      <c r="J3" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="K3" s="15">
+      <c r="K3" s="33">
         <v>70211223</v>
       </c>
-      <c r="L3" s="15" t="s">
+      <c r="L3" s="33" t="s">
         <v>73</v>
       </c>
-      <c r="M3" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="N3" s="15"/>
-      <c r="O3" s="16" t="s">
+      <c r="M3" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="N3" s="33"/>
+      <c r="O3" s="33" t="s">
         <v>75</v>
       </c>
-      <c r="P3" s="16" t="s">
+      <c r="P3" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="Q3" s="16">
+      <c r="Q3" s="33">
         <v>76.900000000000006</v>
       </c>
-      <c r="R3" s="16" t="b">
+      <c r="R3" s="33" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A4" s="14">
+      <c r="A4" s="38">
         <v>110</v>
       </c>
       <c r="B4" s="14" t="s">
@@ -7849,28 +7896,28 @@
       <c r="K4" s="14">
         <v>70203019</v>
       </c>
-      <c r="L4" s="15" t="s">
+      <c r="L4" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="M4" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="N4" s="15"/>
-      <c r="O4" s="16" t="s">
+      <c r="M4" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="N4" s="14"/>
+      <c r="O4" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="P4" s="16" t="s">
+      <c r="P4" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="Q4" s="16">
+      <c r="Q4" s="14">
         <v>84.6</v>
       </c>
-      <c r="R4" s="16" t="b">
+      <c r="R4" s="14" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A5" s="14">
+      <c r="A5" s="38">
         <v>545</v>
       </c>
       <c r="B5" s="14" t="s">
@@ -7925,7 +7972,7 @@
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A6" s="14">
+      <c r="A6" s="38">
         <v>288</v>
       </c>
       <c r="B6" s="14" t="s">
@@ -7980,7 +8027,7 @@
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A7" s="14">
+      <c r="A7" s="38">
         <v>410</v>
       </c>
       <c r="B7" s="14" t="s">
@@ -8037,7 +8084,7 @@
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A8" s="14">
+      <c r="A8" s="38">
         <v>293</v>
       </c>
       <c r="B8" s="14" t="s">
@@ -8092,7 +8139,7 @@
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A9" s="14">
+      <c r="A9" s="38">
         <v>2</v>
       </c>
       <c r="B9" s="14" t="s">
@@ -8146,7 +8193,7 @@
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A10" s="14">
+      <c r="A10" s="38">
         <v>588</v>
       </c>
       <c r="B10" s="14" t="s">
@@ -8200,7 +8247,7 @@
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A11" s="14">
+      <c r="A11" s="38">
         <v>392</v>
       </c>
       <c r="B11" s="14" t="s">
@@ -8254,7 +8301,7 @@
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A12" s="14">
+      <c r="A12" s="38">
         <v>515</v>
       </c>
       <c r="B12" s="14" t="s">
@@ -8308,7 +8355,7 @@
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A13" s="14">
+      <c r="A13" s="38">
         <v>66</v>
       </c>
       <c r="B13" s="14" t="s">
@@ -8362,7 +8409,7 @@
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A14" s="14">
+      <c r="A14" s="38">
         <v>581</v>
       </c>
       <c r="B14" s="14" t="s">
@@ -8419,7 +8466,7 @@
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A15" s="14">
+      <c r="A15" s="38">
         <v>459</v>
       </c>
       <c r="B15" s="14" t="s">
@@ -8474,7 +8521,7 @@
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A16" s="14">
+      <c r="A16" s="38">
         <v>594</v>
       </c>
       <c r="B16" s="14" t="s">
@@ -8524,7 +8571,7 @@
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A17" s="14">
+      <c r="A17" s="38">
         <v>67</v>
       </c>
       <c r="B17" s="14" t="s">
@@ -8579,7 +8626,7 @@
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A18" s="14">
+      <c r="A18" s="38">
         <v>314</v>
       </c>
       <c r="B18" s="14" t="s">
@@ -8634,7 +8681,7 @@
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A19" s="14">
+      <c r="A19" s="38">
         <v>1</v>
       </c>
       <c r="B19" s="14" t="s">
@@ -8688,7 +8735,7 @@
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A20" s="14">
+      <c r="A20" s="38">
         <v>324</v>
       </c>
       <c r="B20" s="14" t="s">
@@ -8743,7 +8790,7 @@
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A21" s="14">
+      <c r="A21" s="38">
         <v>552</v>
       </c>
       <c r="B21" s="14" t="s">
@@ -8797,7 +8844,7 @@
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A22" s="14">
+      <c r="A22" s="38">
         <v>178</v>
       </c>
       <c r="B22" s="14" t="s">
@@ -8851,7 +8898,7 @@
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A23" s="14">
+      <c r="A23" s="38">
         <v>385</v>
       </c>
       <c r="B23" s="14" t="s">
@@ -8906,7 +8953,7 @@
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A24" s="14">
+      <c r="A24" s="38">
         <v>243</v>
       </c>
       <c r="B24" s="14" t="s">
@@ -8961,7 +9008,7 @@
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A25" s="14">
+      <c r="A25" s="38">
         <v>23</v>
       </c>
       <c r="B25" s="14" t="s">
@@ -9015,7 +9062,7 @@
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A26" s="14">
+      <c r="A26" s="38">
         <v>386</v>
       </c>
       <c r="B26" s="14" t="s">
@@ -9069,7 +9116,7 @@
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A27" s="14">
+      <c r="A27" s="38">
         <v>368</v>
       </c>
       <c r="B27" s="14" t="s">
@@ -9124,7 +9171,7 @@
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A28" s="14">
+      <c r="A28" s="38">
         <v>254</v>
       </c>
       <c r="B28" s="14" t="s">
@@ -9179,7 +9226,7 @@
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A29" s="14">
+      <c r="A29" s="38">
         <v>371</v>
       </c>
       <c r="B29" s="14" t="s">
@@ -9233,7 +9280,7 @@
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A30" s="14">
+      <c r="A30" s="38">
         <v>610</v>
       </c>
       <c r="B30" s="14" t="s">
@@ -9288,7 +9335,7 @@
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A31" s="14">
+      <c r="A31" s="38">
         <v>311</v>
       </c>
       <c r="B31" s="14" t="s">
@@ -9343,7 +9390,7 @@
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A32" s="14">
+      <c r="A32" s="38">
         <v>420</v>
       </c>
       <c r="B32" s="14" t="s">
@@ -9398,7 +9445,7 @@
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A33" s="14">
+      <c r="A33" s="38">
         <v>399</v>
       </c>
       <c r="B33" s="14" t="s">
@@ -9450,7 +9497,7 @@
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A34" s="14">
+      <c r="A34" s="38">
         <v>303</v>
       </c>
       <c r="B34" s="14" t="s">
@@ -9504,7 +9551,7 @@
       </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A35" s="14">
+      <c r="A35" s="38">
         <v>586</v>
       </c>
       <c r="B35" s="14" t="s">
@@ -9558,7 +9605,7 @@
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A36" s="14">
+      <c r="A36" s="38">
         <v>88</v>
       </c>
       <c r="B36" s="14" t="s">
@@ -9614,7 +9661,7 @@
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A37" s="14">
+      <c r="A37" s="38">
         <v>260</v>
       </c>
       <c r="B37" s="14" t="s">
@@ -9669,7 +9716,7 @@
       </c>
     </row>
     <row r="38" spans="1:18" s="21" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="20">
+      <c r="A38" s="39">
         <v>159</v>
       </c>
       <c r="B38" s="20" t="s">
@@ -9723,7 +9770,7 @@
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A39" s="14">
+      <c r="A39" s="38">
         <v>177</v>
       </c>
       <c r="B39" s="14" t="s">
@@ -9777,7 +9824,7 @@
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A40" s="14">
+      <c r="A40" s="38">
         <v>649</v>
       </c>
       <c r="B40" s="14" t="s">
@@ -9833,7 +9880,7 @@
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A41" s="14">
+      <c r="A41" s="38">
         <v>313</v>
       </c>
       <c r="B41" s="14" t="s">
@@ -9881,7 +9928,7 @@
       </c>
     </row>
     <row r="42" spans="1:18" s="21" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="14">
+      <c r="A42" s="38">
         <v>262</v>
       </c>
       <c r="B42" s="20" t="s">
@@ -9929,7 +9976,7 @@
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A43" s="14">
+      <c r="A43" s="38">
         <v>128</v>
       </c>
       <c r="B43" s="14" t="s">
@@ -9977,7 +10024,7 @@
       </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A44" s="14">
+      <c r="A44" s="38">
         <v>553</v>
       </c>
       <c r="B44" s="14" t="s">
@@ -10021,7 +10068,7 @@
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A45" s="14">
+      <c r="A45" s="38">
         <v>393</v>
       </c>
       <c r="B45" s="14" t="s">
@@ -10069,7 +10116,7 @@
       </c>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A46" s="14">
+      <c r="A46" s="38">
         <v>620</v>
       </c>
       <c r="B46" s="14" t="s">
@@ -10096,9 +10143,11 @@
       <c r="K46" s="15"/>
       <c r="L46" s="15"/>
       <c r="M46" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="N46" s="15"/>
+        <v>1</v>
+      </c>
+      <c r="N46" s="23" t="s">
+        <v>2233</v>
+      </c>
       <c r="O46" s="16" t="s">
         <v>217</v>
       </c>
@@ -10113,7 +10162,7 @@
       </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A47" s="14">
+      <c r="A47" s="38">
         <v>87</v>
       </c>
       <c r="B47" s="14" t="s">
@@ -10167,7 +10216,7 @@
       </c>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A48" s="14">
+      <c r="A48" s="38">
         <v>232</v>
       </c>
       <c r="B48" s="14" t="s">
@@ -10223,7 +10272,7 @@
       </c>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A49" s="14">
+      <c r="A49" s="38">
         <v>523</v>
       </c>
       <c r="B49" s="14" t="s">
@@ -10278,7 +10327,7 @@
       </c>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A50" s="14">
+      <c r="A50" s="38">
         <v>108</v>
       </c>
       <c r="B50" s="14" t="s">
@@ -10332,7 +10381,7 @@
       </c>
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A51" s="14">
+      <c r="A51" s="38">
         <v>396</v>
       </c>
       <c r="B51" s="14" t="s">
@@ -10386,7 +10435,7 @@
       </c>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A52" s="14">
+      <c r="A52" s="38">
         <v>554</v>
       </c>
       <c r="B52" s="14" t="s">
@@ -10436,7 +10485,7 @@
       </c>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A53" s="14">
+      <c r="A53" s="38">
         <v>403</v>
       </c>
       <c r="B53" s="14" t="s">
@@ -10491,7 +10540,7 @@
       </c>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A54" s="14">
+      <c r="A54" s="38">
         <v>336</v>
       </c>
       <c r="B54" s="14" t="s">
@@ -10546,7 +10595,7 @@
       </c>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A55" s="14">
+      <c r="A55" s="38">
         <v>369</v>
       </c>
       <c r="B55" s="14" t="s">
@@ -10601,7 +10650,7 @@
       </c>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A56" s="14">
+      <c r="A56" s="38">
         <v>323</v>
       </c>
       <c r="B56" s="14" t="s">
@@ -10656,7 +10705,7 @@
       </c>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A57" s="14">
+      <c r="A57" s="38">
         <v>237</v>
       </c>
       <c r="B57" s="14" t="s">
@@ -10710,7 +10759,7 @@
       </c>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A58" s="14">
+      <c r="A58" s="38">
         <v>400</v>
       </c>
       <c r="B58" s="14" t="s">
@@ -10765,7 +10814,7 @@
       </c>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A59" s="14">
+      <c r="A59" s="38">
         <v>417</v>
       </c>
       <c r="B59" s="14" t="s">
@@ -10819,7 +10868,7 @@
       </c>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A60" s="14">
+      <c r="A60" s="38">
         <v>401</v>
       </c>
       <c r="B60" s="14" t="s">
@@ -10873,7 +10922,7 @@
       </c>
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A61" s="14">
+      <c r="A61" s="38">
         <v>427</v>
       </c>
       <c r="B61" s="14" t="s">
@@ -10928,7 +10977,7 @@
       </c>
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A62" s="14">
+      <c r="A62" s="38">
         <v>587</v>
       </c>
       <c r="B62" s="14" t="s">
@@ -10982,7 +11031,7 @@
       </c>
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A63" s="14">
+      <c r="A63" s="38">
         <v>71</v>
       </c>
       <c r="B63" s="14" t="s">
@@ -11037,7 +11086,7 @@
       </c>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A64" s="14">
+      <c r="A64" s="38">
         <v>389</v>
       </c>
       <c r="B64" s="14" t="s">
@@ -11092,7 +11141,7 @@
       </c>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A65" s="14">
+      <c r="A65" s="38">
         <v>174</v>
       </c>
       <c r="B65" s="14" t="s">
@@ -11147,7 +11196,7 @@
       </c>
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A66" s="14">
+      <c r="A66" s="38">
         <v>611</v>
       </c>
       <c r="B66" s="14" t="s">
@@ -11202,7 +11251,7 @@
       </c>
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A67" s="14">
+      <c r="A67" s="38">
         <v>506</v>
       </c>
       <c r="B67" s="14" t="s">
@@ -11256,7 +11305,7 @@
       </c>
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A68" s="14">
+      <c r="A68" s="38">
         <v>328</v>
       </c>
       <c r="B68" s="14" t="s">
@@ -11311,7 +11360,7 @@
       </c>
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A69" s="14">
+      <c r="A69" s="38">
         <v>376</v>
       </c>
       <c r="B69" s="14" t="s">
@@ -11366,7 +11415,7 @@
       </c>
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A70" s="14">
+      <c r="A70" s="38">
         <v>447</v>
       </c>
       <c r="B70" s="18" t="s">
@@ -11422,7 +11471,7 @@
       </c>
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A71" s="14">
+      <c r="A71" s="38">
         <v>419</v>
       </c>
       <c r="B71" s="14" t="s">
@@ -11474,7 +11523,7 @@
       </c>
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A72" s="14">
+      <c r="A72" s="38">
         <v>20</v>
       </c>
       <c r="B72" s="14" t="s">
@@ -11529,7 +11578,7 @@
       </c>
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A73" s="14">
+      <c r="A73" s="38">
         <v>439</v>
       </c>
       <c r="B73" s="14" t="s">
@@ -11583,7 +11632,7 @@
       </c>
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A74" s="14">
+      <c r="A74" s="38">
         <v>514</v>
       </c>
       <c r="B74" s="14" t="s">
@@ -11638,7 +11687,7 @@
       </c>
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A75" s="14">
+      <c r="A75" s="38">
         <v>541</v>
       </c>
       <c r="B75" s="14" t="s">
@@ -11688,7 +11737,7 @@
       </c>
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A76" s="14">
+      <c r="A76" s="38">
         <v>242</v>
       </c>
       <c r="B76" s="14" t="s">
@@ -11742,7 +11791,7 @@
       </c>
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A77" s="14">
+      <c r="A77" s="38">
         <v>58</v>
       </c>
       <c r="B77" s="14" t="s">
@@ -11790,7 +11839,7 @@
       </c>
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A78" s="14">
+      <c r="A78" s="38">
         <v>19</v>
       </c>
       <c r="B78" s="14" t="s">
@@ -11838,7 +11887,7 @@
       </c>
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A79" s="14">
+      <c r="A79" s="38">
         <v>579</v>
       </c>
       <c r="B79" s="14" t="s">
@@ -11867,7 +11916,7 @@
       <c r="M79" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="N79" s="15"/>
+      <c r="N79" s="23"/>
       <c r="O79" s="16" t="s">
         <v>432</v>
       </c>
@@ -11882,7 +11931,7 @@
       </c>
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A80" s="14">
+      <c r="A80" s="38">
         <v>414</v>
       </c>
       <c r="B80" s="14" t="s">
@@ -11930,7 +11979,7 @@
       </c>
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A81" s="14">
+      <c r="A81" s="38">
         <v>56</v>
       </c>
       <c r="B81" s="14" t="s">
@@ -11978,7 +12027,7 @@
       </c>
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A82" s="14">
+      <c r="A82" s="38">
         <v>3587</v>
       </c>
       <c r="B82" s="14" t="s">
@@ -12026,7 +12075,7 @@
       </c>
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A83" s="14">
+      <c r="A83" s="38">
         <v>367</v>
       </c>
       <c r="B83" s="14" t="s">
@@ -12074,7 +12123,7 @@
       </c>
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A84" s="14">
+      <c r="A84" s="38">
         <v>432</v>
       </c>
       <c r="B84" s="18" t="s">
@@ -12118,7 +12167,7 @@
       </c>
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A85" s="14">
+      <c r="A85" s="38">
         <v>458</v>
       </c>
       <c r="B85" s="14" t="s">
@@ -12166,7 +12215,7 @@
       </c>
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A86" s="14">
+      <c r="A86" s="38">
         <v>359</v>
       </c>
       <c r="B86" s="18" t="s">
@@ -12214,7 +12263,7 @@
       </c>
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A87" s="14">
+      <c r="A87" s="38">
         <v>652</v>
       </c>
       <c r="B87" s="14" t="s">
@@ -12264,7 +12313,7 @@
       </c>
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A88" s="14">
+      <c r="A88" s="38">
         <v>340</v>
       </c>
       <c r="B88" s="14" t="s">
@@ -12312,7 +12361,7 @@
       </c>
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A89" s="14">
+      <c r="A89" s="38">
         <v>645</v>
       </c>
       <c r="B89" s="18" t="s">
@@ -12356,7 +12405,7 @@
       </c>
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A90" s="14">
+      <c r="A90" s="38">
         <v>395</v>
       </c>
       <c r="B90" s="14" t="s">
@@ -12404,7 +12453,7 @@
       </c>
     </row>
     <row r="91" spans="1:18" s="30" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A91" s="14">
+      <c r="A91" s="38">
         <v>18</v>
       </c>
       <c r="B91" s="29" t="s">
@@ -12452,7 +12501,7 @@
       </c>
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A92" s="14">
+      <c r="A92" s="38">
         <v>326</v>
       </c>
       <c r="B92" s="14" t="s">
@@ -12500,7 +12549,7 @@
       </c>
     </row>
     <row r="93" spans="1:18" s="21" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="14">
+      <c r="A93" s="38">
         <v>76</v>
       </c>
       <c r="B93" s="20" t="s">
@@ -12550,7 +12599,7 @@
       </c>
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A94" s="14">
+      <c r="A94" s="38">
         <v>535</v>
       </c>
       <c r="B94" s="14" t="s">
@@ -12598,7 +12647,7 @@
       </c>
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A95" s="14">
+      <c r="A95" s="38">
         <v>383</v>
       </c>
       <c r="B95" s="14" t="s">
@@ -12646,7 +12695,7 @@
       </c>
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A96" s="14">
+      <c r="A96" s="38">
         <v>267</v>
       </c>
       <c r="B96" s="14" t="s">
@@ -12694,7 +12743,7 @@
       </c>
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A97" s="14">
+      <c r="A97" s="38">
         <v>496</v>
       </c>
       <c r="B97" s="14" t="s">
@@ -12719,9 +12768,11 @@
       <c r="I97" s="14"/>
       <c r="J97" s="14"/>
       <c r="K97" s="15"/>
-      <c r="L97" s="15"/>
+      <c r="L97" s="15" t="s">
+        <v>458</v>
+      </c>
       <c r="M97" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N97" s="15"/>
       <c r="O97" s="16" t="s">
@@ -12738,7 +12789,7 @@
       </c>
     </row>
     <row r="98" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A98" s="14">
+      <c r="A98" s="38">
         <v>3506</v>
       </c>
       <c r="B98" s="14" t="s">
@@ -12762,10 +12813,14 @@
       <c r="H98" s="14"/>
       <c r="I98" s="14"/>
       <c r="J98" s="14"/>
-      <c r="K98" s="15"/>
-      <c r="L98" s="15"/>
+      <c r="K98" s="15">
+        <v>70214077</v>
+      </c>
+      <c r="L98" s="15" t="s">
+        <v>80</v>
+      </c>
       <c r="M98" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N98" s="15"/>
       <c r="O98" s="16" t="s">
@@ -12782,7 +12837,7 @@
       </c>
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A99" s="14">
+      <c r="A99" s="38">
         <v>228</v>
       </c>
       <c r="B99" s="14" t="s">
@@ -12830,7 +12885,7 @@
       </c>
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A100" s="14">
+      <c r="A100" s="38">
         <v>317</v>
       </c>
       <c r="B100" s="14" t="s">
@@ -12878,7 +12933,7 @@
       </c>
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A101" s="14">
+      <c r="A101" s="38">
         <v>251</v>
       </c>
       <c r="B101" s="14" t="s">
@@ -12926,7 +12981,7 @@
       </c>
     </row>
     <row r="102" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A102" s="14">
+      <c r="A102" s="38">
         <v>457</v>
       </c>
       <c r="B102" s="14" t="s">
@@ -12974,7 +13029,7 @@
       </c>
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A103" s="14">
+      <c r="A103" s="38">
         <v>534</v>
       </c>
       <c r="B103" s="14" t="s">
@@ -13022,7 +13077,7 @@
       </c>
     </row>
     <row r="104" spans="1:18" s="21" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A104" s="14">
+      <c r="A104" s="38">
         <v>263</v>
       </c>
       <c r="B104" s="20" t="s">
@@ -13070,7 +13125,7 @@
       </c>
     </row>
     <row r="105" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A105" s="14">
+      <c r="A105" s="38">
         <v>86</v>
       </c>
       <c r="B105" s="14" t="s">
@@ -13118,7 +13173,7 @@
       </c>
     </row>
     <row r="106" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A106" s="14">
+      <c r="A106" s="38">
         <v>608</v>
       </c>
       <c r="B106" s="14" t="s">
@@ -13162,7 +13217,7 @@
       </c>
     </row>
     <row r="107" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A107" s="14">
+      <c r="A107" s="38">
         <v>573</v>
       </c>
       <c r="B107" s="14" t="s">
@@ -13206,7 +13261,7 @@
       </c>
     </row>
     <row r="108" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A108" s="14">
+      <c r="A108" s="38">
         <v>4919</v>
       </c>
       <c r="B108" s="14" t="s">
@@ -13250,7 +13305,7 @@
       </c>
     </row>
     <row r="109" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A109" s="14">
+      <c r="A109" s="38">
         <v>527</v>
       </c>
       <c r="B109" s="14" t="s">
@@ -13294,7 +13349,7 @@
       </c>
     </row>
     <row r="110" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A110" s="14">
+      <c r="A110" s="38">
         <v>374</v>
       </c>
       <c r="B110" s="14" t="s">
@@ -13344,7 +13399,7 @@
       </c>
     </row>
     <row r="111" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A111" s="14">
+      <c r="A111" s="38">
         <v>287</v>
       </c>
       <c r="B111" s="14" t="s">
@@ -13388,7 +13443,7 @@
       </c>
     </row>
     <row r="112" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A112" s="14">
+      <c r="A112" s="38">
         <v>48</v>
       </c>
       <c r="B112" s="14" t="s">
@@ -13432,7 +13487,7 @@
       </c>
     </row>
     <row r="113" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A113" s="14">
+      <c r="A113" s="38">
         <v>501</v>
       </c>
       <c r="B113" s="14" t="s">
@@ -13476,7 +13531,7 @@
       </c>
     </row>
     <row r="114" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A114" s="14">
+      <c r="A114" s="38">
         <v>430</v>
       </c>
       <c r="B114" s="14" t="s">
@@ -13520,7 +13575,7 @@
       </c>
     </row>
     <row r="115" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A115" s="14">
+      <c r="A115" s="38">
         <v>616</v>
       </c>
       <c r="B115" s="14" t="s">
@@ -13564,7 +13619,7 @@
       </c>
     </row>
     <row r="116" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A116" s="14">
+      <c r="A116" s="38">
         <v>315</v>
       </c>
       <c r="B116" s="14" t="s">
@@ -13608,7 +13663,7 @@
       </c>
     </row>
     <row r="117" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A117" s="14">
+      <c r="A117" s="38">
         <v>265</v>
       </c>
       <c r="B117" s="14" t="s">
@@ -13652,7 +13707,7 @@
       </c>
     </row>
     <row r="118" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A118" s="14">
+      <c r="A118" s="38">
         <v>571</v>
       </c>
       <c r="B118" s="14" t="s">
@@ -13696,7 +13751,7 @@
       </c>
     </row>
     <row r="119" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A119" s="14">
+      <c r="A119" s="38">
         <v>532</v>
       </c>
       <c r="B119" s="14" t="s">
@@ -13740,7 +13795,7 @@
       </c>
     </row>
     <row r="120" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A120" s="14">
+      <c r="A120" s="38">
         <v>312</v>
       </c>
       <c r="B120" s="14" t="s">
@@ -13784,7 +13839,7 @@
       </c>
     </row>
     <row r="121" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A121" s="14">
+      <c r="A121" s="38">
         <v>542</v>
       </c>
       <c r="B121" s="14" t="s">
@@ -13828,7 +13883,7 @@
       </c>
     </row>
     <row r="122" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A122" s="14">
+      <c r="A122" s="38">
         <v>9</v>
       </c>
       <c r="B122" s="14" t="s">
@@ -13872,7 +13927,7 @@
       </c>
     </row>
     <row r="123" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A123" s="14">
+      <c r="A123" s="38">
         <v>97</v>
       </c>
       <c r="B123" s="14" t="s">
@@ -13916,7 +13971,7 @@
       </c>
     </row>
     <row r="124" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A124" s="14">
+      <c r="A124" s="38">
         <v>275</v>
       </c>
       <c r="B124" s="14" t="s">
@@ -13960,7 +14015,7 @@
       </c>
     </row>
     <row r="125" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A125" s="14">
+      <c r="A125" s="38">
         <v>167</v>
       </c>
       <c r="B125" s="14" t="s">
@@ -14004,7 +14059,7 @@
       </c>
     </row>
     <row r="126" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A126" s="14">
+      <c r="A126" s="38">
         <v>536</v>
       </c>
       <c r="B126" s="14" t="s">
@@ -14054,7 +14109,7 @@
       </c>
     </row>
     <row r="127" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A127" s="14">
+      <c r="A127" s="38">
         <v>307</v>
       </c>
       <c r="B127" s="14" t="s">
@@ -14098,7 +14153,7 @@
       </c>
     </row>
     <row r="128" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A128" s="14">
+      <c r="A128" s="38">
         <v>565</v>
       </c>
       <c r="B128" s="14" t="s">
@@ -14142,7 +14197,7 @@
       </c>
     </row>
     <row r="129" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A129" s="14">
+      <c r="A129" s="38">
         <v>3992</v>
       </c>
       <c r="B129" s="14" t="s">
@@ -14186,7 +14241,7 @@
       </c>
     </row>
     <row r="130" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A130" s="14">
+      <c r="A130" s="38">
         <v>171</v>
       </c>
       <c r="B130" s="14" t="s">
@@ -14230,7 +14285,7 @@
       </c>
     </row>
     <row r="131" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A131" s="14">
+      <c r="A131" s="38">
         <v>2473</v>
       </c>
       <c r="B131" s="14" t="s">
@@ -14274,7 +14329,7 @@
       </c>
     </row>
     <row r="132" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A132" s="14">
+      <c r="A132" s="38">
         <v>21</v>
       </c>
       <c r="B132" s="14" t="s">
@@ -14318,7 +14373,7 @@
       </c>
     </row>
     <row r="133" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A133" s="14">
+      <c r="A133" s="38">
         <v>609</v>
       </c>
       <c r="B133" s="14" t="s">
@@ -14362,7 +14417,7 @@
       </c>
     </row>
     <row r="134" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A134" s="14">
+      <c r="A134" s="38">
         <v>5752</v>
       </c>
       <c r="B134" s="14" t="s">
@@ -14406,7 +14461,7 @@
       </c>
     </row>
     <row r="135" spans="1:18" ht="88.5" x14ac:dyDescent="0.35">
-      <c r="A135" s="14">
+      <c r="A135" s="38">
         <v>2551</v>
       </c>
       <c r="B135" s="14" t="s">
@@ -14456,7 +14511,7 @@
       </c>
     </row>
     <row r="136" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A136" s="14">
+      <c r="A136" s="38">
         <v>337</v>
       </c>
       <c r="B136" s="14" t="s">
@@ -14500,7 +14555,7 @@
       </c>
     </row>
     <row r="137" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A137" s="14">
+      <c r="A137" s="38">
         <v>4413</v>
       </c>
       <c r="B137" s="14" t="s">
@@ -14548,7 +14603,7 @@
       </c>
     </row>
     <row r="138" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A138" s="14">
+      <c r="A138" s="38">
         <v>80</v>
       </c>
       <c r="B138" s="14" t="s">
@@ -14592,7 +14647,7 @@
       </c>
     </row>
     <row r="139" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A139" s="14">
+      <c r="A139" s="38">
         <v>398</v>
       </c>
       <c r="B139" s="14" t="s">
@@ -14636,7 +14691,7 @@
       </c>
     </row>
     <row r="140" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A140" s="14">
+      <c r="A140" s="38">
         <v>117</v>
       </c>
       <c r="B140" s="14" t="s">
@@ -14680,7 +14735,7 @@
       </c>
     </row>
     <row r="141" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A141" s="14">
+      <c r="A141" s="38">
         <v>214</v>
       </c>
       <c r="B141" s="14" t="s">
@@ -14724,7 +14779,7 @@
       </c>
     </row>
     <row r="142" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A142" s="14">
+      <c r="A142" s="38">
         <v>405</v>
       </c>
       <c r="B142" s="14" t="s">
@@ -14768,7 +14823,7 @@
       </c>
     </row>
     <row r="143" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A143" s="14">
+      <c r="A143" s="38">
         <v>435</v>
       </c>
       <c r="B143" s="14" t="s">
@@ -14812,7 +14867,7 @@
       </c>
     </row>
     <row r="144" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A144" s="14">
+      <c r="A144" s="38">
         <v>525</v>
       </c>
       <c r="B144" s="14" t="s">
@@ -14856,7 +14911,7 @@
       </c>
     </row>
     <row r="145" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A145" s="14">
+      <c r="A145" s="38">
         <v>497</v>
       </c>
       <c r="B145" s="14" t="s">
@@ -14900,7 +14955,7 @@
       </c>
     </row>
     <row r="146" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A146" s="14">
+      <c r="A146" s="38">
         <v>316</v>
       </c>
       <c r="B146" s="14" t="s">
@@ -14944,7 +14999,7 @@
       </c>
     </row>
     <row r="147" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A147" s="14">
+      <c r="A147" s="38">
         <v>5882</v>
       </c>
       <c r="B147" s="14" t="s">
@@ -14988,7 +15043,7 @@
       </c>
     </row>
     <row r="148" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A148" s="14">
+      <c r="A148" s="38">
         <v>235</v>
       </c>
       <c r="B148" s="14" t="s">
@@ -15032,7 +15087,7 @@
       </c>
     </row>
     <row r="149" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A149" s="14">
+      <c r="A149" s="38">
         <v>3588</v>
       </c>
       <c r="B149" s="14" t="s">
@@ -15076,7 +15131,7 @@
       </c>
     </row>
     <row r="150" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A150" s="14">
+      <c r="A150" s="38">
         <v>4915</v>
       </c>
       <c r="B150" s="14" t="s">
@@ -15120,7 +15175,7 @@
       </c>
     </row>
     <row r="151" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A151" s="14">
+      <c r="A151" s="38">
         <v>5</v>
       </c>
       <c r="B151" s="14" t="s">
@@ -15164,7 +15219,7 @@
       </c>
     </row>
     <row r="152" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A152" s="14">
+      <c r="A152" s="38">
         <v>592</v>
       </c>
       <c r="B152" s="14" t="s">
@@ -15208,7 +15263,7 @@
       </c>
     </row>
     <row r="153" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A153" s="14">
+      <c r="A153" s="38">
         <v>546</v>
       </c>
       <c r="B153" s="14" t="s">
@@ -15252,7 +15307,7 @@
       </c>
     </row>
     <row r="154" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A154" s="14">
+      <c r="A154" s="38">
         <v>256</v>
       </c>
       <c r="B154" s="14" t="s">
@@ -15296,7 +15351,7 @@
       </c>
     </row>
     <row r="155" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A155" s="14">
+      <c r="A155" s="38">
         <v>5692</v>
       </c>
       <c r="B155" s="14" t="s">
@@ -15340,7 +15395,7 @@
       </c>
     </row>
     <row r="156" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A156" s="14">
+      <c r="A156" s="38">
         <v>173</v>
       </c>
       <c r="B156" s="14" t="s">
@@ -15384,7 +15439,7 @@
       </c>
     </row>
     <row r="157" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A157" s="14">
+      <c r="A157" s="38">
         <v>375</v>
       </c>
       <c r="B157" s="14" t="s">
@@ -15432,7 +15487,7 @@
       </c>
     </row>
     <row r="158" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A158" s="14">
+      <c r="A158" s="38">
         <v>4461</v>
       </c>
       <c r="B158" s="14" t="s">
@@ -15476,7 +15531,7 @@
       </c>
     </row>
     <row r="159" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A159" s="14">
+      <c r="A159" s="38">
         <v>247</v>
       </c>
       <c r="B159" s="14" t="s">
@@ -15524,7 +15579,7 @@
       </c>
     </row>
     <row r="160" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A160" s="14">
+      <c r="A160" s="38">
         <v>297</v>
       </c>
       <c r="B160" s="14" t="s">
@@ -15568,7 +15623,7 @@
       </c>
     </row>
     <row r="161" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A161" s="14">
+      <c r="A161" s="38">
         <v>6199</v>
       </c>
       <c r="B161" s="14" t="s">
@@ -15612,7 +15667,7 @@
       </c>
     </row>
     <row r="162" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A162" s="14">
+      <c r="A162" s="38">
         <v>658</v>
       </c>
       <c r="B162" s="14" t="s">
@@ -15662,7 +15717,7 @@
       </c>
     </row>
     <row r="163" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A163" s="14">
+      <c r="A163" s="38">
         <v>131</v>
       </c>
       <c r="B163" s="14" t="s">
@@ -15706,7 +15761,7 @@
       </c>
     </row>
     <row r="164" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A164" s="14">
+      <c r="A164" s="38">
         <v>277</v>
       </c>
       <c r="B164" s="14" t="s">
@@ -15750,7 +15805,7 @@
       </c>
     </row>
     <row r="165" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A165" s="14">
+      <c r="A165" s="38">
         <v>355</v>
       </c>
       <c r="B165" s="14" t="s">
@@ -15794,7 +15849,7 @@
       </c>
     </row>
     <row r="166" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A166" s="14">
+      <c r="A166" s="38">
         <v>57</v>
       </c>
       <c r="B166" s="14" t="s">
@@ -15838,7 +15893,7 @@
       </c>
     </row>
     <row r="167" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A167" s="14">
+      <c r="A167" s="38">
         <v>341</v>
       </c>
       <c r="B167" s="14" t="s">
@@ -15882,7 +15937,7 @@
       </c>
     </row>
     <row r="168" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A168" s="14">
+      <c r="A168" s="38">
         <v>426</v>
       </c>
       <c r="B168" s="14" t="s">
@@ -15926,7 +15981,7 @@
       </c>
     </row>
     <row r="169" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A169" s="14">
+      <c r="A169" s="38">
         <v>498</v>
       </c>
       <c r="B169" s="14" t="s">
@@ -15970,7 +16025,7 @@
       </c>
     </row>
     <row r="170" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A170" s="14">
+      <c r="A170" s="38">
         <v>282</v>
       </c>
       <c r="B170" s="14" t="s">
@@ -16018,7 +16073,7 @@
       </c>
     </row>
     <row r="171" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A171" s="14">
+      <c r="A171" s="38">
         <v>165</v>
       </c>
       <c r="B171" s="14" t="s">
@@ -16062,7 +16117,7 @@
       </c>
     </row>
     <row r="172" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A172" s="14">
+      <c r="A172" s="38">
         <v>348</v>
       </c>
       <c r="B172" s="14" t="s">
@@ -16106,7 +16161,7 @@
       </c>
     </row>
     <row r="173" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A173" s="14">
+      <c r="A173" s="38">
         <v>528</v>
       </c>
       <c r="B173" s="14" t="s">
@@ -16150,7 +16205,7 @@
       </c>
     </row>
     <row r="174" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A174" s="14">
+      <c r="A174" s="38">
         <v>259</v>
       </c>
       <c r="B174" s="14" t="s">
@@ -16194,7 +16249,7 @@
       </c>
     </row>
     <row r="175" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A175" s="14">
+      <c r="A175" s="38">
         <v>132</v>
       </c>
       <c r="B175" s="14" t="s">
@@ -16238,7 +16293,7 @@
       </c>
     </row>
     <row r="176" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A176" s="14">
+      <c r="A176" s="38">
         <v>507</v>
       </c>
       <c r="B176" s="14" t="s">
@@ -16286,7 +16341,7 @@
       </c>
     </row>
     <row r="177" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A177" s="14">
+      <c r="A177" s="38">
         <v>123</v>
       </c>
       <c r="B177" s="14" t="s">
@@ -16330,7 +16385,7 @@
       </c>
     </row>
     <row r="178" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A178" s="14">
+      <c r="A178" s="38">
         <v>112</v>
       </c>
       <c r="B178" s="14" t="s">
@@ -16374,7 +16429,7 @@
       </c>
     </row>
     <row r="179" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A179" s="14">
+      <c r="A179" s="38">
         <v>207</v>
       </c>
       <c r="B179" s="14" t="s">
@@ -16418,7 +16473,7 @@
       </c>
     </row>
     <row r="180" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A180" s="14">
+      <c r="A180" s="38">
         <v>121</v>
       </c>
       <c r="B180" s="14" t="s">
@@ -16462,7 +16517,7 @@
       </c>
     </row>
     <row r="181" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A181" s="14">
+      <c r="A181" s="38">
         <v>322</v>
       </c>
       <c r="B181" s="14" t="s">
@@ -16506,7 +16561,7 @@
       </c>
     </row>
     <row r="182" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A182" s="14">
+      <c r="A182" s="38">
         <v>384</v>
       </c>
       <c r="B182" s="14" t="s">
@@ -16550,7 +16605,7 @@
       </c>
     </row>
     <row r="183" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A183" s="14">
+      <c r="A183" s="38">
         <v>59</v>
       </c>
       <c r="B183" s="14" t="s">
@@ -16594,7 +16649,7 @@
       </c>
     </row>
     <row r="184" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A184" s="14">
+      <c r="A184" s="38">
         <v>327</v>
       </c>
       <c r="B184" s="14" t="s">
@@ -16638,7 +16693,7 @@
       </c>
     </row>
     <row r="185" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A185" s="14">
+      <c r="A185" s="38">
         <v>5599</v>
       </c>
       <c r="B185" s="14" t="s">
@@ -16682,7 +16737,7 @@
       </c>
     </row>
     <row r="186" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A186" s="14">
+      <c r="A186" s="38">
         <v>640</v>
       </c>
       <c r="B186" s="14" t="s">
@@ -16726,7 +16781,7 @@
       </c>
     </row>
     <row r="187" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A187" s="14">
+      <c r="A187" s="38">
         <v>433</v>
       </c>
       <c r="B187" s="14" t="s">
@@ -16770,7 +16825,7 @@
       </c>
     </row>
     <row r="188" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A188" s="14">
+      <c r="A188" s="38">
         <v>622</v>
       </c>
       <c r="B188" s="14" t="s">
@@ -16814,7 +16869,7 @@
       </c>
     </row>
     <row r="189" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A189" s="14">
+      <c r="A189" s="38">
         <v>169</v>
       </c>
       <c r="B189" s="14" t="s">
@@ -16858,7 +16913,7 @@
       </c>
     </row>
     <row r="190" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A190" s="14">
+      <c r="A190" s="38">
         <v>255</v>
       </c>
       <c r="B190" s="14" t="s">
@@ -16906,7 +16961,7 @@
       </c>
     </row>
     <row r="191" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A191" s="14">
+      <c r="A191" s="38">
         <v>499</v>
       </c>
       <c r="B191" s="14" t="s">
@@ -16950,7 +17005,7 @@
       </c>
     </row>
     <row r="192" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A192" s="14">
+      <c r="A192" s="38">
         <v>407</v>
       </c>
       <c r="B192" s="14" t="s">
@@ -16994,7 +17049,7 @@
       </c>
     </row>
     <row r="193" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A193" s="14">
+      <c r="A193" s="38">
         <v>10</v>
       </c>
       <c r="B193" s="14" t="s">
@@ -17038,7 +17093,7 @@
       </c>
     </row>
     <row r="194" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A194" s="14">
+      <c r="A194" s="38">
         <v>522</v>
       </c>
       <c r="B194" s="14" t="s">
@@ -17082,7 +17137,7 @@
       </c>
     </row>
     <row r="195" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A195" s="14">
+      <c r="A195" s="38">
         <v>4148</v>
       </c>
       <c r="B195" s="14" t="s">
@@ -17126,7 +17181,7 @@
       </c>
     </row>
     <row r="196" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A196" s="14">
+      <c r="A196" s="38">
         <v>261</v>
       </c>
       <c r="B196" s="14" t="s">
@@ -17170,7 +17225,7 @@
       </c>
     </row>
     <row r="197" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A197" s="14">
+      <c r="A197" s="38">
         <v>51</v>
       </c>
       <c r="B197" s="14" t="s">
@@ -17214,7 +17269,7 @@
       </c>
     </row>
     <row r="198" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A198" s="14">
+      <c r="A198" s="38">
         <v>443</v>
       </c>
       <c r="B198" s="14" t="s">
@@ -17262,7 +17317,7 @@
       </c>
     </row>
     <row r="199" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A199" s="14">
+      <c r="A199" s="38">
         <v>6</v>
       </c>
       <c r="B199" s="14" t="s">
@@ -17306,7 +17361,7 @@
       </c>
     </row>
     <row r="200" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A200" s="14">
+      <c r="A200" s="38">
         <v>650</v>
       </c>
       <c r="B200" s="14" t="s">
@@ -17350,7 +17405,7 @@
       </c>
     </row>
     <row r="201" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A201" s="14">
+      <c r="A201" s="38">
         <v>4882</v>
       </c>
       <c r="B201" s="14" t="s">
@@ -17394,7 +17449,7 @@
       </c>
     </row>
     <row r="202" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A202" s="14">
+      <c r="A202" s="38">
         <v>625</v>
       </c>
       <c r="B202" s="14" t="s">
@@ -17438,7 +17493,7 @@
       </c>
     </row>
     <row r="203" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A203" s="14">
+      <c r="A203" s="38">
         <v>3809</v>
       </c>
       <c r="B203" s="14" t="s">
@@ -17482,7 +17537,7 @@
       </c>
     </row>
     <row r="204" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A204" s="14">
+      <c r="A204" s="38">
         <v>623</v>
       </c>
       <c r="B204" s="14" t="s">
@@ -17526,7 +17581,7 @@
       </c>
     </row>
     <row r="205" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A205" s="14">
+      <c r="A205" s="38">
         <v>185</v>
       </c>
       <c r="B205" s="14" t="s">
@@ -17570,7 +17625,7 @@
       </c>
     </row>
     <row r="206" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A206" s="14">
+      <c r="A206" s="38">
         <v>1892</v>
       </c>
       <c r="B206" s="14" t="s">
@@ -17614,7 +17669,7 @@
       </c>
     </row>
     <row r="207" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A207" s="14">
+      <c r="A207" s="38">
         <v>600</v>
       </c>
       <c r="B207" s="14" t="s">
@@ -17658,7 +17713,7 @@
       </c>
     </row>
     <row r="208" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A208" s="14">
+      <c r="A208" s="38">
         <v>334</v>
       </c>
       <c r="B208" s="14" t="s">
@@ -17702,7 +17757,7 @@
       </c>
     </row>
     <row r="209" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A209" s="14">
+      <c r="A209" s="38">
         <v>563</v>
       </c>
       <c r="B209" s="14" t="s">
@@ -17746,7 +17801,7 @@
       </c>
     </row>
     <row r="210" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A210" s="14">
+      <c r="A210" s="38">
         <v>3021</v>
       </c>
       <c r="B210" s="14" t="s">
@@ -17790,7 +17845,7 @@
       </c>
     </row>
     <row r="211" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A211" s="14">
+      <c r="A211" s="38">
         <v>183</v>
       </c>
       <c r="B211" s="14" t="s">
@@ -17834,7 +17889,7 @@
       </c>
     </row>
     <row r="212" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A212" s="14">
+      <c r="A212" s="38">
         <v>4149</v>
       </c>
       <c r="B212" s="14" t="s">
@@ -17878,7 +17933,7 @@
       </c>
     </row>
     <row r="213" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A213" s="14">
+      <c r="A213" s="38">
         <v>591</v>
       </c>
       <c r="B213" s="14" t="s">
@@ -17922,7 +17977,7 @@
       </c>
     </row>
     <row r="214" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A214" s="14">
+      <c r="A214" s="38">
         <v>379</v>
       </c>
       <c r="B214" s="14" t="s">
@@ -17966,7 +18021,7 @@
       </c>
     </row>
     <row r="215" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A215" s="14">
+      <c r="A215" s="38">
         <v>366</v>
       </c>
       <c r="B215" s="14" t="s">
@@ -18014,7 +18069,7 @@
       </c>
     </row>
     <row r="216" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A216" s="14">
+      <c r="A216" s="38">
         <v>83</v>
       </c>
       <c r="B216" s="14" t="s">
@@ -18062,7 +18117,7 @@
       </c>
     </row>
     <row r="217" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A217" s="14">
+      <c r="A217" s="38">
         <v>3993</v>
       </c>
       <c r="B217" s="14" t="s">
@@ -18106,7 +18161,7 @@
       </c>
     </row>
     <row r="218" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A218" s="14">
+      <c r="A218" s="38">
         <v>154</v>
       </c>
       <c r="B218" s="14" t="s">
@@ -18150,7 +18205,7 @@
       </c>
     </row>
     <row r="219" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A219" s="14">
+      <c r="A219" s="38">
         <v>49</v>
       </c>
       <c r="B219" s="14" t="s">
@@ -18194,7 +18249,7 @@
       </c>
     </row>
     <row r="220" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A220" s="14">
+      <c r="A220" s="38">
         <v>638</v>
       </c>
       <c r="B220" s="14" t="s">
@@ -18238,7 +18293,7 @@
       </c>
     </row>
     <row r="221" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A221" s="14">
+      <c r="A221" s="38">
         <v>269</v>
       </c>
       <c r="B221" s="14" t="s">
@@ -18282,7 +18337,7 @@
       </c>
     </row>
     <row r="222" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A222" s="14">
+      <c r="A222" s="38">
         <v>65</v>
       </c>
       <c r="B222" s="14" t="s">
@@ -18326,7 +18381,7 @@
       </c>
     </row>
     <row r="223" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A223" s="14">
+      <c r="A223" s="38">
         <v>145</v>
       </c>
       <c r="B223" s="14" t="s">
@@ -18370,7 +18425,7 @@
       </c>
     </row>
     <row r="224" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A224" s="14">
+      <c r="A224" s="38">
         <v>206</v>
       </c>
       <c r="B224" s="14" t="s">
@@ -18414,7 +18469,7 @@
       </c>
     </row>
     <row r="225" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A225" s="14">
+      <c r="A225" s="38">
         <v>318</v>
       </c>
       <c r="B225" s="14" t="s">
@@ -18458,7 +18513,7 @@
       </c>
     </row>
     <row r="226" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A226" s="14">
+      <c r="A226" s="38">
         <v>4916</v>
       </c>
       <c r="B226" s="14" t="s">
@@ -18502,7 +18557,7 @@
       </c>
     </row>
     <row r="227" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A227" s="14">
+      <c r="A227" s="38">
         <v>268</v>
       </c>
       <c r="B227" s="14" t="s">
@@ -18546,7 +18601,7 @@
       </c>
     </row>
     <row r="228" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A228" s="14">
+      <c r="A228" s="38">
         <v>245</v>
       </c>
       <c r="B228" s="14" t="s">
@@ -18594,7 +18649,7 @@
       </c>
     </row>
     <row r="229" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A229" s="14">
+      <c r="A229" s="38">
         <v>13</v>
       </c>
       <c r="B229" s="14" t="s">
@@ -18638,7 +18693,7 @@
       </c>
     </row>
     <row r="230" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A230" s="14">
+      <c r="A230" s="38">
         <v>321</v>
       </c>
       <c r="B230" s="14" t="s">
@@ -18682,7 +18737,7 @@
       </c>
     </row>
     <row r="231" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A231" s="14">
+      <c r="A231" s="38">
         <v>202</v>
       </c>
       <c r="B231" s="14" t="s">
@@ -18726,7 +18781,7 @@
       </c>
     </row>
     <row r="232" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A232" s="14">
+      <c r="A232" s="38">
         <v>134</v>
       </c>
       <c r="B232" s="14" t="s">
@@ -18770,7 +18825,7 @@
       </c>
     </row>
     <row r="233" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A233" s="14">
+      <c r="A233" s="38">
         <v>377</v>
       </c>
       <c r="B233" s="14" t="s">
@@ -18814,7 +18869,7 @@
       </c>
     </row>
     <row r="234" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A234" s="14">
+      <c r="A234" s="38">
         <v>166</v>
       </c>
       <c r="B234" s="14" t="s">
@@ -18858,7 +18913,7 @@
       </c>
     </row>
     <row r="235" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A235" s="14">
+      <c r="A235" s="38">
         <v>382</v>
       </c>
       <c r="B235" s="14" t="s">
@@ -18902,7 +18957,7 @@
       </c>
     </row>
     <row r="236" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A236" s="14">
+      <c r="A236" s="38">
         <v>511</v>
       </c>
       <c r="B236" s="14" t="s">
@@ -18946,7 +19001,7 @@
       </c>
     </row>
     <row r="237" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A237" s="14">
+      <c r="A237" s="38">
         <v>347</v>
       </c>
       <c r="B237" s="14" t="s">
@@ -18990,7 +19045,7 @@
       </c>
     </row>
     <row r="238" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A238" s="14">
+      <c r="A238" s="38">
         <v>8</v>
       </c>
       <c r="B238" s="14" t="s">
@@ -19034,7 +19089,7 @@
       </c>
     </row>
     <row r="239" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A239" s="14">
+      <c r="A239" s="38">
         <v>101</v>
       </c>
       <c r="B239" s="14" t="s">
@@ -19078,7 +19133,7 @@
       </c>
     </row>
     <row r="240" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A240" s="14">
+      <c r="A240" s="38">
         <v>143</v>
       </c>
       <c r="B240" s="14" t="s">
@@ -19122,7 +19177,7 @@
       </c>
     </row>
     <row r="241" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A241" s="14">
+      <c r="A241" s="38">
         <v>412</v>
       </c>
       <c r="B241" s="14" t="s">
@@ -19166,7 +19221,7 @@
       </c>
     </row>
     <row r="242" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A242" s="14">
+      <c r="A242" s="38">
         <v>352</v>
       </c>
       <c r="B242" s="14" t="s">
@@ -19210,7 +19265,7 @@
       </c>
     </row>
     <row r="243" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A243" s="14">
+      <c r="A243" s="38">
         <v>209</v>
       </c>
       <c r="B243" s="14" t="s">
@@ -19254,7 +19309,7 @@
       </c>
     </row>
     <row r="244" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A244" s="14">
+      <c r="A244" s="38">
         <v>578</v>
       </c>
       <c r="B244" s="14" t="s">
@@ -19298,7 +19353,7 @@
       </c>
     </row>
     <row r="245" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A245" s="14">
+      <c r="A245" s="38">
         <v>257</v>
       </c>
       <c r="B245" s="14" t="s">
@@ -19342,7 +19397,7 @@
       </c>
     </row>
     <row r="246" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A246" s="14">
+      <c r="A246" s="38">
         <v>624</v>
       </c>
       <c r="B246" s="14" t="s">
@@ -19386,7 +19441,7 @@
       </c>
     </row>
     <row r="247" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A247" s="14">
+      <c r="A247" s="38">
         <v>320</v>
       </c>
       <c r="B247" s="14" t="s">
@@ -19430,7 +19485,7 @@
       </c>
     </row>
     <row r="248" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A248" s="14">
+      <c r="A248" s="38">
         <v>370</v>
       </c>
       <c r="B248" s="14" t="s">
@@ -19478,7 +19533,7 @@
       </c>
     </row>
     <row r="249" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A249" s="14">
+      <c r="A249" s="38">
         <v>484</v>
       </c>
       <c r="B249" s="14" t="s">
@@ -19522,7 +19577,7 @@
       </c>
     </row>
     <row r="250" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A250" s="14">
+      <c r="A250" s="38">
         <v>451</v>
       </c>
       <c r="B250" s="14" t="s">
@@ -19566,7 +19621,7 @@
       </c>
     </row>
     <row r="251" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A251" s="14">
+      <c r="A251" s="38">
         <v>162</v>
       </c>
       <c r="B251" s="14" t="s">
@@ -19610,7 +19665,7 @@
       </c>
     </row>
     <row r="252" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A252" s="14">
+      <c r="A252" s="38">
         <v>558</v>
       </c>
       <c r="B252" s="14" t="s">
@@ -19654,7 +19709,7 @@
       </c>
     </row>
     <row r="253" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A253" s="14">
+      <c r="A253" s="38">
         <v>467</v>
       </c>
       <c r="B253" s="14" t="s">
@@ -19698,7 +19753,7 @@
       </c>
     </row>
     <row r="254" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A254" s="14">
+      <c r="A254" s="38">
         <v>3807</v>
       </c>
       <c r="B254" s="14" t="s">
@@ -19742,7 +19797,7 @@
       </c>
     </row>
     <row r="255" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A255" s="14">
+      <c r="A255" s="38">
         <v>99</v>
       </c>
       <c r="B255" s="14" t="s">
@@ -19786,7 +19841,7 @@
       </c>
     </row>
     <row r="256" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A256" s="14">
+      <c r="A256" s="38">
         <v>555</v>
       </c>
       <c r="B256" s="14" t="s">
@@ -19830,7 +19885,7 @@
       </c>
     </row>
     <row r="257" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A257" s="14">
+      <c r="A257" s="38">
         <v>2874</v>
       </c>
       <c r="B257" s="14" t="s">
@@ -19874,7 +19929,7 @@
       </c>
     </row>
     <row r="258" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A258" s="14">
+      <c r="A258" s="38">
         <v>491</v>
       </c>
       <c r="B258" s="14" t="s">
@@ -19918,7 +19973,7 @@
       </c>
     </row>
     <row r="259" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A259" s="14">
+      <c r="A259" s="38">
         <v>335</v>
       </c>
       <c r="B259" s="14" t="s">
@@ -19962,7 +20017,7 @@
       </c>
     </row>
     <row r="260" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A260" s="14">
+      <c r="A260" s="38">
         <v>3812</v>
       </c>
       <c r="B260" s="14" t="s">
@@ -20006,7 +20061,7 @@
       </c>
     </row>
     <row r="261" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A261" s="14">
+      <c r="A261" s="38">
         <v>208</v>
       </c>
       <c r="B261" s="14" t="s">
@@ -20050,7 +20105,7 @@
       </c>
     </row>
     <row r="262" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A262" s="14">
+      <c r="A262" s="38">
         <v>127</v>
       </c>
       <c r="B262" s="14" t="s">
@@ -20094,7 +20149,7 @@
       </c>
     </row>
     <row r="263" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A263" s="14">
+      <c r="A263" s="38">
         <v>612</v>
       </c>
       <c r="B263" s="14" t="s">
@@ -20138,7 +20193,7 @@
       </c>
     </row>
     <row r="264" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A264" s="14">
+      <c r="A264" s="38">
         <v>204</v>
       </c>
       <c r="B264" s="14" t="s">
@@ -20182,7 +20237,7 @@
       </c>
     </row>
     <row r="265" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A265" s="14">
+      <c r="A265" s="38">
         <v>404</v>
       </c>
       <c r="B265" s="14" t="s">
@@ -20226,7 +20281,7 @@
       </c>
     </row>
     <row r="266" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A266" s="14">
+      <c r="A266" s="38">
         <v>236</v>
       </c>
       <c r="B266" s="14" t="s">
@@ -20270,7 +20325,7 @@
       </c>
     </row>
     <row r="267" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A267" s="14">
+      <c r="A267" s="38">
         <v>436</v>
       </c>
       <c r="B267" s="14" t="s">
@@ -20314,7 +20369,7 @@
       </c>
     </row>
     <row r="268" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A268" s="14">
+      <c r="A268" s="38">
         <v>221</v>
       </c>
       <c r="B268" s="14" t="s">
@@ -20358,7 +20413,7 @@
       </c>
     </row>
     <row r="269" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A269" s="14">
+      <c r="A269" s="38">
         <v>635</v>
       </c>
       <c r="B269" s="14" t="s">
@@ -20402,7 +20457,7 @@
       </c>
     </row>
     <row r="270" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A270" s="14">
+      <c r="A270" s="38">
         <v>6467</v>
       </c>
       <c r="B270" s="14" t="s">
@@ -20446,7 +20501,7 @@
       </c>
     </row>
     <row r="271" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A271" s="14">
+      <c r="A271" s="38">
         <v>84</v>
       </c>
       <c r="B271" s="14" t="s">
@@ -20494,7 +20549,7 @@
       </c>
     </row>
     <row r="272" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A272" s="14">
+      <c r="A272" s="38">
         <v>331</v>
       </c>
       <c r="B272" s="14" t="s">
@@ -20538,7 +20593,7 @@
       </c>
     </row>
     <row r="273" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A273" s="14">
+      <c r="A273" s="38">
         <v>415</v>
       </c>
       <c r="B273" s="14" t="s">
@@ -20582,7 +20637,7 @@
       </c>
     </row>
     <row r="274" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A274" s="14">
+      <c r="A274" s="38">
         <v>629</v>
       </c>
       <c r="B274" s="14" t="s">
@@ -20626,7 +20681,7 @@
       </c>
     </row>
     <row r="275" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A275" s="14">
+      <c r="A275" s="38">
         <v>4913</v>
       </c>
       <c r="B275" s="14" t="s">
@@ -20670,7 +20725,7 @@
       </c>
     </row>
     <row r="276" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A276" s="14">
+      <c r="A276" s="38">
         <v>126</v>
       </c>
       <c r="B276" s="14" t="s">
@@ -20714,7 +20769,7 @@
       </c>
     </row>
     <row r="277" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A277" s="14">
+      <c r="A277" s="38">
         <v>120</v>
       </c>
       <c r="B277" s="14" t="s">
@@ -20758,7 +20813,7 @@
       </c>
     </row>
     <row r="278" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A278" s="14">
+      <c r="A278" s="38">
         <v>72</v>
       </c>
       <c r="B278" s="14" t="s">
@@ -20802,7 +20857,7 @@
       </c>
     </row>
     <row r="279" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A279" s="14">
+      <c r="A279" s="38">
         <v>470</v>
       </c>
       <c r="B279" s="14" t="s">
@@ -20846,7 +20901,7 @@
       </c>
     </row>
     <row r="280" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A280" s="14">
+      <c r="A280" s="38">
         <v>122</v>
       </c>
       <c r="B280" s="14" t="s">
@@ -20890,7 +20945,7 @@
       </c>
     </row>
     <row r="281" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A281" s="14">
+      <c r="A281" s="38">
         <v>114</v>
       </c>
       <c r="B281" s="14" t="s">
@@ -20934,7 +20989,7 @@
       </c>
     </row>
     <row r="282" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A282" s="14">
+      <c r="A282" s="38">
         <v>442</v>
       </c>
       <c r="B282" s="14" t="s">
@@ -20982,7 +21037,7 @@
       </c>
     </row>
     <row r="283" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A283" s="14">
+      <c r="A283" s="38">
         <v>281</v>
       </c>
       <c r="B283" s="14" t="s">
@@ -21030,7 +21085,7 @@
       </c>
     </row>
     <row r="284" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A284" s="14">
+      <c r="A284" s="38">
         <v>452</v>
       </c>
       <c r="B284" s="14" t="s">
@@ -21074,7 +21129,7 @@
       </c>
     </row>
     <row r="285" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A285" s="14">
+      <c r="A285" s="38">
         <v>521</v>
       </c>
       <c r="B285" s="14" t="s">
@@ -21118,7 +21173,7 @@
       </c>
     </row>
     <row r="286" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A286" s="14">
+      <c r="A286" s="38">
         <v>130</v>
       </c>
       <c r="B286" s="14" t="s">
@@ -21162,7 +21217,7 @@
       </c>
     </row>
     <row r="287" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A287" s="14">
+      <c r="A287" s="38">
         <v>5684</v>
       </c>
       <c r="B287" s="14" t="s">
@@ -21206,7 +21261,7 @@
       </c>
     </row>
     <row r="288" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A288" s="14">
+      <c r="A288" s="38">
         <v>300</v>
       </c>
       <c r="B288" s="14" t="s">
@@ -21250,7 +21305,7 @@
       </c>
     </row>
     <row r="289" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A289" s="14">
+      <c r="A289" s="38">
         <v>296</v>
       </c>
       <c r="B289" s="14" t="s">
@@ -21294,7 +21349,7 @@
       </c>
     </row>
     <row r="290" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A290" s="14">
+      <c r="A290" s="38">
         <v>24</v>
       </c>
       <c r="B290" s="14" t="s">
@@ -21338,7 +21393,7 @@
       </c>
     </row>
     <row r="291" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A291" s="14">
+      <c r="A291" s="38">
         <v>264</v>
       </c>
       <c r="B291" s="14" t="s">
@@ -21386,7 +21441,7 @@
       </c>
     </row>
     <row r="292" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A292" s="14">
+      <c r="A292" s="38">
         <v>493</v>
       </c>
       <c r="B292" s="14" t="s">
@@ -21430,7 +21485,7 @@
       </c>
     </row>
     <row r="293" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A293" s="14">
+      <c r="A293" s="38">
         <v>3571</v>
       </c>
       <c r="B293" s="14" t="s">
@@ -21474,7 +21529,7 @@
       </c>
     </row>
     <row r="294" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A294" s="14">
+      <c r="A294" s="38">
         <v>468</v>
       </c>
       <c r="B294" s="14" t="s">
@@ -21518,7 +21573,7 @@
       </c>
     </row>
     <row r="295" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A295" s="14">
+      <c r="A295" s="38">
         <v>353</v>
       </c>
       <c r="B295" s="14" t="s">
@@ -21562,7 +21617,7 @@
       </c>
     </row>
     <row r="296" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A296" s="14">
+      <c r="A296" s="38">
         <v>556</v>
       </c>
       <c r="B296" s="14" t="s">
@@ -21606,7 +21661,7 @@
       </c>
     </row>
     <row r="297" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A297" s="14">
+      <c r="A297" s="38">
         <v>4917</v>
       </c>
       <c r="B297" s="14" t="s">
@@ -21650,7 +21705,7 @@
       </c>
     </row>
     <row r="298" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A298" s="14">
+      <c r="A298" s="38">
         <v>5042</v>
       </c>
       <c r="B298" s="14" t="s">
@@ -21694,7 +21749,7 @@
       </c>
     </row>
     <row r="299" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A299" s="14">
+      <c r="A299" s="38">
         <v>453</v>
       </c>
       <c r="B299" s="14" t="s">
@@ -21738,7 +21793,7 @@
       </c>
     </row>
     <row r="300" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A300" s="14">
+      <c r="A300" s="38">
         <v>5839</v>
       </c>
       <c r="B300" s="14" t="s">
@@ -21782,7 +21837,7 @@
       </c>
     </row>
     <row r="301" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A301" s="14">
+      <c r="A301" s="38">
         <v>5683</v>
       </c>
       <c r="B301" s="14" t="s">
@@ -21826,7 +21881,7 @@
       </c>
     </row>
     <row r="302" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A302" s="14">
+      <c r="A302" s="38">
         <v>196</v>
       </c>
       <c r="B302" s="14" t="s">
@@ -21870,7 +21925,7 @@
       </c>
     </row>
     <row r="303" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A303" s="14">
+      <c r="A303" s="38">
         <v>137</v>
       </c>
       <c r="B303" s="14" t="s">
@@ -21914,7 +21969,7 @@
       </c>
     </row>
     <row r="304" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A304" s="14">
+      <c r="A304" s="38">
         <v>295</v>
       </c>
       <c r="B304" s="14" t="s">
@@ -21958,7 +22013,7 @@
       </c>
     </row>
     <row r="305" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A305" s="14">
+      <c r="A305" s="38">
         <v>223</v>
       </c>
       <c r="B305" s="14" t="s">
@@ -22002,7 +22057,7 @@
       </c>
     </row>
     <row r="306" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A306" s="14">
+      <c r="A306" s="38">
         <v>4</v>
       </c>
       <c r="B306" s="14" t="s">
@@ -22046,7 +22101,7 @@
       </c>
     </row>
     <row r="307" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A307" s="14">
+      <c r="A307" s="38">
         <v>319</v>
       </c>
       <c r="B307" s="14" t="s">
@@ -22090,7 +22145,7 @@
       </c>
     </row>
     <row r="308" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A308" s="14">
+      <c r="A308" s="38">
         <v>494</v>
       </c>
       <c r="B308" s="14" t="s">
@@ -22134,7 +22189,7 @@
       </c>
     </row>
     <row r="309" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A309" s="14">
+      <c r="A309" s="38">
         <v>5965</v>
       </c>
       <c r="B309" s="14" t="s">
@@ -22178,7 +22233,7 @@
       </c>
     </row>
     <row r="310" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A310" s="14">
+      <c r="A310" s="38">
         <v>4611</v>
       </c>
       <c r="B310" s="14" t="s">
@@ -22222,7 +22277,7 @@
       </c>
     </row>
     <row r="311" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A311" s="14">
+      <c r="A311" s="38">
         <v>606</v>
       </c>
       <c r="B311" s="14" t="s">
@@ -22266,7 +22321,7 @@
       </c>
     </row>
     <row r="312" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A312" s="14">
+      <c r="A312" s="38">
         <v>216</v>
       </c>
       <c r="B312" s="14" t="s">
@@ -22310,7 +22365,7 @@
       </c>
     </row>
     <row r="313" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A313" s="14">
+      <c r="A313" s="38">
         <v>94</v>
       </c>
       <c r="B313" s="14" t="s">
@@ -22354,7 +22409,7 @@
       </c>
     </row>
     <row r="314" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A314" s="14">
+      <c r="A314" s="38">
         <v>6545</v>
       </c>
       <c r="B314" s="14" t="s">
@@ -22398,7 +22453,7 @@
       </c>
     </row>
     <row r="315" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A315" s="14">
+      <c r="A315" s="38">
         <v>356</v>
       </c>
       <c r="B315" s="14" t="s">
@@ -22442,7 +22497,7 @@
       </c>
     </row>
     <row r="316" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A316" s="14">
+      <c r="A316" s="38">
         <v>438</v>
       </c>
       <c r="B316" s="14" t="s">
@@ -22490,7 +22545,7 @@
       </c>
     </row>
     <row r="317" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A317" s="14">
+      <c r="A317" s="38">
         <v>164</v>
       </c>
       <c r="B317" s="14" t="s">
@@ -22534,7 +22589,7 @@
       </c>
     </row>
     <row r="318" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A318" s="14">
+      <c r="A318" s="38">
         <v>3</v>
       </c>
       <c r="B318" s="14" t="s">
@@ -22578,7 +22633,7 @@
       </c>
     </row>
     <row r="319" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A319" s="14">
+      <c r="A319" s="38">
         <v>6446</v>
       </c>
       <c r="B319" s="14" t="s">
@@ -22622,7 +22677,7 @@
       </c>
     </row>
     <row r="320" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A320" s="14">
+      <c r="A320" s="38">
         <v>529</v>
       </c>
       <c r="B320" s="14" t="s">
@@ -22666,7 +22721,7 @@
       </c>
     </row>
     <row r="321" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A321" s="14">
+      <c r="A321" s="38">
         <v>596</v>
       </c>
       <c r="B321" s="14" t="s">
@@ -22710,7 +22765,7 @@
       </c>
     </row>
     <row r="322" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A322" s="14">
+      <c r="A322" s="38">
         <v>98</v>
       </c>
       <c r="B322" s="14" t="s">
@@ -22754,7 +22809,7 @@
       </c>
     </row>
     <row r="323" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A323" s="14">
+      <c r="A323" s="38">
         <v>537</v>
       </c>
       <c r="B323" s="14" t="s">
@@ -22802,7 +22857,7 @@
       </c>
     </row>
     <row r="324" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A324" s="14">
+      <c r="A324" s="38">
         <v>5049</v>
       </c>
       <c r="B324" s="14" t="s">
@@ -22846,7 +22901,7 @@
       </c>
     </row>
     <row r="325" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A325" s="14">
+      <c r="A325" s="38">
         <v>3810</v>
       </c>
       <c r="B325" s="14" t="s">
@@ -22890,7 +22945,7 @@
       </c>
     </row>
     <row r="326" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A326" s="14">
+      <c r="A326" s="38">
         <v>6031</v>
       </c>
       <c r="B326" s="14" t="s">
@@ -22934,7 +22989,7 @@
       </c>
     </row>
     <row r="327" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A327" s="14">
+      <c r="A327" s="38">
         <v>339</v>
       </c>
       <c r="B327" s="14" t="s">
@@ -22978,7 +23033,7 @@
       </c>
     </row>
     <row r="328" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A328" s="14">
+      <c r="A328" s="38">
         <v>330</v>
       </c>
       <c r="B328" s="14" t="s">
@@ -23022,7 +23077,7 @@
       </c>
     </row>
     <row r="329" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A329" s="14">
+      <c r="A329" s="38">
         <v>351</v>
       </c>
       <c r="B329" s="14" t="s">
@@ -23066,7 +23121,7 @@
       </c>
     </row>
     <row r="330" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A330" s="14">
+      <c r="A330" s="38">
         <v>346</v>
       </c>
       <c r="B330" s="14" t="s">
@@ -23110,7 +23165,7 @@
       </c>
     </row>
     <row r="331" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A331" s="14">
+      <c r="A331" s="38">
         <v>184</v>
       </c>
       <c r="B331" s="14" t="s">
@@ -23154,7 +23209,7 @@
       </c>
     </row>
     <row r="332" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A332" s="14">
+      <c r="A332" s="38">
         <v>53</v>
       </c>
       <c r="B332" s="14" t="s">
@@ -23198,7 +23253,7 @@
       </c>
     </row>
     <row r="333" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A333" s="14">
+      <c r="A333" s="38">
         <v>423</v>
       </c>
       <c r="B333" s="14" t="s">
@@ -23242,7 +23297,7 @@
       </c>
     </row>
     <row r="334" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A334" s="14">
+      <c r="A334" s="38">
         <v>413</v>
       </c>
       <c r="B334" s="14" t="s">
@@ -23286,7 +23341,7 @@
       </c>
     </row>
     <row r="335" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A335" s="14">
+      <c r="A335" s="38">
         <v>560</v>
       </c>
       <c r="B335" s="14" t="s">
@@ -23330,7 +23385,7 @@
       </c>
     </row>
     <row r="336" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A336" s="14">
+      <c r="A336" s="38">
         <v>575</v>
       </c>
       <c r="B336" s="14" t="s">
@@ -23374,7 +23429,7 @@
       </c>
     </row>
     <row r="337" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A337" s="14">
+      <c r="A337" s="38">
         <v>566</v>
       </c>
       <c r="B337" s="14" t="s">
@@ -23418,7 +23473,7 @@
       </c>
     </row>
     <row r="338" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A338" s="14">
+      <c r="A338" s="38">
         <v>75</v>
       </c>
       <c r="B338" s="14" t="s">
@@ -23462,7 +23517,7 @@
       </c>
     </row>
     <row r="339" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A339" s="14">
+      <c r="A339" s="38">
         <v>149</v>
       </c>
       <c r="B339" s="14" t="s">
@@ -23506,7 +23561,7 @@
       </c>
     </row>
     <row r="340" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A340" s="14">
+      <c r="A340" s="38">
         <v>222</v>
       </c>
       <c r="B340" s="14" t="s">
@@ -23550,7 +23605,7 @@
       </c>
     </row>
     <row r="341" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A341" s="14">
+      <c r="A341" s="38">
         <v>378</v>
       </c>
       <c r="B341" s="14" t="s">
@@ -23594,7 +23649,7 @@
       </c>
     </row>
     <row r="342" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A342" s="14">
+      <c r="A342" s="38">
         <v>3504</v>
       </c>
       <c r="B342" s="14" t="s">
@@ -23638,7 +23693,7 @@
       </c>
     </row>
     <row r="343" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A343" s="14">
+      <c r="A343" s="38">
         <v>92</v>
       </c>
       <c r="B343" s="14" t="s">
@@ -23682,7 +23737,7 @@
       </c>
     </row>
     <row r="344" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A344" s="14">
+      <c r="A344" s="38">
         <v>512</v>
       </c>
       <c r="B344" s="14" t="s">
@@ -23726,7 +23781,7 @@
       </c>
     </row>
     <row r="345" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A345" s="14">
+      <c r="A345" s="38">
         <v>613</v>
       </c>
       <c r="B345" s="14" t="s">
@@ -23770,7 +23825,7 @@
       </c>
     </row>
     <row r="346" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A346" s="14">
+      <c r="A346" s="38">
         <v>634</v>
       </c>
       <c r="B346" s="14" t="s">
@@ -23814,7 +23869,7 @@
       </c>
     </row>
     <row r="347" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A347" s="14">
+      <c r="A347" s="38">
         <v>107</v>
       </c>
       <c r="B347" s="14" t="s">
@@ -23858,7 +23913,7 @@
       </c>
     </row>
     <row r="348" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A348" s="14">
+      <c r="A348" s="38">
         <v>380</v>
       </c>
       <c r="B348" s="14" t="s">
@@ -23902,7 +23957,7 @@
       </c>
     </row>
     <row r="349" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A349" s="14">
+      <c r="A349" s="38">
         <v>194</v>
       </c>
       <c r="B349" s="14" t="s">
@@ -23946,7 +24001,7 @@
       </c>
     </row>
     <row r="350" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A350" s="14">
+      <c r="A350" s="38">
         <v>478</v>
       </c>
       <c r="B350" s="14" t="s">
@@ -23990,7 +24045,7 @@
       </c>
     </row>
     <row r="351" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A351" s="14">
+      <c r="A351" s="38">
         <v>105</v>
       </c>
       <c r="B351" s="14" t="s">
@@ -24034,7 +24089,7 @@
       </c>
     </row>
     <row r="352" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A352" s="14">
+      <c r="A352" s="38">
         <v>4702</v>
       </c>
       <c r="B352" s="14" t="s">
@@ -24078,7 +24133,7 @@
       </c>
     </row>
     <row r="353" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A353" s="14">
+      <c r="A353" s="38">
         <v>544</v>
       </c>
       <c r="B353" s="14" t="s">
@@ -24122,7 +24177,7 @@
       </c>
     </row>
     <row r="354" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A354" s="14">
+      <c r="A354" s="38">
         <v>548</v>
       </c>
       <c r="B354" s="14" t="s">
@@ -24166,7 +24221,7 @@
       </c>
     </row>
     <row r="355" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A355" s="14">
+      <c r="A355" s="38">
         <v>598</v>
       </c>
       <c r="B355" s="14" t="s">
@@ -24210,7 +24265,7 @@
       </c>
     </row>
     <row r="356" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A356" s="14">
+      <c r="A356" s="38">
         <v>325</v>
       </c>
       <c r="B356" s="14" t="s">
@@ -24254,7 +24309,7 @@
       </c>
     </row>
     <row r="357" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A357" s="14">
+      <c r="A357" s="38">
         <v>195</v>
       </c>
       <c r="B357" s="14" t="s">
@@ -24298,7 +24353,7 @@
       </c>
     </row>
     <row r="358" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A358" s="14">
+      <c r="A358" s="38">
         <v>78</v>
       </c>
       <c r="B358" s="14" t="s">
@@ -24342,7 +24397,7 @@
       </c>
     </row>
     <row r="359" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A359" s="14">
+      <c r="A359" s="38">
         <v>655</v>
       </c>
       <c r="B359" s="14" t="s">
@@ -24392,7 +24447,7 @@
       </c>
     </row>
     <row r="360" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A360" s="14">
+      <c r="A360" s="38">
         <v>4948</v>
       </c>
       <c r="B360" s="14" t="s">
@@ -24436,7 +24491,7 @@
       </c>
     </row>
     <row r="361" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A361" s="14">
+      <c r="A361" s="38">
         <v>203</v>
       </c>
       <c r="B361" s="14" t="s">
@@ -24480,7 +24535,7 @@
       </c>
     </row>
     <row r="362" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A362" s="14">
+      <c r="A362" s="38">
         <v>2848</v>
       </c>
       <c r="B362" s="14" t="s">
@@ -24524,7 +24579,7 @@
       </c>
     </row>
     <row r="363" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A363" s="14">
+      <c r="A363" s="38">
         <v>618</v>
       </c>
       <c r="B363" s="14" t="s">
@@ -24568,7 +24623,7 @@
       </c>
     </row>
     <row r="364" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A364" s="14">
+      <c r="A364" s="38">
         <v>615</v>
       </c>
       <c r="B364" s="14" t="s">
@@ -24612,7 +24667,7 @@
       </c>
     </row>
     <row r="365" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A365" s="14">
+      <c r="A365" s="38">
         <v>524</v>
       </c>
       <c r="B365" s="14" t="s">
@@ -24656,7 +24711,7 @@
       </c>
     </row>
     <row r="366" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A366" s="14">
+      <c r="A366" s="38">
         <v>4399</v>
       </c>
       <c r="B366" s="14" t="s">
@@ -24700,7 +24755,7 @@
       </c>
     </row>
     <row r="367" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A367" s="14">
+      <c r="A367" s="38">
         <v>160</v>
       </c>
       <c r="B367" s="14" t="s">
@@ -24744,7 +24799,7 @@
       </c>
     </row>
     <row r="368" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A368" s="14">
+      <c r="A368" s="38">
         <v>4414</v>
       </c>
       <c r="B368" s="14" t="s">
@@ -24788,7 +24843,7 @@
       </c>
     </row>
     <row r="369" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A369" s="14">
+      <c r="A369" s="38">
         <v>6105</v>
       </c>
       <c r="B369" s="14" t="s">
@@ -24832,7 +24887,7 @@
       </c>
     </row>
     <row r="370" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A370" s="14">
+      <c r="A370" s="38">
         <v>4406</v>
       </c>
       <c r="B370" s="14" t="s">
@@ -24880,7 +24935,7 @@
       </c>
     </row>
     <row r="371" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A371" s="14">
+      <c r="A371" s="38">
         <v>5595</v>
       </c>
       <c r="B371" s="14" t="s">
@@ -24924,7 +24979,7 @@
       </c>
     </row>
     <row r="372" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A372" s="14">
+      <c r="A372" s="38">
         <v>559</v>
       </c>
       <c r="B372" s="14" t="s">
@@ -24968,7 +25023,7 @@
       </c>
     </row>
     <row r="373" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A373" s="14">
+      <c r="A373" s="38">
         <v>4918</v>
       </c>
       <c r="B373" s="14" t="s">
@@ -25012,7 +25067,7 @@
       </c>
     </row>
     <row r="374" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A374" s="14">
+      <c r="A374" s="38">
         <v>431</v>
       </c>
       <c r="B374" s="14" t="s">
@@ -25060,7 +25115,7 @@
       </c>
     </row>
     <row r="375" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A375" s="14">
+      <c r="A375" s="38">
         <v>4701</v>
       </c>
       <c r="B375" s="14" t="s">
@@ -25104,7 +25159,7 @@
       </c>
     </row>
     <row r="376" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A376" s="14">
+      <c r="A376" s="38">
         <v>113</v>
       </c>
       <c r="B376" s="14" t="s">
@@ -25148,7 +25203,7 @@
       </c>
     </row>
     <row r="377" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A377" s="14">
+      <c r="A377" s="38">
         <v>104</v>
       </c>
       <c r="B377" s="14" t="s">
@@ -25192,7 +25247,7 @@
       </c>
     </row>
     <row r="378" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A378" s="14">
+      <c r="A378" s="38">
         <v>6440</v>
       </c>
       <c r="B378" s="14" t="s">
@@ -25236,7 +25291,7 @@
       </c>
     </row>
     <row r="379" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A379" s="14">
+      <c r="A379" s="38">
         <v>111</v>
       </c>
       <c r="B379" s="14" t="s">
@@ -25280,7 +25335,7 @@
       </c>
     </row>
     <row r="380" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A380" s="14">
+      <c r="A380" s="38">
         <v>5932</v>
       </c>
       <c r="B380" s="14" t="s">
@@ -25324,7 +25379,7 @@
       </c>
     </row>
     <row r="381" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A381" s="14">
+      <c r="A381" s="38">
         <v>306</v>
       </c>
       <c r="B381" s="14" t="s">
@@ -25368,7 +25423,7 @@
       </c>
     </row>
     <row r="382" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A382" s="14">
+      <c r="A382" s="38">
         <v>212</v>
       </c>
       <c r="B382" s="14" t="s">
@@ -25412,7 +25467,7 @@
       </c>
     </row>
     <row r="383" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A383" s="14">
+      <c r="A383" s="38">
         <v>2632</v>
       </c>
       <c r="B383" s="14" t="s">
@@ -25456,7 +25511,7 @@
       </c>
     </row>
     <row r="384" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A384" s="14">
+      <c r="A384" s="38">
         <v>280</v>
       </c>
       <c r="B384" s="14" t="s">
@@ -25500,7 +25555,7 @@
       </c>
     </row>
     <row r="385" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A385" s="14">
+      <c r="A385" s="38">
         <v>170</v>
       </c>
       <c r="B385" s="14" t="s">
@@ -25544,7 +25599,7 @@
       </c>
     </row>
     <row r="386" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A386" s="14">
+      <c r="A386" s="38">
         <v>1536</v>
       </c>
       <c r="B386" s="14" t="s">
@@ -25594,7 +25649,7 @@
       </c>
     </row>
     <row r="387" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A387" s="14">
+      <c r="A387" s="38">
         <v>200</v>
       </c>
       <c r="B387" s="14" t="s">
@@ -25638,7 +25693,7 @@
       </c>
     </row>
     <row r="388" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A388" s="14">
+      <c r="A388" s="38">
         <v>82</v>
       </c>
       <c r="B388" s="14" t="s">
@@ -25686,7 +25741,7 @@
       </c>
     </row>
     <row r="389" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A389" s="14">
+      <c r="A389" s="38">
         <v>4401</v>
       </c>
       <c r="B389" s="14" t="s">
@@ -25730,7 +25785,7 @@
       </c>
     </row>
     <row r="390" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A390" s="14">
+      <c r="A390" s="38">
         <v>6304</v>
       </c>
       <c r="B390" s="14" t="s">
@@ -25774,7 +25829,7 @@
       </c>
     </row>
     <row r="391" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A391" s="14">
+      <c r="A391" s="38">
         <v>5490</v>
       </c>
       <c r="B391" s="14" t="s">
@@ -25818,7 +25873,7 @@
       </c>
     </row>
     <row r="392" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A392" s="14">
+      <c r="A392" s="38">
         <v>182</v>
       </c>
       <c r="B392" s="14" t="s">
@@ -25862,7 +25917,7 @@
       </c>
     </row>
     <row r="393" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A393" s="14">
+      <c r="A393" s="38">
         <v>466</v>
       </c>
       <c r="B393" s="14" t="s">
@@ -25906,7 +25961,7 @@
       </c>
     </row>
     <row r="394" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A394" s="14">
+      <c r="A394" s="38">
         <v>3577</v>
       </c>
       <c r="B394" s="14" t="s">
@@ -25950,7 +26005,7 @@
       </c>
     </row>
     <row r="395" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A395" s="14">
+      <c r="A395" s="38">
         <v>409</v>
       </c>
       <c r="B395" s="14" t="s">
@@ -25994,7 +26049,7 @@
       </c>
     </row>
     <row r="396" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A396" s="14">
+      <c r="A396" s="38">
         <v>140</v>
       </c>
       <c r="B396" s="14" t="s">
@@ -26038,7 +26093,7 @@
       </c>
     </row>
     <row r="397" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A397" s="14">
+      <c r="A397" s="38">
         <v>2869</v>
       </c>
       <c r="B397" s="14" t="s">
@@ -26082,7 +26137,7 @@
       </c>
     </row>
     <row r="398" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A398" s="14">
+      <c r="A398" s="38">
         <v>3242</v>
       </c>
       <c r="B398" s="14" t="s">
@@ -26126,7 +26181,7 @@
       </c>
     </row>
     <row r="399" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A399" s="14">
+      <c r="A399" s="38">
         <v>456</v>
       </c>
       <c r="B399" s="14" t="s">
@@ -26170,7 +26225,7 @@
       </c>
     </row>
     <row r="400" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A400" s="14">
+      <c r="A400" s="38">
         <v>7890</v>
       </c>
       <c r="B400" s="14" t="s">
@@ -26214,7 +26269,7 @@
       </c>
     </row>
     <row r="401" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A401" s="14">
+      <c r="A401" s="38">
         <v>3546</v>
       </c>
       <c r="B401" s="14" t="s">
@@ -26258,7 +26313,7 @@
       </c>
     </row>
     <row r="402" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A402" s="14">
+      <c r="A402" s="38">
         <v>3073</v>
       </c>
       <c r="B402" s="14" t="s">
@@ -26306,7 +26361,7 @@
       </c>
     </row>
     <row r="403" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A403" s="14">
+      <c r="A403" s="38">
         <v>213</v>
       </c>
       <c r="B403" s="14" t="s">
@@ -26350,7 +26405,7 @@
       </c>
     </row>
     <row r="404" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A404" s="14">
+      <c r="A404" s="38">
         <v>4952</v>
       </c>
       <c r="B404" s="14" t="s">
@@ -26394,7 +26449,7 @@
       </c>
     </row>
     <row r="405" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A405" s="14">
+      <c r="A405" s="38">
         <v>77</v>
       </c>
       <c r="B405" s="14" t="s">
@@ -26438,7 +26493,7 @@
       </c>
     </row>
     <row r="406" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A406" s="14">
+      <c r="A406" s="38">
         <v>6579</v>
       </c>
       <c r="B406" s="14" t="s">
@@ -26482,7 +26537,7 @@
       </c>
     </row>
     <row r="407" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A407" s="14">
+      <c r="A407" s="38">
         <v>118</v>
       </c>
       <c r="B407" s="14" t="s">
@@ -26526,7 +26581,7 @@
       </c>
     </row>
     <row r="408" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A408" s="14">
+      <c r="A408" s="38">
         <v>434</v>
       </c>
       <c r="B408" s="14" t="s">
@@ -26570,7 +26625,7 @@
       </c>
     </row>
     <row r="409" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A409" s="14">
+      <c r="A409" s="38">
         <v>4542</v>
       </c>
       <c r="B409" s="14" t="s">
@@ -26618,7 +26673,7 @@
       </c>
     </row>
     <row r="410" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A410" s="14">
+      <c r="A410" s="38">
         <v>73</v>
       </c>
       <c r="B410" s="14" t="s">
@@ -26662,7 +26717,7 @@
       </c>
     </row>
     <row r="411" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A411" s="14">
+      <c r="A411" s="38">
         <v>642</v>
       </c>
       <c r="B411" s="14" t="s">
@@ -26706,7 +26761,7 @@
       </c>
     </row>
     <row r="412" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A412" s="14">
+      <c r="A412" s="38">
         <v>3925</v>
       </c>
       <c r="B412" s="14" t="s">
@@ -26750,7 +26805,7 @@
       </c>
     </row>
     <row r="413" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A413" s="14">
+      <c r="A413" s="38">
         <v>74</v>
       </c>
       <c r="B413" s="14" t="s">
@@ -26794,7 +26849,7 @@
       </c>
     </row>
     <row r="414" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A414" s="14">
+      <c r="A414" s="38">
         <v>3586</v>
       </c>
       <c r="B414" s="14" t="s">
@@ -26838,7 +26893,7 @@
       </c>
     </row>
     <row r="415" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A415" s="14">
+      <c r="A415" s="38">
         <v>590</v>
       </c>
       <c r="B415" s="14" t="s">
@@ -26882,7 +26937,7 @@
       </c>
     </row>
     <row r="416" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A416" s="14">
+      <c r="A416" s="38">
         <v>32</v>
       </c>
       <c r="B416" s="14" t="s">
@@ -26932,7 +26987,7 @@
       </c>
     </row>
     <row r="417" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A417" s="14">
+      <c r="A417" s="38">
         <v>3096</v>
       </c>
       <c r="B417" s="14" t="s">
@@ -26976,7 +27031,7 @@
       </c>
     </row>
     <row r="418" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A418" s="14">
+      <c r="A418" s="38">
         <v>373</v>
       </c>
       <c r="B418" s="14" t="s">
@@ -27020,7 +27075,7 @@
       </c>
     </row>
     <row r="419" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A419" s="14">
+      <c r="A419" s="38">
         <v>397</v>
       </c>
       <c r="B419" s="14" t="s">
@@ -27064,7 +27119,7 @@
       </c>
     </row>
     <row r="420" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A420" s="14">
+      <c r="A420" s="38">
         <v>5883</v>
       </c>
       <c r="B420" s="14" t="s">
@@ -27108,7 +27163,7 @@
       </c>
     </row>
     <row r="421" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A421" s="14">
+      <c r="A421" s="38">
         <v>69</v>
       </c>
       <c r="B421" s="14" t="s">
@@ -27152,7 +27207,7 @@
       </c>
     </row>
     <row r="422" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A422" s="14">
+      <c r="A422" s="38">
         <v>133</v>
       </c>
       <c r="B422" s="14" t="s">
@@ -27196,7 +27251,7 @@
       </c>
     </row>
     <row r="423" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A423" s="14">
+      <c r="A423" s="38">
         <v>657</v>
       </c>
       <c r="B423" s="14" t="s">
@@ -27246,7 +27301,7 @@
       </c>
     </row>
     <row r="424" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A424" s="14">
+      <c r="A424" s="38">
         <v>106</v>
       </c>
       <c r="B424" s="14" t="s">
@@ -27290,7 +27345,7 @@
       </c>
     </row>
     <row r="425" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A425" s="14">
+      <c r="A425" s="38">
         <v>6451</v>
       </c>
       <c r="B425" s="14" t="s">
@@ -27338,7 +27393,7 @@
       </c>
     </row>
     <row r="426" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A426" s="14">
+      <c r="A426" s="38">
         <v>290</v>
       </c>
       <c r="B426" s="14" t="s">
@@ -27382,7 +27437,7 @@
       </c>
     </row>
     <row r="427" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A427" s="14">
+      <c r="A427" s="38">
         <v>161</v>
       </c>
       <c r="B427" s="14" t="s">
@@ -27426,7 +27481,7 @@
       </c>
     </row>
     <row r="428" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A428" s="14">
+      <c r="A428" s="38">
         <v>4199</v>
       </c>
       <c r="B428" s="14" t="s">
@@ -27470,7 +27525,7 @@
       </c>
     </row>
     <row r="429" spans="1:18" ht="76" x14ac:dyDescent="0.35">
-      <c r="A429" s="14">
+      <c r="A429" s="38">
         <v>3076</v>
       </c>
       <c r="B429" s="14" t="s">
@@ -27520,7 +27575,7 @@
       </c>
     </row>
     <row r="430" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A430" s="14">
+      <c r="A430" s="38">
         <v>4460</v>
       </c>
       <c r="B430" s="14" t="s">
@@ -27564,7 +27619,7 @@
       </c>
     </row>
     <row r="431" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A431" s="14">
+      <c r="A431" s="38">
         <v>3553</v>
       </c>
       <c r="B431" s="14" t="s">
@@ -27608,7 +27663,7 @@
       </c>
     </row>
     <row r="432" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A432" s="14">
+      <c r="A432" s="38">
         <v>125</v>
       </c>
       <c r="B432" s="14" t="s">
@@ -27652,7 +27707,7 @@
       </c>
     </row>
     <row r="433" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A433" s="14">
+      <c r="A433" s="38">
         <v>17</v>
       </c>
       <c r="B433" s="14" t="s">
@@ -27696,7 +27751,7 @@
       </c>
     </row>
     <row r="434" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A434" s="14">
+      <c r="A434" s="38">
         <v>488</v>
       </c>
       <c r="B434" s="14" t="s">
@@ -27740,7 +27795,7 @@
       </c>
     </row>
     <row r="435" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A435" s="14">
+      <c r="A435" s="38">
         <v>576</v>
       </c>
       <c r="B435" s="14" t="s">
@@ -27784,7 +27839,7 @@
       </c>
     </row>
     <row r="436" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A436" s="14">
+      <c r="A436" s="38">
         <v>332</v>
       </c>
       <c r="B436" s="14" t="s">
@@ -27828,7 +27883,7 @@
       </c>
     </row>
     <row r="437" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A437" s="14">
+      <c r="A437" s="38">
         <v>5362</v>
       </c>
       <c r="B437" s="14" t="s">
@@ -27872,7 +27927,7 @@
       </c>
     </row>
     <row r="438" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A438" s="14">
+      <c r="A438" s="38">
         <v>5908</v>
       </c>
       <c r="B438" s="14" t="s">
@@ -27916,7 +27971,7 @@
       </c>
     </row>
     <row r="439" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A439" s="14">
+      <c r="A439" s="38">
         <v>8776</v>
       </c>
       <c r="B439" s="14" t="s">
@@ -27960,7 +28015,7 @@
       </c>
     </row>
     <row r="440" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A440" s="14">
+      <c r="A440" s="38">
         <v>6274</v>
       </c>
       <c r="B440" s="14" t="s">
@@ -28004,7 +28059,7 @@
       </c>
     </row>
     <row r="441" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A441" s="14">
+      <c r="A441" s="38">
         <v>6071</v>
       </c>
       <c r="B441" s="14" t="s">
@@ -28048,7 +28103,7 @@
       </c>
     </row>
     <row r="442" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A442" s="14">
+      <c r="A442" s="38">
         <v>6213</v>
       </c>
       <c r="B442" s="14" t="s">
@@ -28092,7 +28147,7 @@
       </c>
     </row>
     <row r="443" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A443" s="14">
+      <c r="A443" s="38">
         <v>551</v>
       </c>
       <c r="B443" s="14" t="s">
@@ -28136,7 +28191,7 @@
       </c>
     </row>
     <row r="444" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A444" s="14">
+      <c r="A444" s="38">
         <v>5850</v>
       </c>
       <c r="B444" s="14" t="s">
@@ -28180,7 +28235,7 @@
       </c>
     </row>
     <row r="445" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A445" s="14">
+      <c r="A445" s="38">
         <v>437</v>
       </c>
       <c r="B445" s="14" t="s">
@@ -28224,7 +28279,7 @@
       </c>
     </row>
     <row r="446" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A446" s="14">
+      <c r="A446" s="38">
         <v>276</v>
       </c>
       <c r="B446" s="14" t="s">
@@ -28268,7 +28323,7 @@
       </c>
     </row>
     <row r="447" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A447" s="14">
+      <c r="A447" s="38">
         <v>14</v>
       </c>
       <c r="B447" s="14" t="s">
@@ -28312,7 +28367,7 @@
       </c>
     </row>
     <row r="448" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A448" s="14">
+      <c r="A448" s="38">
         <v>201</v>
       </c>
       <c r="B448" s="14" t="s">
@@ -28356,7 +28411,7 @@
       </c>
     </row>
     <row r="449" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A449" s="14">
+      <c r="A449" s="38">
         <v>299</v>
       </c>
       <c r="B449" s="14" t="s">
@@ -28400,7 +28455,7 @@
       </c>
     </row>
     <row r="450" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A450" s="14">
+      <c r="A450" s="38">
         <v>530</v>
       </c>
       <c r="B450" s="14" t="s">
@@ -28444,7 +28499,7 @@
       </c>
     </row>
     <row r="451" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A451" s="14">
+      <c r="A451" s="38">
         <v>15</v>
       </c>
       <c r="B451" s="14" t="s">
@@ -28488,7 +28543,7 @@
       </c>
     </row>
     <row r="452" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A452" s="14">
+      <c r="A452" s="38">
         <v>115</v>
       </c>
       <c r="B452" s="14" t="s">
@@ -28532,7 +28587,7 @@
       </c>
     </row>
     <row r="453" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A453" s="14">
+      <c r="A453" s="38">
         <v>653</v>
       </c>
       <c r="B453" s="14" t="s">
@@ -28582,7 +28637,7 @@
       </c>
     </row>
     <row r="454" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A454" s="14">
+      <c r="A454" s="38">
         <v>440</v>
       </c>
       <c r="B454" s="14" t="s">
@@ -28626,7 +28681,7 @@
       </c>
     </row>
     <row r="455" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A455" s="14">
+      <c r="A455" s="38">
         <v>654</v>
       </c>
       <c r="B455" s="14" t="s">
@@ -28676,7 +28731,7 @@
       </c>
     </row>
     <row r="456" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A456" s="14">
+      <c r="A456" s="38">
         <v>4999</v>
       </c>
       <c r="B456" s="14" t="s">
@@ -28720,7 +28775,7 @@
       </c>
     </row>
     <row r="457" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A457" s="14">
+      <c r="A457" s="38">
         <v>44</v>
       </c>
       <c r="B457" s="14" t="s">
@@ -28764,7 +28819,7 @@
       </c>
     </row>
     <row r="458" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A458" s="14">
+      <c r="A458" s="38">
         <v>549</v>
       </c>
       <c r="B458" s="14" t="s">
@@ -28808,7 +28863,7 @@
       </c>
     </row>
     <row r="459" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A459" s="14">
+      <c r="A459" s="38">
         <v>372</v>
       </c>
       <c r="B459" s="14" t="s">
@@ -28852,7 +28907,7 @@
       </c>
     </row>
     <row r="460" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A460" s="14">
+      <c r="A460" s="38">
         <v>329</v>
       </c>
       <c r="B460" s="14" t="s">
@@ -28896,7 +28951,7 @@
       </c>
     </row>
     <row r="461" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A461" s="14">
+      <c r="A461" s="38">
         <v>350</v>
       </c>
       <c r="B461" s="14" t="s">
@@ -28940,7 +28995,7 @@
       </c>
     </row>
     <row r="462" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A462" s="14">
+      <c r="A462" s="38">
         <v>6469</v>
       </c>
       <c r="B462" s="14" t="s">
@@ -28984,7 +29039,7 @@
       </c>
     </row>
     <row r="463" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A463" s="14">
+      <c r="A463" s="38">
         <v>22</v>
       </c>
       <c r="B463" s="14" t="s">
@@ -29028,7 +29083,7 @@
       </c>
     </row>
     <row r="464" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A464" s="14">
+      <c r="A464" s="38">
         <v>656</v>
       </c>
       <c r="B464" s="14" t="s">
@@ -29078,7 +29133,7 @@
       </c>
     </row>
     <row r="465" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A465" s="14">
+      <c r="A465" s="38">
         <v>135</v>
       </c>
       <c r="B465" s="14" t="s">
@@ -29122,7 +29177,7 @@
       </c>
     </row>
     <row r="466" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A466" s="14">
+      <c r="A466" s="38">
         <v>3501</v>
       </c>
       <c r="B466" s="14" t="s">
@@ -29166,7 +29221,7 @@
       </c>
     </row>
     <row r="467" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A467" s="14">
+      <c r="A467" s="38">
         <v>2775</v>
       </c>
       <c r="B467" s="14" t="s">
@@ -29210,7 +29265,7 @@
       </c>
     </row>
     <row r="468" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A468" s="14">
+      <c r="A468" s="38">
         <v>3079</v>
       </c>
       <c r="B468" s="14" t="s">
@@ -29254,7 +29309,7 @@
       </c>
     </row>
     <row r="469" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A469" s="14">
+      <c r="A469" s="38">
         <v>4398</v>
       </c>
       <c r="B469" s="14" t="s">
@@ -29298,7 +29353,7 @@
       </c>
     </row>
     <row r="470" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A470" s="14">
+      <c r="A470" s="38">
         <v>3503</v>
       </c>
       <c r="B470" s="14" t="s">
@@ -29342,7 +29397,7 @@
       </c>
     </row>
     <row r="471" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A471" s="14">
+      <c r="A471" s="38">
         <v>6547</v>
       </c>
       <c r="B471" s="14" t="s">
@@ -29386,7 +29441,7 @@
       </c>
     </row>
     <row r="472" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A472" s="14">
+      <c r="A472" s="38">
         <v>6472</v>
       </c>
       <c r="B472" s="14" t="s">
@@ -29430,7 +29485,7 @@
       </c>
     </row>
     <row r="473" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A473" s="14">
+      <c r="A473" s="38">
         <v>2694</v>
       </c>
       <c r="B473" s="14" t="s">
@@ -29474,7 +29529,7 @@
       </c>
     </row>
     <row r="474" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A474" s="14">
+      <c r="A474" s="38">
         <v>5300</v>
       </c>
       <c r="B474" s="14" t="s">
@@ -29518,7 +29573,7 @@
       </c>
     </row>
     <row r="475" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A475" s="14">
+      <c r="A475" s="38">
         <v>205</v>
       </c>
       <c r="B475" s="14" t="s">
@@ -29562,7 +29617,7 @@
       </c>
     </row>
     <row r="476" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A476" s="14">
+      <c r="A476" s="38">
         <v>388</v>
       </c>
       <c r="B476" s="14" t="s">
@@ -29606,7 +29661,7 @@
       </c>
     </row>
     <row r="477" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A477" s="14">
+      <c r="A477" s="38">
         <v>176</v>
       </c>
       <c r="B477" s="14" t="s">
@@ -29650,7 +29705,7 @@
       </c>
     </row>
     <row r="478" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A478" s="14">
+      <c r="A478" s="38">
         <v>3813</v>
       </c>
       <c r="B478" s="14" t="s">
@@ -29694,7 +29749,7 @@
       </c>
     </row>
     <row r="479" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A479" s="14">
+      <c r="A479" s="38">
         <v>365</v>
       </c>
       <c r="B479" s="14" t="s">
@@ -29738,7 +29793,7 @@
       </c>
     </row>
     <row r="480" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A480" s="14">
+      <c r="A480" s="38">
         <v>619</v>
       </c>
       <c r="B480" s="14" t="s">
@@ -29782,7 +29837,7 @@
       </c>
     </row>
     <row r="481" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A481" s="14">
+      <c r="A481" s="38">
         <v>4886</v>
       </c>
       <c r="B481" s="14" t="s">
@@ -29826,7 +29881,7 @@
       </c>
     </row>
     <row r="482" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A482" s="14">
+      <c r="A482" s="38">
         <v>231</v>
       </c>
       <c r="B482" s="14" t="s">
@@ -29874,7 +29929,7 @@
       </c>
     </row>
     <row r="483" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A483" s="14">
+      <c r="A483" s="38">
         <v>2182</v>
       </c>
       <c r="B483" s="14" t="s">
@@ -29918,7 +29973,7 @@
       </c>
     </row>
     <row r="484" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A484" s="14">
+      <c r="A484" s="38">
         <v>7386</v>
       </c>
       <c r="B484" s="14" t="s">
@@ -29962,7 +30017,7 @@
       </c>
     </row>
     <row r="485" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A485" s="14">
+      <c r="A485" s="38">
         <v>60</v>
       </c>
       <c r="B485" s="14" t="s">
@@ -30006,7 +30061,7 @@
       </c>
     </row>
     <row r="486" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A486" s="14">
+      <c r="A486" s="38">
         <v>3529</v>
       </c>
       <c r="B486" s="14" t="s">
@@ -30050,7 +30105,7 @@
       </c>
     </row>
     <row r="487" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A487" s="14">
+      <c r="A487" s="38">
         <v>179</v>
       </c>
       <c r="B487" s="14" t="s">
@@ -30094,7 +30149,7 @@
       </c>
     </row>
     <row r="488" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A488" s="14">
+      <c r="A488" s="38">
         <v>233</v>
       </c>
       <c r="B488" s="14" t="s">
@@ -30144,7 +30199,7 @@
       </c>
     </row>
     <row r="489" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A489" s="14">
+      <c r="A489" s="38">
         <v>2184</v>
       </c>
       <c r="B489" s="14" t="s">
@@ -30188,7 +30243,7 @@
       </c>
     </row>
     <row r="490" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A490" s="14">
+      <c r="A490" s="38">
         <v>7460</v>
       </c>
       <c r="B490" s="14" t="s">
@@ -30232,7 +30287,7 @@
       </c>
     </row>
     <row r="491" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A491" s="14">
+      <c r="A491" s="38">
         <v>641</v>
       </c>
       <c r="B491" s="14" t="s">
@@ -30276,7 +30331,7 @@
       </c>
     </row>
     <row r="492" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A492" s="14">
+      <c r="A492" s="38">
         <v>6442</v>
       </c>
       <c r="B492" s="14" t="s">
@@ -30320,7 +30375,7 @@
       </c>
     </row>
     <row r="493" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A493" s="14">
+      <c r="A493" s="38">
         <v>482</v>
       </c>
       <c r="B493" s="14" t="s">
@@ -30364,7 +30419,7 @@
       </c>
     </row>
     <row r="494" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A494" s="14">
+      <c r="A494" s="38">
         <v>6466</v>
       </c>
       <c r="B494" s="14" t="s">
@@ -30408,7 +30463,7 @@
       </c>
     </row>
     <row r="495" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A495" s="14">
+      <c r="A495" s="38">
         <v>660</v>
       </c>
       <c r="B495" s="14" t="s">
@@ -30452,7 +30507,7 @@
       </c>
     </row>
     <row r="496" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A496" s="14">
+      <c r="A496" s="38">
         <v>6464</v>
       </c>
       <c r="B496" s="14" t="s">
@@ -30496,7 +30551,7 @@
       </c>
     </row>
     <row r="497" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A497" s="14">
+      <c r="A497" s="38">
         <v>41</v>
       </c>
       <c r="B497" s="14" t="s">
@@ -30540,7 +30595,7 @@
       </c>
     </row>
     <row r="498" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A498" s="14">
+      <c r="A498" s="38">
         <v>12</v>
       </c>
       <c r="B498" s="14" t="s">
@@ -30584,7 +30639,7 @@
       </c>
     </row>
     <row r="499" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A499" s="14">
+      <c r="A499" s="38">
         <v>6068</v>
       </c>
       <c r="B499" s="14" t="s">
@@ -30628,7 +30683,7 @@
       </c>
     </row>
     <row r="500" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A500" s="14">
+      <c r="A500" s="38">
         <v>47</v>
       </c>
       <c r="B500" s="14" t="s">
@@ -30672,7 +30727,7 @@
       </c>
     </row>
     <row r="501" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A501" s="14">
+      <c r="A501" s="38">
         <v>518</v>
       </c>
       <c r="B501" s="14" t="s">
@@ -30716,7 +30771,7 @@
       </c>
     </row>
     <row r="502" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A502" s="14">
+      <c r="A502" s="38">
         <v>6653</v>
       </c>
       <c r="B502" s="14" t="s">
@@ -30760,7 +30815,7 @@
       </c>
     </row>
     <row r="503" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A503" s="14">
+      <c r="A503" s="38">
         <v>5834</v>
       </c>
       <c r="B503" s="14" t="s">
@@ -30804,7 +30859,7 @@
       </c>
     </row>
     <row r="504" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A504" s="14">
+      <c r="A504" s="38">
         <v>2672</v>
       </c>
       <c r="B504" s="14" t="s">
@@ -30848,7 +30903,7 @@
       </c>
     </row>
     <row r="505" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A505" s="14">
+      <c r="A505" s="38">
         <v>6240</v>
       </c>
       <c r="B505" s="14" t="s">
@@ -30892,7 +30947,7 @@
       </c>
     </row>
     <row r="506" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A506" s="14">
+      <c r="A506" s="38">
         <v>3498</v>
       </c>
       <c r="B506" s="14" t="s">
@@ -30936,7 +30991,7 @@
       </c>
     </row>
     <row r="507" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A507" s="14">
+      <c r="A507" s="38">
         <v>225</v>
       </c>
       <c r="B507" s="14" t="s">
@@ -30980,7 +31035,7 @@
       </c>
     </row>
     <row r="508" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A508" s="14">
+      <c r="A508" s="38">
         <v>5876</v>
       </c>
       <c r="B508" s="14" t="s">
@@ -31024,7 +31079,7 @@
       </c>
     </row>
     <row r="509" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A509" s="14">
+      <c r="A509" s="38">
         <v>5448</v>
       </c>
       <c r="B509" s="14" t="s">
@@ -31072,7 +31127,7 @@
       </c>
     </row>
     <row r="510" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A510" s="14">
+      <c r="A510" s="38">
         <v>5864</v>
       </c>
       <c r="B510" s="14" t="s">
@@ -31116,7 +31171,7 @@
       </c>
     </row>
     <row r="511" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A511" s="14">
+      <c r="A511" s="38">
         <v>8246</v>
       </c>
       <c r="B511" s="14" t="s">
@@ -31160,7 +31215,7 @@
       </c>
     </row>
     <row r="512" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A512" s="14">
+      <c r="A512" s="38">
         <v>342</v>
       </c>
       <c r="B512" s="14" t="s">
@@ -31204,7 +31259,7 @@
       </c>
     </row>
     <row r="513" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A513" s="14">
+      <c r="A513" s="38">
         <v>402</v>
       </c>
       <c r="B513" s="14" t="s">
@@ -31248,7 +31303,7 @@
       </c>
     </row>
     <row r="514" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A514" s="14">
+      <c r="A514" s="38">
         <v>561</v>
       </c>
       <c r="B514" s="14" t="s">
@@ -31292,7 +31347,7 @@
       </c>
     </row>
     <row r="515" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A515" s="14">
+      <c r="A515" s="38">
         <v>4707</v>
       </c>
       <c r="B515" s="14" t="s">
@@ -31336,7 +31391,7 @@
       </c>
     </row>
     <row r="516" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A516" s="14">
+      <c r="A516" s="38">
         <v>294</v>
       </c>
       <c r="B516" s="14" t="s">
@@ -31380,7 +31435,7 @@
       </c>
     </row>
     <row r="517" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A517" s="14">
+      <c r="A517" s="38">
         <v>8392</v>
       </c>
       <c r="B517" s="14" t="s">
@@ -31424,7 +31479,7 @@
       </c>
     </row>
     <row r="518" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A518" s="14">
+      <c r="A518" s="38">
         <v>441</v>
       </c>
       <c r="B518" s="14" t="s">
@@ -31472,7 +31527,7 @@
       </c>
     </row>
     <row r="519" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A519" s="14">
+      <c r="A519" s="38">
         <v>5212</v>
       </c>
       <c r="B519" s="14" t="s">
@@ -31520,7 +31575,7 @@
       </c>
     </row>
     <row r="520" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A520" s="14">
+      <c r="A520" s="38">
         <v>547</v>
       </c>
       <c r="B520" s="14" t="s">
@@ -31564,7 +31619,7 @@
       </c>
     </row>
     <row r="521" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A521" s="14">
+      <c r="A521" s="38">
         <v>6553</v>
       </c>
       <c r="B521" s="14" t="s">
@@ -31608,7 +31663,7 @@
       </c>
     </row>
     <row r="522" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A522" s="14">
+      <c r="A522" s="38">
         <v>95</v>
       </c>
       <c r="B522" s="14" t="s">
@@ -31652,7 +31707,7 @@
       </c>
     </row>
     <row r="523" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A523" s="14">
+      <c r="A523" s="38">
         <v>7</v>
       </c>
       <c r="B523" s="14" t="s">
@@ -31696,7 +31751,7 @@
       </c>
     </row>
     <row r="524" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A524" s="14">
+      <c r="A524" s="38">
         <v>513</v>
       </c>
       <c r="B524" s="14" t="s">
@@ -31740,7 +31795,7 @@
       </c>
     </row>
     <row r="525" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A525" s="14">
+      <c r="A525" s="38">
         <v>3052</v>
       </c>
       <c r="B525" s="14" t="s">
@@ -31784,7 +31839,7 @@
       </c>
     </row>
     <row r="526" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A526" s="14">
+      <c r="A526" s="38">
         <v>3134</v>
       </c>
       <c r="B526" s="14" t="s">
@@ -31832,7 +31887,7 @@
       </c>
     </row>
     <row r="527" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A527" s="14">
+      <c r="A527" s="38">
         <v>116</v>
       </c>
       <c r="B527" s="14" t="s">
@@ -31876,7 +31931,7 @@
       </c>
     </row>
     <row r="528" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A528" s="14">
+      <c r="A528" s="38">
         <v>394</v>
       </c>
       <c r="B528" s="14" t="s">
@@ -31920,7 +31975,7 @@
       </c>
     </row>
     <row r="529" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A529" s="14">
+      <c r="A529" s="38">
         <v>4539</v>
       </c>
       <c r="B529" s="14" t="s">
@@ -31964,7 +32019,7 @@
       </c>
     </row>
     <row r="530" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A530" s="14">
+      <c r="A530" s="38">
         <v>390</v>
       </c>
       <c r="B530" s="14" t="s">
@@ -32012,7 +32067,7 @@
       </c>
     </row>
     <row r="531" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A531" s="14">
+      <c r="A531" s="38">
         <v>503</v>
       </c>
       <c r="B531" s="14" t="s">
@@ -32056,7 +32111,7 @@
       </c>
     </row>
     <row r="532" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A532" s="14">
+      <c r="A532" s="38">
         <v>283</v>
       </c>
       <c r="B532" s="14" t="s">
@@ -32100,7 +32155,7 @@
       </c>
     </row>
     <row r="533" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A533" s="14">
+      <c r="A533" s="38">
         <v>90</v>
       </c>
       <c r="B533" s="14" t="s">
@@ -32144,7 +32199,7 @@
       </c>
     </row>
     <row r="534" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A534" s="14">
+      <c r="A534" s="38">
         <v>639</v>
       </c>
       <c r="B534" s="14" t="s">
@@ -32188,7 +32243,7 @@
       </c>
     </row>
     <row r="535" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A535" s="14">
+      <c r="A535" s="38">
         <v>220</v>
       </c>
       <c r="B535" s="14" t="s">
@@ -32232,7 +32287,7 @@
       </c>
     </row>
     <row r="536" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A536" s="14">
+      <c r="A536" s="38">
         <v>463</v>
       </c>
       <c r="B536" s="14" t="s">
@@ -32276,7 +32331,7 @@
       </c>
     </row>
     <row r="537" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A537" s="14">
+      <c r="A537" s="38">
         <v>211</v>
       </c>
       <c r="B537" s="14" t="s">
@@ -32320,7 +32375,7 @@
       </c>
     </row>
     <row r="538" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A538" s="14">
+      <c r="A538" s="38">
         <v>6443</v>
       </c>
       <c r="B538" s="14" t="s">
@@ -32364,7 +32419,7 @@
       </c>
     </row>
     <row r="539" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A539" s="14">
+      <c r="A539" s="38">
         <v>224</v>
       </c>
       <c r="B539" s="14" t="s">
@@ -32408,7 +32463,7 @@
       </c>
     </row>
     <row r="540" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A540" s="14">
+      <c r="A540" s="38">
         <v>476</v>
       </c>
       <c r="B540" s="14" t="s">
@@ -32454,7 +32509,7 @@
       </c>
     </row>
     <row r="541" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A541" s="14">
+      <c r="A541" s="38">
         <v>253</v>
       </c>
       <c r="B541" s="14" t="s">
@@ -32498,7 +32553,7 @@
       </c>
     </row>
     <row r="542" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A542" s="14">
+      <c r="A542" s="38">
         <v>4379</v>
       </c>
       <c r="B542" s="14" t="s">
@@ -32542,7 +32597,7 @@
       </c>
     </row>
     <row r="543" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A543" s="14">
+      <c r="A543" s="38">
         <v>418</v>
       </c>
       <c r="B543" s="14" t="s">
@@ -32586,7 +32641,7 @@
       </c>
     </row>
     <row r="544" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A544" s="14">
+      <c r="A544" s="38">
         <v>4076</v>
       </c>
       <c r="B544" s="14" t="s">
@@ -32630,7 +32685,7 @@
       </c>
     </row>
     <row r="545" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A545" s="14">
+      <c r="A545" s="38">
         <v>562</v>
       </c>
       <c r="B545" s="14" t="s">
@@ -32674,7 +32729,7 @@
       </c>
     </row>
     <row r="546" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A546" s="14">
+      <c r="A546" s="38">
         <v>5958</v>
       </c>
       <c r="B546" s="14" t="s">
@@ -32718,7 +32773,7 @@
       </c>
     </row>
     <row r="547" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A547" s="14">
+      <c r="A547" s="38">
         <v>509</v>
       </c>
       <c r="B547" s="14" t="s">
@@ -32762,7 +32817,7 @@
       </c>
     </row>
     <row r="548" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A548" s="14">
+      <c r="A548" s="38">
         <v>477</v>
       </c>
       <c r="B548" s="14" t="s">
@@ -32806,7 +32861,7 @@
       </c>
     </row>
     <row r="549" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A549" s="14">
+      <c r="A549" s="38">
         <v>4914</v>
       </c>
       <c r="B549" s="14" t="s">
@@ -32850,7 +32905,7 @@
       </c>
     </row>
     <row r="550" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A550" s="14">
+      <c r="A550" s="38">
         <v>100</v>
       </c>
       <c r="B550" s="14" t="s">
@@ -32894,7 +32949,7 @@
       </c>
     </row>
     <row r="551" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A551" s="14">
+      <c r="A551" s="38">
         <v>429</v>
       </c>
       <c r="B551" s="14" t="s">
@@ -32938,7 +32993,7 @@
       </c>
     </row>
     <row r="552" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A552" s="14">
+      <c r="A552" s="38">
         <v>158</v>
       </c>
       <c r="B552" s="14" t="s">
@@ -32982,7 +33037,7 @@
       </c>
     </row>
     <row r="553" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A553" s="14">
+      <c r="A553" s="38">
         <v>4896</v>
       </c>
       <c r="B553" s="14" t="s">
@@ -33026,7 +33081,7 @@
       </c>
     </row>
     <row r="554" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A554" s="14">
+      <c r="A554" s="38">
         <v>519</v>
       </c>
       <c r="B554" s="14" t="s">
@@ -33070,7 +33125,7 @@
       </c>
     </row>
     <row r="555" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A555" s="14">
+      <c r="A555" s="38">
         <v>210</v>
       </c>
       <c r="B555" s="14" t="s">
@@ -33114,7 +33169,7 @@
       </c>
     </row>
     <row r="556" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A556" s="14">
+      <c r="A556" s="38">
         <v>186</v>
       </c>
       <c r="B556" s="14" t="s">
@@ -33158,7 +33213,7 @@
       </c>
     </row>
     <row r="557" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A557" s="14">
+      <c r="A557" s="38">
         <v>193</v>
       </c>
       <c r="B557" s="14" t="s">
@@ -33202,7 +33257,7 @@
       </c>
     </row>
     <row r="558" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A558" s="14">
+      <c r="A558" s="38">
         <v>599</v>
       </c>
       <c r="B558" s="14" t="s">
@@ -33246,7 +33301,7 @@
       </c>
     </row>
     <row r="559" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A559" s="14">
+      <c r="A559" s="38">
         <v>129</v>
       </c>
       <c r="B559" s="14" t="s">
@@ -33290,7 +33345,7 @@
       </c>
     </row>
     <row r="560" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A560" s="14">
+      <c r="A560" s="38">
         <v>5369</v>
       </c>
       <c r="B560" s="14" t="s">
@@ -33334,7 +33389,7 @@
       </c>
     </row>
     <row r="561" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A561" s="14">
+      <c r="A561" s="38">
         <v>4986</v>
       </c>
       <c r="B561" s="14" t="s">
@@ -33378,7 +33433,7 @@
       </c>
     </row>
     <row r="562" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A562" s="14">
+      <c r="A562" s="38">
         <v>5377</v>
       </c>
       <c r="B562" s="14" t="s">
@@ -33426,7 +33481,7 @@
       </c>
     </row>
     <row r="563" spans="1:18" ht="63.5" x14ac:dyDescent="0.35">
-      <c r="A563" s="14">
+      <c r="A563" s="38">
         <v>3585</v>
       </c>
       <c r="B563" s="14" t="s">
@@ -33476,7 +33531,7 @@
       </c>
     </row>
     <row r="564" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A564" s="14">
+      <c r="A564" s="38">
         <v>487</v>
       </c>
       <c r="B564" s="14" t="s">
@@ -33520,7 +33575,7 @@
       </c>
     </row>
     <row r="565" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A565" s="14">
+      <c r="A565" s="38">
         <v>5743</v>
       </c>
       <c r="B565" s="14" t="s">
@@ -33564,7 +33619,7 @@
       </c>
     </row>
     <row r="566" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A566" s="14">
+      <c r="A566" s="38">
         <v>344</v>
       </c>
       <c r="B566" s="14" t="s">
@@ -33608,7 +33663,7 @@
       </c>
     </row>
     <row r="567" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A567" s="14">
+      <c r="A567" s="38">
         <v>147</v>
       </c>
       <c r="B567" s="14" t="s">
@@ -33652,7 +33707,7 @@
       </c>
     </row>
     <row r="568" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A568" s="14">
+      <c r="A568" s="38">
         <v>6454</v>
       </c>
       <c r="B568" s="14" t="s">
@@ -33696,7 +33751,7 @@
       </c>
     </row>
     <row r="569" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A569" s="14">
+      <c r="A569" s="38">
         <v>6441</v>
       </c>
       <c r="B569" s="14" t="s">
@@ -33740,7 +33795,7 @@
       </c>
     </row>
     <row r="570" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A570" s="14">
+      <c r="A570" s="38">
         <v>5959</v>
       </c>
       <c r="B570" s="14" t="s">
@@ -33784,7 +33839,7 @@
       </c>
     </row>
     <row r="571" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A571" s="14">
+      <c r="A571" s="38">
         <v>62</v>
       </c>
       <c r="B571" s="14" t="s">
@@ -33828,7 +33883,7 @@
       </c>
     </row>
     <row r="572" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A572" s="14">
+      <c r="A572" s="38">
         <v>8201</v>
       </c>
       <c r="B572" s="14" t="s">
@@ -33872,7 +33927,7 @@
       </c>
     </row>
     <row r="573" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A573" s="14">
+      <c r="A573" s="38">
         <v>6456</v>
       </c>
       <c r="B573" s="14" t="s">
@@ -33920,7 +33975,7 @@
       </c>
     </row>
     <row r="574" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A574" s="14">
+      <c r="A574" s="38">
         <v>643</v>
       </c>
       <c r="B574" s="14" t="s">
@@ -33964,7 +34019,7 @@
       </c>
     </row>
     <row r="575" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A575" s="14">
+      <c r="A575" s="38">
         <v>2875</v>
       </c>
       <c r="B575" s="14" t="s">
@@ -34008,7 +34063,7 @@
       </c>
     </row>
     <row r="576" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A576" s="14">
+      <c r="A576" s="38">
         <v>602</v>
       </c>
       <c r="B576" s="14" t="s">
@@ -34052,7 +34107,7 @@
       </c>
     </row>
     <row r="577" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A577" s="14">
+      <c r="A577" s="38">
         <v>502</v>
       </c>
       <c r="B577" s="14" t="s">
@@ -34096,7 +34151,7 @@
       </c>
     </row>
     <row r="578" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A578" s="14">
+      <c r="A578" s="38">
         <v>465</v>
       </c>
       <c r="B578" s="14" t="s">
@@ -34140,7 +34195,7 @@
       </c>
     </row>
     <row r="579" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A579" s="14">
+      <c r="A579" s="38">
         <v>7372</v>
       </c>
       <c r="B579" s="14" t="s">
@@ -34184,7 +34239,7 @@
       </c>
     </row>
     <row r="580" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A580" s="14">
+      <c r="A580" s="38">
         <v>8707</v>
       </c>
       <c r="B580" s="14" t="s">
@@ -34228,7 +34283,7 @@
       </c>
     </row>
     <row r="581" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A581" s="14">
+      <c r="A581" s="38">
         <v>2881</v>
       </c>
       <c r="B581" s="14" t="s">
@@ -34272,7 +34327,7 @@
       </c>
     </row>
     <row r="582" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A582" s="14">
+      <c r="A582" s="38">
         <v>4374</v>
       </c>
       <c r="B582" s="14" t="s">
@@ -34316,7 +34371,7 @@
       </c>
     </row>
     <row r="583" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A583" s="14">
+      <c r="A583" s="38">
         <v>7370</v>
       </c>
       <c r="B583" s="14" t="s">
@@ -34360,7 +34415,7 @@
       </c>
     </row>
     <row r="584" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A584" s="14">
+      <c r="A584" s="38">
         <v>2261</v>
       </c>
       <c r="B584" s="14" t="s">
@@ -34404,7 +34459,7 @@
       </c>
     </row>
     <row r="585" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A585" s="14">
+      <c r="A585" s="38">
         <v>6986</v>
       </c>
       <c r="B585" s="14" t="s">
@@ -34448,7 +34503,7 @@
       </c>
     </row>
     <row r="586" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A586" s="14">
+      <c r="A586" s="38">
         <v>89</v>
       </c>
       <c r="B586" s="14" t="s">
@@ -34492,7 +34547,7 @@
       </c>
     </row>
     <row r="587" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A587" s="14">
+      <c r="A587" s="38">
         <v>189</v>
       </c>
       <c r="B587" s="14" t="s">
@@ -34536,7 +34591,7 @@
       </c>
     </row>
     <row r="588" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A588" s="14">
+      <c r="A588" s="38">
         <v>7392</v>
       </c>
       <c r="B588" s="14" t="s">
@@ -34580,7 +34635,7 @@
       </c>
     </row>
     <row r="589" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A589" s="14">
+      <c r="A589" s="38">
         <v>5931</v>
       </c>
       <c r="B589" s="14" t="s">
@@ -34624,7 +34679,7 @@
       </c>
     </row>
     <row r="590" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A590" s="14">
+      <c r="A590" s="38">
         <v>464</v>
       </c>
       <c r="B590" s="14" t="s">
@@ -34668,7 +34723,7 @@
       </c>
     </row>
     <row r="591" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A591" s="14">
+      <c r="A591" s="38">
         <v>7714</v>
       </c>
       <c r="B591" s="14" t="s">
@@ -34712,7 +34767,7 @@
       </c>
     </row>
     <row r="592" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A592" s="14">
+      <c r="A592" s="38">
         <v>481</v>
       </c>
       <c r="B592" s="14" t="s">
@@ -34756,7 +34811,7 @@
       </c>
     </row>
     <row r="593" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A593" s="14">
+      <c r="A593" s="38">
         <v>469</v>
       </c>
       <c r="B593" s="14" t="s">
@@ -34800,7 +34855,7 @@
       </c>
     </row>
     <row r="594" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A594" s="14">
+      <c r="A594" s="38">
         <v>5875</v>
       </c>
       <c r="B594" s="14" t="s">
@@ -34844,7 +34899,7 @@
       </c>
     </row>
     <row r="595" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A595" s="14">
+      <c r="A595" s="38">
         <v>6030</v>
       </c>
       <c r="B595" s="14" t="s">
@@ -34888,7 +34943,7 @@
       </c>
     </row>
     <row r="596" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A596" s="14">
+      <c r="A596" s="38">
         <v>483</v>
       </c>
       <c r="B596" s="14" t="s">
@@ -34932,7 +34987,7 @@
       </c>
     </row>
     <row r="597" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A597" s="14">
+      <c r="A597" s="38">
         <v>5732</v>
       </c>
       <c r="B597" s="14" t="s">
@@ -34976,7 +35031,7 @@
       </c>
     </row>
     <row r="598" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A598" s="14">
+      <c r="A598" s="38">
         <v>604</v>
       </c>
       <c r="B598" s="14" t="s">
@@ -35020,7 +35075,7 @@
       </c>
     </row>
     <row r="599" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A599" s="14">
+      <c r="A599" s="38">
         <v>181</v>
       </c>
       <c r="B599" s="14" t="s">
@@ -35064,7 +35119,7 @@
       </c>
     </row>
     <row r="600" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A600" s="14">
+      <c r="A600" s="38">
         <v>52</v>
       </c>
       <c r="B600" s="14" t="s">
@@ -35108,7 +35163,7 @@
       </c>
     </row>
     <row r="601" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A601" s="14">
+      <c r="A601" s="38">
         <v>3007</v>
       </c>
       <c r="B601" s="14" t="s">
@@ -35152,7 +35207,7 @@
       </c>
     </row>
     <row r="602" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A602" s="14">
+      <c r="A602" s="38">
         <v>7367</v>
       </c>
       <c r="B602" s="14" t="s">
@@ -35196,7 +35251,7 @@
       </c>
     </row>
     <row r="603" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A603" s="14">
+      <c r="A603" s="38">
         <v>345</v>
       </c>
       <c r="B603" s="14" t="s">
@@ -35240,7 +35295,7 @@
       </c>
     </row>
     <row r="604" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A604" s="14">
+      <c r="A604" s="38">
         <v>6546</v>
       </c>
       <c r="B604" s="14" t="s">
@@ -35284,7 +35339,7 @@
       </c>
     </row>
     <row r="605" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A605" s="14">
+      <c r="A605" s="38">
         <v>6371</v>
       </c>
       <c r="B605" s="14" t="s">
@@ -35328,7 +35383,7 @@
       </c>
     </row>
     <row r="606" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A606" s="14">
+      <c r="A606" s="38">
         <v>445</v>
       </c>
       <c r="B606" s="14" t="s">
@@ -35372,7 +35427,7 @@
       </c>
     </row>
     <row r="607" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A607" s="14">
+      <c r="A607" s="38">
         <v>480</v>
       </c>
       <c r="B607" s="14" t="s">
@@ -35416,7 +35471,7 @@
       </c>
     </row>
     <row r="608" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A608" s="14">
+      <c r="A608" s="38">
         <v>3589</v>
       </c>
       <c r="B608" s="14" t="s">
@@ -35460,7 +35515,7 @@
       </c>
     </row>
     <row r="609" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A609" s="14">
+      <c r="A609" s="38">
         <v>119</v>
       </c>
       <c r="B609" s="14" t="s">
@@ -35504,7 +35559,7 @@
       </c>
     </row>
     <row r="610" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A610" s="14">
+      <c r="A610" s="38">
         <v>449</v>
       </c>
       <c r="B610" s="14" t="s">
@@ -35548,7 +35603,7 @@
       </c>
     </row>
     <row r="611" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A611" s="14">
+      <c r="A611" s="38">
         <v>5168</v>
       </c>
       <c r="B611" s="14" t="s">
@@ -35592,7 +35647,7 @@
       </c>
     </row>
     <row r="612" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A612" s="14">
+      <c r="A612" s="38">
         <v>6167</v>
       </c>
       <c r="B612" s="14" t="s">
@@ -35636,7 +35691,7 @@
       </c>
     </row>
     <row r="613" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A613" s="14">
+      <c r="A613" s="38">
         <v>3994</v>
       </c>
       <c r="B613" s="14" t="s">
@@ -35680,7 +35735,7 @@
       </c>
     </row>
     <row r="614" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A614" s="14">
+      <c r="A614" s="38">
         <v>6447</v>
       </c>
       <c r="B614" s="14" t="s">
@@ -35724,7 +35779,7 @@
       </c>
     </row>
     <row r="615" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A615" s="14">
+      <c r="A615" s="38">
         <v>2682</v>
       </c>
       <c r="B615" s="14" t="s">
@@ -35768,7 +35823,7 @@
       </c>
     </row>
     <row r="616" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A616" s="14">
+      <c r="A616" s="38">
         <v>450</v>
       </c>
       <c r="B616" s="14" t="s">
@@ -35812,7 +35867,7 @@
       </c>
     </row>
     <row r="617" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A617" s="14">
+      <c r="A617" s="38">
         <v>3531</v>
       </c>
       <c r="B617" s="14" t="s">
@@ -35856,7 +35911,7 @@
       </c>
     </row>
     <row r="618" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A618" s="14">
+      <c r="A618" s="38">
         <v>5567</v>
       </c>
       <c r="B618" s="14" t="s">
@@ -35900,7 +35955,7 @@
       </c>
     </row>
     <row r="619" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A619" s="14">
+      <c r="A619" s="38">
         <v>3508</v>
       </c>
       <c r="B619" s="14" t="s">
@@ -35944,7 +35999,7 @@
       </c>
     </row>
     <row r="620" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A620" s="14">
+      <c r="A620" s="38">
         <v>5871</v>
       </c>
       <c r="B620" s="14" t="s">
@@ -35988,7 +36043,7 @@
       </c>
     </row>
     <row r="621" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A621" s="14">
+      <c r="A621" s="38">
         <v>7517</v>
       </c>
       <c r="B621" s="14" t="s">
@@ -36032,7 +36087,7 @@
       </c>
     </row>
     <row r="622" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A622" s="14">
+      <c r="A622" s="38">
         <v>3505</v>
       </c>
       <c r="B622" s="14" t="s">
@@ -36076,7 +36131,7 @@
       </c>
     </row>
     <row r="623" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A623" s="14">
+      <c r="A623" s="38">
         <v>6250</v>
       </c>
       <c r="B623" s="14" t="s">
@@ -36120,7 +36175,7 @@
       </c>
     </row>
     <row r="624" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A624" s="14">
+      <c r="A624" s="38">
         <v>589</v>
       </c>
       <c r="B624" s="14" t="s">
@@ -36164,7 +36219,7 @@
       </c>
     </row>
     <row r="625" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A625" s="14">
+      <c r="A625" s="38">
         <v>3080</v>
       </c>
       <c r="B625" s="14" t="s">
@@ -36208,7 +36263,7 @@
       </c>
     </row>
     <row r="626" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A626" s="14">
+      <c r="A626" s="38">
         <v>597</v>
       </c>
       <c r="B626" s="14" t="s">
@@ -36252,7 +36307,7 @@
       </c>
     </row>
     <row r="627" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A627" s="14">
+      <c r="A627" s="38">
         <v>422</v>
       </c>
       <c r="B627" s="14" t="s">
@@ -36296,7 +36351,7 @@
       </c>
     </row>
     <row r="628" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A628" s="14">
+      <c r="A628" s="38">
         <v>4261</v>
       </c>
       <c r="B628" s="14" t="s">
@@ -36340,7 +36395,7 @@
       </c>
     </row>
     <row r="629" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A629" s="14">
+      <c r="A629" s="38">
         <v>4400</v>
       </c>
       <c r="B629" s="14" t="s">
@@ -36384,7 +36439,7 @@
       </c>
     </row>
     <row r="630" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A630" s="14">
+      <c r="A630" s="38">
         <v>2668</v>
       </c>
       <c r="B630" s="14" t="s">
@@ -36432,7 +36487,7 @@
       </c>
     </row>
     <row r="631" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A631" s="14">
+      <c r="A631" s="38">
         <v>278</v>
       </c>
       <c r="B631" s="14" t="s">
@@ -36476,7 +36531,7 @@
       </c>
     </row>
     <row r="632" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A632" s="14">
+      <c r="A632" s="38">
         <v>4404</v>
       </c>
       <c r="B632" s="14" t="s">
@@ -36520,7 +36575,7 @@
       </c>
     </row>
     <row r="633" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A633" s="14">
+      <c r="A633" s="38">
         <v>172</v>
       </c>
       <c r="B633" s="14" t="s">
@@ -36564,7 +36619,7 @@
       </c>
     </row>
     <row r="634" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A634" s="14">
+      <c r="A634" s="38">
         <v>199</v>
       </c>
       <c r="B634" s="14" t="s">
@@ -36608,7 +36663,7 @@
       </c>
     </row>
     <row r="635" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A635" s="14">
+      <c r="A635" s="38">
         <v>580</v>
       </c>
       <c r="B635" s="14" t="s">
@@ -36652,7 +36707,7 @@
       </c>
     </row>
     <row r="636" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A636" s="14">
+      <c r="A636" s="38">
         <v>3136</v>
       </c>
       <c r="B636" s="14" t="s">
@@ -36696,7 +36751,7 @@
       </c>
     </row>
     <row r="637" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A637" s="14">
+      <c r="A637" s="38">
         <v>192</v>
       </c>
       <c r="B637" s="14" t="s">
@@ -36740,7 +36795,7 @@
       </c>
     </row>
     <row r="638" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A638" s="14">
+      <c r="A638" s="38">
         <v>6095</v>
       </c>
       <c r="B638" s="14" t="s">
@@ -36784,7 +36839,7 @@
       </c>
     </row>
     <row r="639" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A639" s="14">
+      <c r="A639" s="38">
         <v>5863</v>
       </c>
       <c r="B639" s="14" t="s">
@@ -36828,7 +36883,7 @@
       </c>
     </row>
     <row r="640" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A640" s="14">
+      <c r="A640" s="38">
         <v>4576</v>
       </c>
       <c r="B640" s="14" t="s">
@@ -36872,7 +36927,7 @@
       </c>
     </row>
     <row r="641" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A641" s="14">
+      <c r="A641" s="38">
         <v>2850</v>
       </c>
       <c r="B641" s="14" t="s">
@@ -36916,7 +36971,7 @@
       </c>
     </row>
     <row r="642" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A642" s="14">
+      <c r="A642" s="38">
         <v>7377</v>
       </c>
       <c r="B642" s="14" t="s">
@@ -36960,7 +37015,7 @@
       </c>
     </row>
     <row r="643" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A643" s="14">
+      <c r="A643" s="38">
         <v>215</v>
       </c>
       <c r="B643" s="14" t="s">
@@ -37004,7 +37059,7 @@
       </c>
     </row>
     <row r="644" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A644" s="14">
+      <c r="A644" s="38">
         <v>2546</v>
       </c>
       <c r="B644" s="14" t="s">
@@ -37048,7 +37103,7 @@
       </c>
     </row>
     <row r="645" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A645" s="14">
+      <c r="A645" s="38">
         <v>157</v>
       </c>
       <c r="B645" s="14" t="s">
@@ -37092,7 +37147,7 @@
       </c>
     </row>
     <row r="646" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A646" s="14">
+      <c r="A646" s="38">
         <v>646</v>
       </c>
       <c r="B646" s="14" t="s">
@@ -37136,7 +37191,7 @@
       </c>
     </row>
     <row r="647" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A647" s="14">
+      <c r="A647" s="38">
         <v>416</v>
       </c>
       <c r="B647" s="14" t="s">
@@ -37180,7 +37235,7 @@
       </c>
     </row>
     <row r="648" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A648" s="14">
+      <c r="A648" s="38">
         <v>38</v>
       </c>
       <c r="B648" s="14" t="s">
@@ -37224,7 +37279,7 @@
       </c>
     </row>
     <row r="649" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A649" s="14">
+      <c r="A649" s="38">
         <v>8877</v>
       </c>
       <c r="B649" s="14" t="s">
@@ -37268,7 +37323,7 @@
       </c>
     </row>
     <row r="650" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A650" s="14">
+      <c r="A650" s="38">
         <v>187</v>
       </c>
       <c r="B650" s="14" t="s">
@@ -37312,7 +37367,7 @@
       </c>
     </row>
     <row r="651" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A651" s="14">
+      <c r="A651" s="38">
         <v>7838</v>
       </c>
       <c r="B651" s="14" t="s">
@@ -37356,7 +37411,7 @@
       </c>
     </row>
     <row r="652" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A652" s="14">
+      <c r="A652" s="38">
         <v>500</v>
       </c>
       <c r="B652" s="14" t="s">
@@ -37400,7 +37455,7 @@
       </c>
     </row>
     <row r="653" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A653" s="14">
+      <c r="A653" s="38">
         <v>6455</v>
       </c>
       <c r="B653" s="14" t="s">
@@ -37448,7 +37503,7 @@
       </c>
     </row>
     <row r="654" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A654" s="14">
+      <c r="A654" s="38">
         <v>7837</v>
       </c>
       <c r="B654" s="14" t="s">
@@ -37492,7 +37547,7 @@
       </c>
     </row>
     <row r="655" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A655" s="14">
+      <c r="A655" s="38">
         <v>582</v>
       </c>
       <c r="B655" s="14" t="s">
@@ -37538,7 +37593,7 @@
       </c>
     </row>
     <row r="656" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A656" s="14">
+      <c r="A656" s="38">
         <v>520</v>
       </c>
       <c r="B656" s="14" t="s">
@@ -37582,7 +37637,7 @@
       </c>
     </row>
     <row r="657" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A657" s="14">
+      <c r="A657" s="38">
         <v>61</v>
       </c>
       <c r="B657" s="14" t="s">
@@ -37626,7 +37681,7 @@
       </c>
     </row>
     <row r="658" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A658" s="14">
+      <c r="A658" s="38">
         <v>7459</v>
       </c>
       <c r="B658" s="14" t="s">
@@ -37670,7 +37725,7 @@
       </c>
     </row>
     <row r="659" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A659" s="14">
+      <c r="A659" s="38">
         <v>7839</v>
       </c>
       <c r="B659" s="14" t="s">
@@ -37714,7 +37769,7 @@
       </c>
     </row>
     <row r="660" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A660" s="14">
+      <c r="A660" s="38">
         <v>8863</v>
       </c>
       <c r="B660" s="14" t="s">
@@ -37758,7 +37813,7 @@
       </c>
     </row>
     <row r="661" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A661" s="14">
+      <c r="A661" s="38">
         <v>4824</v>
       </c>
       <c r="B661" s="14" t="s">
@@ -37802,7 +37857,7 @@
       </c>
     </row>
     <row r="662" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A662" s="14">
+      <c r="A662" s="38">
         <v>7381</v>
       </c>
       <c r="B662" s="14" t="s">
@@ -37846,7 +37901,7 @@
       </c>
     </row>
     <row r="663" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A663" s="14">
+      <c r="A663" s="38">
         <v>8872</v>
       </c>
       <c r="B663" s="14" t="s">
@@ -37894,7 +37949,7 @@
       </c>
     </row>
     <row r="664" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A664" s="14">
+      <c r="A664" s="38">
         <v>6655</v>
       </c>
       <c r="B664" s="14" t="s">
@@ -37938,7 +37993,7 @@
       </c>
     </row>
     <row r="665" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A665" s="14">
+      <c r="A665" s="38">
         <v>3520</v>
       </c>
       <c r="B665" s="14" t="s">
@@ -37982,7 +38037,7 @@
       </c>
     </row>
     <row r="666" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A666" s="14">
+      <c r="A666" s="38">
         <v>3527</v>
       </c>
       <c r="B666" s="14" t="s">
@@ -38026,7 +38081,7 @@
       </c>
     </row>
     <row r="667" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A667" s="14">
+      <c r="A667" s="38">
         <v>175</v>
       </c>
       <c r="B667" s="14" t="s">
@@ -38070,7 +38125,7 @@
       </c>
     </row>
     <row r="668" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A668" s="14">
+      <c r="A668" s="38">
         <v>151</v>
       </c>
       <c r="B668" s="14" t="s">
@@ -38114,7 +38169,7 @@
       </c>
     </row>
     <row r="669" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A669" s="14">
+      <c r="A669" s="38">
         <v>446</v>
       </c>
       <c r="B669" s="14" t="s">
@@ -38162,7 +38217,7 @@
       </c>
     </row>
     <row r="670" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A670" s="14">
+      <c r="A670" s="38">
         <v>3584</v>
       </c>
       <c r="B670" s="14" t="s">
@@ -38206,7 +38261,7 @@
       </c>
     </row>
     <row r="671" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A671" s="14">
+      <c r="A671" s="38">
         <v>6444</v>
       </c>
       <c r="B671" s="14" t="s">
@@ -38250,7 +38305,7 @@
       </c>
     </row>
     <row r="672" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A672" s="14">
+      <c r="A672" s="38">
         <v>2765</v>
       </c>
       <c r="B672" s="14" t="s">
@@ -38294,7 +38349,7 @@
       </c>
     </row>
     <row r="673" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A673" s="14">
+      <c r="A673" s="38">
         <v>8611</v>
       </c>
       <c r="B673" s="14" t="s">
@@ -38338,7 +38393,7 @@
       </c>
     </row>
     <row r="674" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A674" s="14">
+      <c r="A674" s="38">
         <v>8460</v>
       </c>
       <c r="B674" s="14" t="s">
@@ -38382,7 +38437,7 @@
       </c>
     </row>
     <row r="675" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A675" s="14">
+      <c r="A675" s="38">
         <v>3530</v>
       </c>
       <c r="B675" s="14" t="s">
@@ -38426,7 +38481,7 @@
       </c>
     </row>
     <row r="676" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A676" s="14">
+      <c r="A676" s="38">
         <v>8779</v>
       </c>
       <c r="B676" s="14" t="s">
@@ -38470,7 +38525,7 @@
       </c>
     </row>
     <row r="677" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A677" s="14">
+      <c r="A677" s="38">
         <v>272</v>
       </c>
       <c r="B677" s="14" t="s">
@@ -38514,7 +38569,7 @@
       </c>
     </row>
     <row r="678" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A678" s="14">
+      <c r="A678" s="38">
         <v>8229</v>
       </c>
       <c r="B678" s="14" t="s">
@@ -38558,7 +38613,7 @@
       </c>
     </row>
     <row r="679" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A679" s="14">
+      <c r="A679" s="38">
         <v>5665</v>
       </c>
       <c r="B679" s="14" t="s">
@@ -38602,7 +38657,7 @@
       </c>
     </row>
     <row r="680" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A680" s="14">
+      <c r="A680" s="38">
         <v>3905</v>
       </c>
       <c r="B680" s="14" t="s">
@@ -38646,7 +38701,7 @@
       </c>
     </row>
     <row r="681" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A681" s="14">
+      <c r="A681" s="38">
         <v>2936</v>
       </c>
       <c r="B681" s="14" t="s">
@@ -38690,7 +38745,7 @@
       </c>
     </row>
     <row r="682" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A682" s="14">
+      <c r="A682" s="38">
         <v>227</v>
       </c>
       <c r="B682" s="14" t="s">
@@ -38734,7 +38789,7 @@
       </c>
     </row>
     <row r="683" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A683" s="14">
+      <c r="A683" s="38">
         <v>8869</v>
       </c>
       <c r="B683" s="14" t="s">
@@ -38778,7 +38833,7 @@
       </c>
     </row>
     <row r="684" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A684" s="14">
+      <c r="A684" s="38">
         <v>2392</v>
       </c>
       <c r="B684" s="14" t="s">
@@ -38822,7 +38877,7 @@
       </c>
     </row>
     <row r="685" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A685" s="14">
+      <c r="A685" s="38">
         <v>363</v>
       </c>
       <c r="B685" s="14" t="s">
@@ -38866,7 +38921,7 @@
       </c>
     </row>
     <row r="686" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A686" s="14">
+      <c r="A686" s="38">
         <v>309</v>
       </c>
       <c r="B686" s="14" t="s">
@@ -38910,7 +38965,7 @@
       </c>
     </row>
     <row r="687" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A687" s="14">
+      <c r="A687" s="38">
         <v>2615</v>
       </c>
       <c r="B687" s="14" t="s">
@@ -38954,7 +39009,7 @@
       </c>
     </row>
     <row r="688" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A688" s="14">
+      <c r="A688" s="38">
         <v>266</v>
       </c>
       <c r="B688" s="14" t="s">
@@ -38998,7 +39053,7 @@
       </c>
     </row>
     <row r="689" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A689" s="14">
+      <c r="A689" s="38">
         <v>5164</v>
       </c>
       <c r="B689" s="14" t="s">
@@ -39042,7 +39097,7 @@
       </c>
     </row>
     <row r="690" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A690" s="14">
+      <c r="A690" s="38">
         <v>81</v>
       </c>
       <c r="B690" s="14" t="s">
@@ -39086,7 +39141,7 @@
       </c>
     </row>
     <row r="691" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A691" s="14">
+      <c r="A691" s="38">
         <v>5337</v>
       </c>
       <c r="B691" s="14" t="s">
@@ -39130,7 +39185,7 @@
       </c>
     </row>
     <row r="692" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A692" s="14">
+      <c r="A692" s="38">
         <v>3581</v>
       </c>
       <c r="B692" s="14" t="s">
@@ -39174,7 +39229,7 @@
       </c>
     </row>
     <row r="693" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A693" s="14">
+      <c r="A693" s="38">
         <v>6994</v>
       </c>
       <c r="B693" s="14" t="s">
@@ -39218,7 +39273,7 @@
       </c>
     </row>
     <row r="694" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A694" s="14">
+      <c r="A694" s="38">
         <v>4920</v>
       </c>
       <c r="B694" s="14" t="s">
@@ -39262,7 +39317,7 @@
       </c>
     </row>
     <row r="695" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A695" s="14">
+      <c r="A695" s="38">
         <v>29</v>
       </c>
       <c r="B695" s="14" t="s">
@@ -39306,7 +39361,7 @@
       </c>
     </row>
     <row r="696" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A696" s="14">
+      <c r="A696" s="38">
         <v>627</v>
       </c>
       <c r="B696" s="14" t="s">
@@ -39350,7 +39405,7 @@
       </c>
     </row>
     <row r="697" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A697" s="14">
+      <c r="A697" s="38">
         <v>6106</v>
       </c>
       <c r="B697" s="14" t="s">
@@ -39394,7 +39449,7 @@
       </c>
     </row>
     <row r="698" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A698" s="14">
+      <c r="A698" s="38">
         <v>4403</v>
       </c>
       <c r="B698" s="14" t="s">
@@ -39442,7 +39497,7 @@
       </c>
     </row>
     <row r="699" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A699" s="14">
+      <c r="A699" s="38">
         <v>4668</v>
       </c>
       <c r="B699" s="14" t="s">
@@ -39486,7 +39541,7 @@
       </c>
     </row>
     <row r="700" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A700" s="14">
+      <c r="A700" s="38">
         <v>2076</v>
       </c>
       <c r="B700" s="14" t="s">
@@ -39530,7 +39585,7 @@
       </c>
     </row>
     <row r="701" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A701" s="14">
+      <c r="A701" s="38">
         <v>5600</v>
       </c>
       <c r="B701" s="14" t="s">
@@ -39574,7 +39629,7 @@
       </c>
     </row>
     <row r="702" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A702" s="14">
+      <c r="A702" s="38">
         <v>146</v>
       </c>
       <c r="B702" s="14" t="s">
@@ -39618,7 +39673,7 @@
       </c>
     </row>
     <row r="703" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A703" s="14">
+      <c r="A703" s="38">
         <v>8876</v>
       </c>
       <c r="B703" s="14" t="s">
@@ -39662,7 +39717,7 @@
       </c>
     </row>
     <row r="704" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A704" s="14">
+      <c r="A704" s="38">
         <v>4669</v>
       </c>
       <c r="B704" s="14" t="s">
@@ -39706,7 +39761,7 @@
       </c>
     </row>
     <row r="705" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A705" s="14">
+      <c r="A705" s="38">
         <v>2785</v>
       </c>
       <c r="B705" s="14" t="s">
@@ -39750,7 +39805,7 @@
       </c>
     </row>
     <row r="706" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A706" s="14">
+      <c r="A706" s="38">
         <v>3500</v>
       </c>
       <c r="B706" s="14" t="s">
@@ -39794,7 +39849,7 @@
       </c>
     </row>
     <row r="707" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A707" s="14">
+      <c r="A707" s="38">
         <v>4884</v>
       </c>
       <c r="B707" s="14" t="s">
@@ -39838,7 +39893,7 @@
       </c>
     </row>
     <row r="708" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A708" s="14">
+      <c r="A708" s="38">
         <v>567</v>
       </c>
       <c r="B708" s="14" t="s">
@@ -39882,7 +39937,7 @@
       </c>
     </row>
     <row r="709" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A709" s="14">
+      <c r="A709" s="38">
         <v>4269</v>
       </c>
       <c r="B709" s="14" t="s">
@@ -39926,7 +39981,7 @@
       </c>
     </row>
     <row r="710" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A710" s="14">
+      <c r="A710" s="38">
         <v>234</v>
       </c>
       <c r="B710" s="14" t="s">
@@ -39970,7 +40025,7 @@
       </c>
     </row>
     <row r="711" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A711" s="14">
+      <c r="A711" s="38">
         <v>574</v>
       </c>
       <c r="B711" s="14" t="s">
@@ -40014,7 +40069,7 @@
       </c>
     </row>
     <row r="712" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A712" s="14">
+      <c r="A712" s="38">
         <v>3526</v>
       </c>
       <c r="B712" s="14" t="s">
@@ -40058,7 +40113,7 @@
       </c>
     </row>
     <row r="713" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A713" s="14">
+      <c r="A713" s="38">
         <v>2710</v>
       </c>
       <c r="B713" s="14" t="s">
@@ -40102,7 +40157,7 @@
       </c>
     </row>
     <row r="714" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A714" s="14">
+      <c r="A714" s="38">
         <v>455</v>
       </c>
       <c r="B714" s="14" t="s">
@@ -40146,7 +40201,7 @@
       </c>
     </row>
     <row r="715" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A715" s="14">
+      <c r="A715" s="38">
         <v>5914</v>
       </c>
       <c r="B715" s="14" t="s">
@@ -40190,7 +40245,7 @@
       </c>
     </row>
     <row r="716" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A716" s="14">
+      <c r="A716" s="38">
         <v>6069</v>
       </c>
       <c r="B716" s="14" t="s">
@@ -40234,7 +40289,7 @@
       </c>
     </row>
     <row r="717" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A717" s="14">
+      <c r="A717" s="38">
         <v>6465</v>
       </c>
       <c r="B717" s="14" t="s">
@@ -40278,7 +40333,7 @@
       </c>
     </row>
     <row r="718" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A718" s="14">
+      <c r="A718" s="38">
         <v>308</v>
       </c>
       <c r="B718" s="14" t="s">
@@ -40322,7 +40377,7 @@
       </c>
     </row>
     <row r="719" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A719" s="14">
+      <c r="A719" s="38">
         <v>252</v>
       </c>
       <c r="B719" s="14" t="s">
@@ -40366,7 +40421,7 @@
       </c>
     </row>
     <row r="720" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A720" s="14">
+      <c r="A720" s="38">
         <v>5744</v>
       </c>
       <c r="B720" s="14" t="s">
@@ -40410,7 +40465,7 @@
       </c>
     </row>
     <row r="721" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A721" s="14">
+      <c r="A721" s="38">
         <v>141</v>
       </c>
       <c r="B721" s="14" t="s">
@@ -40454,7 +40509,7 @@
       </c>
     </row>
     <row r="722" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A722" s="14">
+      <c r="A722" s="38">
         <v>5790</v>
       </c>
       <c r="B722" s="14" t="s">
@@ -40498,7 +40553,7 @@
       </c>
     </row>
     <row r="723" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A723" s="14">
+      <c r="A723" s="38">
         <v>5835</v>
       </c>
       <c r="B723" s="14" t="s">
@@ -40542,7 +40597,7 @@
       </c>
     </row>
     <row r="724" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A724" s="14">
+      <c r="A724" s="38">
         <v>4369</v>
       </c>
       <c r="B724" s="14" t="s">
@@ -40586,7 +40641,7 @@
       </c>
     </row>
     <row r="725" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A725" s="14">
+      <c r="A725" s="38">
         <v>4405</v>
       </c>
       <c r="B725" s="14" t="s">
@@ -40630,7 +40685,7 @@
       </c>
     </row>
     <row r="726" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A726" s="14">
+      <c r="A726" s="38">
         <v>6302</v>
       </c>
       <c r="B726" s="14" t="s">
@@ -40674,7 +40729,7 @@
       </c>
     </row>
     <row r="727" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A727" s="14">
+      <c r="A727" s="38">
         <v>2702</v>
       </c>
       <c r="B727" s="14" t="s">
@@ -40718,7 +40773,7 @@
       </c>
     </row>
     <row r="728" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A728" s="14">
+      <c r="A728" s="38">
         <v>96</v>
       </c>
       <c r="B728" s="14" t="s">
@@ -40762,7 +40817,7 @@
       </c>
     </row>
     <row r="729" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A729" s="14">
+      <c r="A729" s="38">
         <v>239</v>
       </c>
       <c r="B729" s="14" t="s">
@@ -40806,7 +40861,7 @@
       </c>
     </row>
     <row r="730" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A730" s="14">
+      <c r="A730" s="38">
         <v>4888</v>
       </c>
       <c r="B730" s="14" t="s">
@@ -40850,7 +40905,7 @@
       </c>
     </row>
     <row r="731" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A731" s="14">
+      <c r="A731" s="38">
         <v>636</v>
       </c>
       <c r="B731" s="14" t="s">
@@ -40894,7 +40949,7 @@
       </c>
     </row>
     <row r="732" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A732" s="14">
+      <c r="A732" s="38">
         <v>6559</v>
       </c>
       <c r="B732" s="14" t="s">
@@ -40938,7 +40993,7 @@
       </c>
     </row>
     <row r="733" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A733" s="14">
+      <c r="A733" s="38">
         <v>2685</v>
       </c>
       <c r="B733" s="14" t="s">
@@ -40982,7 +41037,7 @@
       </c>
     </row>
     <row r="734" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A734" s="14">
+      <c r="A734" s="38">
         <v>5907</v>
       </c>
       <c r="B734" s="14" t="s">
@@ -41026,7 +41081,7 @@
       </c>
     </row>
     <row r="735" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A735" s="14">
+      <c r="A735" s="38">
         <v>6652</v>
       </c>
       <c r="B735" s="14" t="s">
@@ -41070,7 +41125,7 @@
       </c>
     </row>
     <row r="736" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A736" s="14">
+      <c r="A736" s="38">
         <v>6157</v>
       </c>
       <c r="B736" s="14" t="s">
@@ -41114,7 +41169,7 @@
       </c>
     </row>
     <row r="737" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A737" s="14">
+      <c r="A737" s="38">
         <v>197</v>
       </c>
       <c r="B737" s="14" t="s">
@@ -41158,7 +41213,7 @@
       </c>
     </row>
     <row r="738" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A738" s="14">
+      <c r="A738" s="38">
         <v>289</v>
       </c>
       <c r="B738" s="14" t="s">
@@ -41202,7 +41257,7 @@
       </c>
     </row>
     <row r="739" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A739" s="14">
+      <c r="A739" s="38">
         <v>3022</v>
       </c>
       <c r="B739" s="14" t="s">
@@ -41246,7 +41301,7 @@
       </c>
     </row>
     <row r="740" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A740" s="14">
+      <c r="A740" s="38">
         <v>2180</v>
       </c>
       <c r="B740" s="14" t="s">
@@ -41290,7 +41345,7 @@
       </c>
     </row>
     <row r="741" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A741" s="14">
+      <c r="A741" s="38">
         <v>2671</v>
       </c>
       <c r="B741" s="14" t="s">
@@ -41334,7 +41389,7 @@
       </c>
     </row>
     <row r="742" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A742" s="14">
+      <c r="A742" s="38">
         <v>2311</v>
       </c>
       <c r="B742" s="14" t="s">
@@ -41384,7 +41439,7 @@
       </c>
     </row>
     <row r="743" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A743" s="14">
+      <c r="A743" s="38">
         <v>5741</v>
       </c>
       <c r="B743" s="14" t="s">
@@ -41428,7 +41483,7 @@
       </c>
     </row>
     <row r="744" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A744" s="14">
+      <c r="A744" s="38">
         <v>406</v>
       </c>
       <c r="B744" s="14" t="s">
@@ -41472,7 +41527,7 @@
       </c>
     </row>
     <row r="745" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A745" s="14">
+      <c r="A745" s="38">
         <v>1310</v>
       </c>
       <c r="B745" s="14" t="s">
@@ -41522,7 +41577,7 @@
       </c>
     </row>
     <row r="746" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A746" s="14">
+      <c r="A746" s="38">
         <v>142</v>
       </c>
       <c r="B746" s="14" t="s">
@@ -41566,7 +41621,7 @@
       </c>
     </row>
     <row r="747" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A747" s="14">
+      <c r="A747" s="38">
         <v>5441</v>
       </c>
       <c r="B747" s="14" t="s">
@@ -41610,7 +41665,7 @@
       </c>
     </row>
     <row r="748" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A748" s="14">
+      <c r="A748" s="38">
         <v>2887</v>
       </c>
       <c r="B748" s="14" t="s">
@@ -41654,7 +41709,7 @@
       </c>
     </row>
     <row r="749" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A749" s="14">
+      <c r="A749" s="38">
         <v>2667</v>
       </c>
       <c r="B749" s="14" t="s">
@@ -41698,7 +41753,7 @@
       </c>
     </row>
     <row r="750" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A750" s="14">
+      <c r="A750" s="38">
         <v>6746</v>
       </c>
       <c r="B750" s="14" t="s">
@@ -41742,7 +41797,7 @@
       </c>
     </row>
     <row r="751" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A751" s="14">
+      <c r="A751" s="38">
         <v>304</v>
       </c>
       <c r="B751" s="14" t="s">
@@ -41790,7 +41845,7 @@
       </c>
     </row>
     <row r="752" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A752" s="14">
+      <c r="A752" s="38">
         <v>5852</v>
       </c>
       <c r="B752" s="14" t="s">
@@ -41834,7 +41889,7 @@
       </c>
     </row>
     <row r="753" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A753" s="14">
+      <c r="A753" s="38">
         <v>5405</v>
       </c>
       <c r="B753" s="14" t="s">
@@ -41878,7 +41933,7 @@
       </c>
     </row>
     <row r="754" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A754" s="14">
+      <c r="A754" s="38">
         <v>3578</v>
       </c>
       <c r="B754" s="14" t="s">
@@ -41922,7 +41977,7 @@
       </c>
     </row>
     <row r="755" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A755" s="14">
+      <c r="A755" s="38">
         <v>2179</v>
       </c>
       <c r="B755" s="14" t="s">
@@ -41966,7 +42021,7 @@
       </c>
     </row>
     <row r="756" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A756" s="14">
+      <c r="A756" s="38">
         <v>2665</v>
       </c>
       <c r="B756" s="14" t="s">
@@ -42010,7 +42065,7 @@
       </c>
     </row>
     <row r="757" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A757" s="14">
+      <c r="A757" s="38">
         <v>3591</v>
       </c>
       <c r="B757" s="14" t="s">
@@ -42054,7 +42109,7 @@
       </c>
     </row>
     <row r="758" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A758" s="14">
+      <c r="A758" s="38">
         <v>6743</v>
       </c>
       <c r="B758" s="14" t="s">
@@ -42098,7 +42153,7 @@
       </c>
     </row>
     <row r="759" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A759" s="14">
+      <c r="A759" s="38">
         <v>492</v>
       </c>
       <c r="B759" s="14" t="s">
@@ -42142,7 +42197,7 @@
       </c>
     </row>
     <row r="760" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A760" s="14">
+      <c r="A760" s="38">
         <v>5717</v>
       </c>
       <c r="B760" s="14" t="s">
@@ -42186,7 +42241,7 @@
       </c>
     </row>
     <row r="761" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A761" s="14">
+      <c r="A761" s="38">
         <v>2181</v>
       </c>
       <c r="B761" s="14" t="s">
@@ -42230,7 +42285,7 @@
       </c>
     </row>
     <row r="762" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A762" s="14">
+      <c r="A762" s="38">
         <v>5671</v>
       </c>
       <c r="B762" s="14" t="s">
@@ -42274,7 +42329,7 @@
       </c>
     </row>
     <row r="763" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A763" s="14">
+      <c r="A763" s="38">
         <v>6453</v>
       </c>
       <c r="B763" s="14" t="s">
@@ -42322,7 +42377,7 @@
       </c>
     </row>
     <row r="764" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A764" s="14">
+      <c r="A764" s="38">
         <v>3190</v>
       </c>
       <c r="B764" s="14" t="s">
@@ -42366,7 +42421,7 @@
       </c>
     </row>
     <row r="765" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A765" s="14">
+      <c r="A765" s="38">
         <v>2673</v>
       </c>
       <c r="B765" s="14" t="s">
@@ -42410,7 +42465,7 @@
       </c>
     </row>
     <row r="766" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A766" s="14">
+      <c r="A766" s="38">
         <v>6958</v>
       </c>
       <c r="B766" s="14" t="s">
@@ -42454,7 +42509,7 @@
       </c>
     </row>
     <row r="767" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A767" s="14">
+      <c r="A767" s="38">
         <v>6369</v>
       </c>
       <c r="B767" s="14" t="s">
@@ -42498,7 +42553,7 @@
       </c>
     </row>
     <row r="768" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A768" s="14">
+      <c r="A768" s="38">
         <v>3570</v>
       </c>
       <c r="B768" s="14" t="s">
@@ -42542,7 +42597,7 @@
       </c>
     </row>
     <row r="769" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A769" s="14">
+      <c r="A769" s="38">
         <v>8244</v>
       </c>
       <c r="B769" s="14" t="s">
@@ -42586,7 +42641,7 @@
       </c>
     </row>
     <row r="770" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A770" s="14">
+      <c r="A770" s="38">
         <v>6580</v>
       </c>
       <c r="B770" s="14" t="s">
@@ -42630,7 +42685,7 @@
       </c>
     </row>
     <row r="771" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A771" s="14">
+      <c r="A771" s="38">
         <v>3961</v>
       </c>
       <c r="B771" s="14" t="s">
@@ -42674,7 +42729,7 @@
       </c>
     </row>
     <row r="772" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A772" s="14">
+      <c r="A772" s="38">
         <v>6461</v>
       </c>
       <c r="B772" s="14" t="s">
@@ -42718,7 +42773,7 @@
       </c>
     </row>
     <row r="773" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A773" s="14">
+      <c r="A773" s="38">
         <v>6033</v>
       </c>
       <c r="B773" s="14" t="s">
@@ -42762,7 +42817,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S773" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <conditionalFormatting sqref="B2:B773">
     <cfRule type="expression" dxfId="4" priority="5">
       <formula>$H2&lt;&gt;""</formula>
